--- a/docs/OnSite-forecast-PnL.xlsx
+++ b/docs/OnSite-forecast-PnL.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t xml:space="preserve">OnSite - forecast assumptions (blue = editable inputs). All amounts AUD, excluding GST.</t>
   </si>
@@ -152,7 +152,10 @@
     <t xml:space="preserve">New parks</t>
   </si>
   <si>
-    <t xml:space="preserve">OnSite - 12-month forecast profit &amp; loss (AUD, ex GST)</t>
+    <t xml:space="preserve">Monthly churn (% of parks at start of month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnSite - 24-month forecast profit &amp; loss (AUD, ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">M1</t>
@@ -191,10 +194,52 @@
     <t xml:space="preserve">M12</t>
   </si>
   <si>
+    <t xml:space="preserve">M13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Year 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Year 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">New parks signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parks churned</t>
   </si>
   <si>
     <t xml:space="preserve">Parks at start</t>
@@ -281,8 +326,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -370,7 +415,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,15 +436,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -655,7 +704,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -950,6 +999,42 @@
       <c r="M30" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="N30" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="R30" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="S30" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="U30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="V30" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="W30" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="X30" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y30" s="0" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
@@ -990,6 +1075,119 @@
       </c>
       <c r="M31" s="3" t="n">
         <v>56</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -1008,16 +1206,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1025,1518 +1223,3002 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <f aca="false">Assumptions!B31</f>
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <f aca="false">Assumptions!C31</f>
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <f aca="false">Assumptions!D31</f>
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <f aca="false">Assumptions!E31</f>
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <f aca="false">Assumptions!F31</f>
         <v>2</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <f aca="false">Assumptions!G31</f>
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <f aca="false">Assumptions!H31</f>
         <v>12</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <f aca="false">Assumptions!I31</f>
         <v>18</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <f aca="false">Assumptions!J31</f>
         <v>26</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <f aca="false">Assumptions!K31</f>
         <v>34</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="6" t="n">
         <f aca="false">Assumptions!L31</f>
         <v>42</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="6" t="n">
         <f aca="false">Assumptions!M31</f>
         <v>56</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="6" t="n">
+        <f aca="false">Assumptions!N31</f>
+        <v>30</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <f aca="false">Assumptions!O31</f>
+        <v>30</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <f aca="false">Assumptions!P31</f>
+        <v>30</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <f aca="false">Assumptions!Q31</f>
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <f aca="false">Assumptions!R31</f>
+        <v>30</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <f aca="false">Assumptions!S31</f>
+        <v>30</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <f aca="false">Assumptions!T31</f>
+        <v>30</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <f aca="false">Assumptions!U31</f>
+        <v>30</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <f aca="false">Assumptions!V31</f>
+        <v>30</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <f aca="false">Assumptions!W31</f>
+        <v>30</v>
+      </c>
+      <c r="X3" s="6" t="n">
+        <f aca="false">Assumptions!X31</f>
+        <v>30</v>
+      </c>
+      <c r="Y3" s="6" t="n">
+        <f aca="false">Assumptions!Y31</f>
+        <v>30</v>
+      </c>
+      <c r="Z3" s="6" t="n">
         <f aca="false">SUM(B3:M3)</f>
         <v>200</v>
       </c>
+      <c r="AA3" s="6" t="n">
+        <f aca="false">SUM(N3:Y3)</f>
+        <v>360</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <f aca="false">B5*Assumptions!B32</f>
         <v>0</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <f aca="false">B5</f>
+      <c r="C4" s="6" t="n">
+        <f aca="false">C5*Assumptions!C32</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <f aca="false">D5*Assumptions!D32</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <f aca="false">E5*Assumptions!E32</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <f aca="false">F5*Assumptions!F32</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <f aca="false">G5*Assumptions!G32</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <f aca="false">H5*Assumptions!H32</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <f aca="false">I5*Assumptions!I32</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <f aca="false">J5*Assumptions!J32</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <f aca="false">K5*Assumptions!K32</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <f aca="false">L5*Assumptions!L32</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <f aca="false">M5*Assumptions!M32</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <f aca="false">N5*Assumptions!N32</f>
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <f aca="false">C5</f>
-        <v>4</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <f aca="false">D5</f>
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <f aca="false">E5</f>
-        <v>8</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <f aca="false">F5</f>
-        <v>10</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <f aca="false">G5</f>
-        <v>12</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <f aca="false">H5</f>
-        <v>24</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <f aca="false">I5</f>
-        <v>42</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <f aca="false">J5</f>
-        <v>68</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <f aca="false">K5</f>
-        <v>102</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <f aca="false">L5</f>
-        <v>144</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <f aca="false">B4</f>
+      <c r="O4" s="6" t="n">
+        <f aca="false">O5*Assumptions!O32</f>
+        <v>2.28</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <f aca="false">P5*Assumptions!P32</f>
+        <v>2.5572</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <f aca="false">Q5*Assumptions!Q32</f>
+        <v>2.831628</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <f aca="false">R5*Assumptions!R32</f>
+        <v>3.10331172</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <f aca="false">S5*Assumptions!S32</f>
+        <v>3.3722786028</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <f aca="false">T5*Assumptions!T32</f>
+        <v>3.638555816772</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <f aca="false">U5*Assumptions!U32</f>
+        <v>3.90217025860428</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <f aca="false">V5*Assumptions!V32</f>
+        <v>4.16314855601824</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <f aca="false">W5*Assumptions!W32</f>
+        <v>4.42151707045805</v>
+      </c>
+      <c r="X4" s="6" t="n">
+        <f aca="false">X5*Assumptions!X32</f>
+        <v>4.67730189975347</v>
+      </c>
+      <c r="Y4" s="6" t="n">
+        <f aca="false">Y5*Assumptions!Y32</f>
+        <v>4.93052888075594</v>
+      </c>
+      <c r="Z4" s="6" t="n">
+        <f aca="false">SUM(B4:M4)</f>
         <v>0</v>
+      </c>
+      <c r="AA4" s="6" t="n">
+        <f aca="false">SUM(N4:Y4)</f>
+        <v>41.877640805162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <f aca="false">B4+B3</f>
+        <v>73</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <f aca="false">B6</f>
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <f aca="false">C4+C3</f>
+      <c r="D5" s="6" t="n">
+        <f aca="false">C6</f>
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <f aca="false">D4+D3</f>
+      <c r="E5" s="6" t="n">
+        <f aca="false">D6</f>
         <v>6</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <f aca="false">E4+E3</f>
+      <c r="F5" s="6" t="n">
+        <f aca="false">E6</f>
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <f aca="false">F4+F3</f>
+      <c r="G5" s="6" t="n">
+        <f aca="false">F6</f>
         <v>10</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <f aca="false">G4+G3</f>
+      <c r="H5" s="6" t="n">
+        <f aca="false">G6</f>
         <v>12</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <f aca="false">H4+H3</f>
+      <c r="I5" s="6" t="n">
+        <f aca="false">H6</f>
         <v>24</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <f aca="false">I4+I3</f>
+      <c r="J5" s="6" t="n">
+        <f aca="false">I6</f>
         <v>42</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <f aca="false">J4+J3</f>
+      <c r="K5" s="6" t="n">
+        <f aca="false">J6</f>
         <v>68</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <f aca="false">K4+K3</f>
+      <c r="L5" s="6" t="n">
+        <f aca="false">K6</f>
         <v>102</v>
       </c>
-      <c r="L5" s="5" t="n">
-        <f aca="false">L4+L3</f>
+      <c r="M5" s="6" t="n">
+        <f aca="false">L6</f>
         <v>144</v>
       </c>
-      <c r="M5" s="5" t="n">
-        <f aca="false">M4+M3</f>
+      <c r="N5" s="6" t="n">
+        <f aca="false">M6</f>
         <v>200</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <f aca="false">M5</f>
+      <c r="O5" s="6" t="n">
+        <f aca="false">N6</f>
+        <v>228</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <f aca="false">O6</f>
+        <v>255.72</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <f aca="false">P6</f>
+        <v>283.1628</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <f aca="false">Q6</f>
+        <v>310.331172</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <f aca="false">R6</f>
+        <v>337.22786028</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <f aca="false">S6</f>
+        <v>363.8555816772</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <f aca="false">T6</f>
+        <v>390.217025860428</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <f aca="false">U6</f>
+        <v>416.314855601824</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <f aca="false">V6</f>
+        <v>442.151707045805</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <f aca="false">W6</f>
+        <v>467.730189975347</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <f aca="false">X6</f>
+        <v>493.052888075594</v>
+      </c>
+      <c r="Z5" s="6" t="n">
+        <f aca="false">B5</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="6" t="n">
+        <f aca="false">N5</f>
         <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <f aca="false">(B4+B5)/2</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <f aca="false">(C4+C5)/2</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <f aca="false">(D4+D5)/2</f>
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <f aca="false">(E4+E5)/2</f>
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <f aca="false">(F4+F5)/2</f>
-        <v>9</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <f aca="false">(G4+G5)/2</f>
-        <v>11</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <f aca="false">(H4+H5)/2</f>
-        <v>18</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <f aca="false">(I4+I5)/2</f>
-        <v>33</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <f aca="false">(J4+J5)/2</f>
-        <v>55</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <f aca="false">(K4+K5)/2</f>
-        <v>85</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <f aca="false">(L4+L5)/2</f>
-        <v>123</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <f aca="false">(M4+M5)/2</f>
-        <v>172</v>
-      </c>
-      <c r="N6" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <f aca="false">B5+B3-B4</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <f aca="false">C5+C3-C4</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <f aca="false">D5+D3-D4</f>
+        <v>6</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <f aca="false">E5+E3-E4</f>
+        <v>8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <f aca="false">F5+F3-F4</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <f aca="false">G5+G3-G4</f>
+        <v>12</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <f aca="false">H5+H3-H4</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <f aca="false">I5+I3-I4</f>
+        <v>42</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <f aca="false">J5+J3-J4</f>
+        <v>68</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <f aca="false">K5+K3-K4</f>
+        <v>102</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <f aca="false">L5+L3-L4</f>
+        <v>144</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">M5+M3-M4</f>
+        <v>200</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <f aca="false">N5+N3-N4</f>
+        <v>228</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <f aca="false">O5+O3-O4</f>
+        <v>255.72</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <f aca="false">P5+P3-P4</f>
+        <v>283.1628</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <f aca="false">Q5+Q3-Q4</f>
+        <v>310.331172</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <f aca="false">R5+R3-R4</f>
+        <v>337.22786028</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <f aca="false">S5+S3-S4</f>
+        <v>363.8555816772</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <f aca="false">T5+T3-T4</f>
+        <v>390.217025860428</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <f aca="false">U5+U3-U4</f>
+        <v>416.314855601824</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <f aca="false">V5+V3-V4</f>
+        <v>442.151707045805</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <f aca="false">W5+W3-W4</f>
+        <v>467.730189975347</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <f aca="false">X5+X3-X4</f>
+        <v>493.052888075594</v>
+      </c>
+      <c r="Y6" s="6" t="n">
+        <f aca="false">Y5+Y3-Y4</f>
+        <v>518.122359194838</v>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <f aca="false">M6</f>
+        <v>200</v>
+      </c>
+      <c r="AA6" s="6" t="n">
+        <f aca="false">Y6</f>
+        <v>518.122359194838</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <f aca="false">B6*Assumptions!$B$27</f>
+        <v>75</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <f aca="false">(B5+B6)/2</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <f aca="false">(C5+C6)/2</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <f aca="false">(D5+D6)/2</f>
+        <v>5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <f aca="false">(E5+E6)/2</f>
+        <v>7</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <f aca="false">(F5+F6)/2</f>
+        <v>9</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <f aca="false">(G5+G6)/2</f>
+        <v>11</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <f aca="false">(H5+H6)/2</f>
+        <v>18</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <f aca="false">(I5+I6)/2</f>
+        <v>33</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <f aca="false">(J5+J6)/2</f>
+        <v>55</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <f aca="false">(K5+K6)/2</f>
+        <v>85</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <f aca="false">(L5+L6)/2</f>
+        <v>123</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <f aca="false">(M5+M6)/2</f>
+        <v>172</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <f aca="false">(N5+N6)/2</f>
+        <v>214</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <f aca="false">(O5+O6)/2</f>
+        <v>241.86</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <f aca="false">(P5+P6)/2</f>
+        <v>269.4414</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <f aca="false">(Q5+Q6)/2</f>
+        <v>296.746986</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <f aca="false">(R5+R6)/2</f>
+        <v>323.77951614</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <f aca="false">(S5+S6)/2</f>
+        <v>350.5417209786</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <f aca="false">(T5+T6)/2</f>
+        <v>377.036303768814</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <f aca="false">(U5+U6)/2</f>
+        <v>403.265940731126</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <f aca="false">(V5+V6)/2</f>
+        <v>429.233281323815</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <f aca="false">(W5+W6)/2</f>
+        <v>454.940948510576</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <f aca="false">(X5+X6)/2</f>
+        <v>480.391539025471</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <f aca="false">(Y5+Y6)/2</f>
+        <v>505.587623635216</v>
+      </c>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <f aca="false">B7*Assumptions!$B$27</f>
         <v>65</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <f aca="false">C6*Assumptions!$B$27</f>
+      <c r="C8" s="6" t="n">
+        <f aca="false">C7*Assumptions!$B$27</f>
         <v>195</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <f aca="false">D6*Assumptions!$B$27</f>
+      <c r="D8" s="6" t="n">
+        <f aca="false">D7*Assumptions!$B$27</f>
         <v>325</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <f aca="false">E6*Assumptions!$B$27</f>
+      <c r="E8" s="6" t="n">
+        <f aca="false">E7*Assumptions!$B$27</f>
         <v>455</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <f aca="false">F6*Assumptions!$B$27</f>
+      <c r="F8" s="6" t="n">
+        <f aca="false">F7*Assumptions!$B$27</f>
         <v>585</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">G6*Assumptions!$B$27</f>
+      <c r="G8" s="6" t="n">
+        <f aca="false">G7*Assumptions!$B$27</f>
         <v>715</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <f aca="false">H6*Assumptions!$B$27</f>
+      <c r="H8" s="6" t="n">
+        <f aca="false">H7*Assumptions!$B$27</f>
         <v>1170</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <f aca="false">I6*Assumptions!$B$27</f>
+      <c r="I8" s="6" t="n">
+        <f aca="false">I7*Assumptions!$B$27</f>
         <v>2145</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <f aca="false">J6*Assumptions!$B$27</f>
+      <c r="J8" s="6" t="n">
+        <f aca="false">J7*Assumptions!$B$27</f>
         <v>3575</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <f aca="false">K6*Assumptions!$B$27</f>
+      <c r="K8" s="6" t="n">
+        <f aca="false">K7*Assumptions!$B$27</f>
         <v>5525</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <f aca="false">L6*Assumptions!$B$27</f>
+      <c r="L8" s="6" t="n">
+        <f aca="false">L7*Assumptions!$B$27</f>
         <v>7995</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <f aca="false">M6*Assumptions!$B$27</f>
+      <c r="M8" s="6" t="n">
+        <f aca="false">M7*Assumptions!$B$27</f>
         <v>11180</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <f aca="false">SUM(B7:M7)</f>
+      <c r="N8" s="6" t="n">
+        <f aca="false">N7*Assumptions!$B$27</f>
+        <v>13910</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <f aca="false">O7*Assumptions!$B$27</f>
+        <v>15720.9</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <f aca="false">P7*Assumptions!$B$27</f>
+        <v>17513.691</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <f aca="false">Q7*Assumptions!$B$27</f>
+        <v>19288.55409</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <f aca="false">R7*Assumptions!$B$27</f>
+        <v>21045.6685491</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <f aca="false">S7*Assumptions!$B$27</f>
+        <v>22785.211863609</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <f aca="false">T7*Assumptions!$B$27</f>
+        <v>24507.3597449729</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <f aca="false">U7*Assumptions!$B$27</f>
+        <v>26212.2861475232</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <f aca="false">V7*Assumptions!$B$27</f>
+        <v>27900.1632860479</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <f aca="false">W7*Assumptions!$B$27</f>
+        <v>29571.1616531875</v>
+      </c>
+      <c r="X8" s="6" t="n">
+        <f aca="false">X7*Assumptions!$B$27</f>
+        <v>31225.4500366556</v>
+      </c>
+      <c r="Y8" s="6" t="n">
+        <f aca="false">Y7*Assumptions!$B$27</f>
+        <v>32863.195536289</v>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <f aca="false">SUM(B8:M8)</f>
         <v>33930</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="AA8" s="6" t="n">
+        <f aca="false">SUM(N8:Y8)</f>
+        <v>282543.641907385</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <f aca="false">B6*Assumptions!$B$4</f>
-        <v>100</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <f aca="false">C6*Assumptions!$B$4</f>
-        <v>300</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">D6*Assumptions!$B$4</f>
-        <v>500</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <f aca="false">E6*Assumptions!$B$4</f>
-        <v>700</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <f aca="false">F6*Assumptions!$B$4</f>
-        <v>900</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">G6*Assumptions!$B$4</f>
-        <v>1100</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <f aca="false">H6*Assumptions!$B$4</f>
-        <v>1800</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <f aca="false">I6*Assumptions!$B$4</f>
-        <v>3300</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <f aca="false">J6*Assumptions!$B$4</f>
-        <v>5500</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <f aca="false">K6*Assumptions!$B$4</f>
-        <v>8500</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <f aca="false">L6*Assumptions!$B$4</f>
-        <v>12300</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <f aca="false">M6*Assumptions!$B$4</f>
-        <v>17200</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <f aca="false">SUM(B9:M9)</f>
-        <v>52200</v>
-      </c>
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <f aca="false">B7*Assumptions!$B$5</f>
+        <v>78</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <f aca="false">B7*Assumptions!$B$4</f>
+        <v>100</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <f aca="false">C7*Assumptions!$B$4</f>
+        <v>300</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <f aca="false">D7*Assumptions!$B$4</f>
+        <v>500</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <f aca="false">E7*Assumptions!$B$4</f>
+        <v>700</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <f aca="false">F7*Assumptions!$B$4</f>
+        <v>900</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <f aca="false">G7*Assumptions!$B$4</f>
+        <v>1100</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <f aca="false">H7*Assumptions!$B$4</f>
+        <v>1800</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <f aca="false">I7*Assumptions!$B$4</f>
+        <v>3300</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <f aca="false">J7*Assumptions!$B$4</f>
+        <v>5500</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <f aca="false">K7*Assumptions!$B$4</f>
+        <v>8500</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <f aca="false">L7*Assumptions!$B$4</f>
+        <v>12300</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <f aca="false">M7*Assumptions!$B$4</f>
+        <v>17200</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <f aca="false">N7*Assumptions!$B$4</f>
+        <v>21400</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <f aca="false">O7*Assumptions!$B$4</f>
+        <v>24186</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <f aca="false">P7*Assumptions!$B$4</f>
+        <v>26944.14</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <f aca="false">Q7*Assumptions!$B$4</f>
+        <v>29674.6986</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <f aca="false">R7*Assumptions!$B$4</f>
+        <v>32377.951614</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <f aca="false">S7*Assumptions!$B$4</f>
+        <v>35054.17209786</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <f aca="false">T7*Assumptions!$B$4</f>
+        <v>37703.6303768814</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <f aca="false">U7*Assumptions!$B$4</f>
+        <v>40326.5940731126</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <f aca="false">V7*Assumptions!$B$4</f>
+        <v>42923.3281323815</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <f aca="false">W7*Assumptions!$B$4</f>
+        <v>45494.0948510576</v>
+      </c>
+      <c r="X10" s="6" t="n">
+        <f aca="false">X7*Assumptions!$B$4</f>
+        <v>48039.1539025471</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <f aca="false">Y7*Assumptions!$B$4</f>
+        <v>50558.7623635216</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <f aca="false">SUM(B10:M10)</f>
+        <v>52200</v>
+      </c>
+      <c r="AA10" s="6" t="n">
+        <f aca="false">SUM(N10:Y10)</f>
+        <v>434682.526011362</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <f aca="false">B8*Assumptions!$B$5</f>
         <v>195</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <f aca="false">C7*Assumptions!$B$5</f>
+      <c r="C11" s="6" t="n">
+        <f aca="false">C8*Assumptions!$B$5</f>
         <v>585</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <f aca="false">D7*Assumptions!$B$5</f>
+      <c r="D11" s="6" t="n">
+        <f aca="false">D8*Assumptions!$B$5</f>
         <v>975</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <f aca="false">E7*Assumptions!$B$5</f>
+      <c r="E11" s="6" t="n">
+        <f aca="false">E8*Assumptions!$B$5</f>
         <v>1365</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <f aca="false">F7*Assumptions!$B$5</f>
+      <c r="F11" s="6" t="n">
+        <f aca="false">F8*Assumptions!$B$5</f>
         <v>1755</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <f aca="false">G7*Assumptions!$B$5</f>
+      <c r="G11" s="6" t="n">
+        <f aca="false">G8*Assumptions!$B$5</f>
         <v>2145</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <f aca="false">H7*Assumptions!$B$5</f>
+      <c r="H11" s="6" t="n">
+        <f aca="false">H8*Assumptions!$B$5</f>
         <v>3510</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <f aca="false">I7*Assumptions!$B$5</f>
+      <c r="I11" s="6" t="n">
+        <f aca="false">I8*Assumptions!$B$5</f>
         <v>6435</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <f aca="false">J7*Assumptions!$B$5</f>
+      <c r="J11" s="6" t="n">
+        <f aca="false">J8*Assumptions!$B$5</f>
         <v>10725</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <f aca="false">K7*Assumptions!$B$5</f>
+      <c r="K11" s="6" t="n">
+        <f aca="false">K8*Assumptions!$B$5</f>
         <v>16575</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <f aca="false">L7*Assumptions!$B$5</f>
+      <c r="L11" s="6" t="n">
+        <f aca="false">L8*Assumptions!$B$5</f>
         <v>23985</v>
       </c>
-      <c r="M10" s="5" t="n">
-        <f aca="false">M7*Assumptions!$B$5</f>
+      <c r="M11" s="6" t="n">
+        <f aca="false">M8*Assumptions!$B$5</f>
         <v>33540</v>
       </c>
-      <c r="N10" s="5" t="n">
-        <f aca="false">SUM(B10:M10)</f>
+      <c r="N11" s="6" t="n">
+        <f aca="false">N8*Assumptions!$B$5</f>
+        <v>41730</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <f aca="false">O8*Assumptions!$B$5</f>
+        <v>47162.7</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <f aca="false">P8*Assumptions!$B$5</f>
+        <v>52541.073</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <f aca="false">Q8*Assumptions!$B$5</f>
+        <v>57865.66227</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <f aca="false">R8*Assumptions!$B$5</f>
+        <v>63137.0056473</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <f aca="false">S8*Assumptions!$B$5</f>
+        <v>68355.635590827</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <f aca="false">T8*Assumptions!$B$5</f>
+        <v>73522.0792349187</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <f aca="false">U8*Assumptions!$B$5</f>
+        <v>78636.8584425695</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <f aca="false">V8*Assumptions!$B$5</f>
+        <v>83700.4898581439</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <f aca="false">W8*Assumptions!$B$5</f>
+        <v>88713.4849595624</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <f aca="false">X8*Assumptions!$B$5</f>
+        <v>93676.3501099668</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <f aca="false">Y8*Assumptions!$B$5</f>
+        <v>98589.5866088671</v>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <f aca="false">SUM(B11:M11)</f>
         <v>101790</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <f aca="false">B9+B10</f>
+      <c r="AA11" s="6" t="n">
+        <f aca="false">SUM(N11:Y11)</f>
+        <v>847630.925722155</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">B10+B11</f>
         <v>295</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <f aca="false">C9+C10</f>
+      <c r="C12" s="7" t="n">
+        <f aca="false">C10+C11</f>
         <v>885</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <f aca="false">D9+D10</f>
+      <c r="D12" s="7" t="n">
+        <f aca="false">D10+D11</f>
         <v>1475</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <f aca="false">E9+E10</f>
+      <c r="E12" s="7" t="n">
+        <f aca="false">E10+E11</f>
         <v>2065</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <f aca="false">F9+F10</f>
+      <c r="F12" s="7" t="n">
+        <f aca="false">F10+F11</f>
         <v>2655</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <f aca="false">G9+G10</f>
+      <c r="G12" s="7" t="n">
+        <f aca="false">G10+G11</f>
         <v>3245</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false">H9+H10</f>
+      <c r="H12" s="7" t="n">
+        <f aca="false">H10+H11</f>
         <v>5310</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <f aca="false">I9+I10</f>
+      <c r="I12" s="7" t="n">
+        <f aca="false">I10+I11</f>
         <v>9735</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <f aca="false">J9+J10</f>
+      <c r="J12" s="7" t="n">
+        <f aca="false">J10+J11</f>
         <v>16225</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <f aca="false">K9+K10</f>
+      <c r="K12" s="7" t="n">
+        <f aca="false">K10+K11</f>
         <v>25075</v>
       </c>
-      <c r="L11" s="6" t="n">
-        <f aca="false">L9+L10</f>
+      <c r="L12" s="7" t="n">
+        <f aca="false">L10+L11</f>
         <v>36285</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <f aca="false">M9+M10</f>
+      <c r="M12" s="7" t="n">
+        <f aca="false">M10+M11</f>
         <v>50740</v>
       </c>
-      <c r="N11" s="6" t="n">
-        <f aca="false">SUM(B11:M11)</f>
+      <c r="N12" s="7" t="n">
+        <f aca="false">N10+N11</f>
+        <v>63130</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <f aca="false">O10+O11</f>
+        <v>71348.7</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <f aca="false">P10+P11</f>
+        <v>79485.213</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <f aca="false">Q10+Q11</f>
+        <v>87540.36087</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <f aca="false">R10+R11</f>
+        <v>95514.9572613</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <f aca="false">S10+S11</f>
+        <v>103409.807688687</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <f aca="false">T10+T11</f>
+        <v>111225.7096118</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <f aca="false">U10+U11</f>
+        <v>118963.452515682</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <f aca="false">V10+V11</f>
+        <v>126623.817990525</v>
+      </c>
+      <c r="W12" s="7" t="n">
+        <f aca="false">W10+W11</f>
+        <v>134207.57981062</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <f aca="false">X10+X11</f>
+        <v>141715.504012514</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <f aca="false">Y10+Y11</f>
+        <v>149148.348972389</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <f aca="false">SUM(B12:M12)</f>
         <v>153990</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
+      <c r="AA12" s="7" t="n">
+        <f aca="false">SUM(N12:Y12)</f>
+        <v>1282313.45173352</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <f aca="false">B7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>39</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <f aca="false">C7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>117</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <f aca="false">D7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>195</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <f aca="false">E7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>273</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <f aca="false">F7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>351</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <f aca="false">G7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>429</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <f aca="false">H7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>702</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <f aca="false">I7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>1287</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <f aca="false">J7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>2145</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <f aca="false">K7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>3315</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <f aca="false">L7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>4797</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <f aca="false">M7*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
-        <v>6708</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <f aca="false">SUM(B13:M13)</f>
-        <v>20358</v>
-      </c>
+      <c r="A13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <f aca="false">B6*Assumptions!$B$15</f>
-        <v>6</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <f aca="false">C6*Assumptions!$B$15</f>
-        <v>18</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <f aca="false">D6*Assumptions!$B$15</f>
-        <v>30</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <f aca="false">E6*Assumptions!$B$15</f>
-        <v>42</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <f aca="false">F6*Assumptions!$B$15</f>
-        <v>54</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <f aca="false">G6*Assumptions!$B$15</f>
-        <v>66</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <f aca="false">H6*Assumptions!$B$15</f>
-        <v>108</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <f aca="false">I6*Assumptions!$B$15</f>
-        <v>198</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <f aca="false">J6*Assumptions!$B$15</f>
-        <v>330</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <f aca="false">K6*Assumptions!$B$15</f>
-        <v>510</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <f aca="false">L6*Assumptions!$B$15</f>
-        <v>738</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <f aca="false">M6*Assumptions!$B$15</f>
-        <v>1032</v>
-      </c>
-      <c r="N14" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <f aca="false">B8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <f aca="false">C8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>117</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <f aca="false">D8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>195</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <f aca="false">E8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>273</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <f aca="false">F8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>351</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <f aca="false">G8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>429</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <f aca="false">H8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>702</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <f aca="false">I8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>1287</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <f aca="false">J8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>2145</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <f aca="false">K8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>3315</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <f aca="false">L8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>4797</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <f aca="false">M8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>6708</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <f aca="false">N8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>8346</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <f aca="false">O8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>9432.54</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <f aca="false">P8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>10508.2146</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <f aca="false">Q8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>11573.132454</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <f aca="false">R8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>12627.40112946</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <f aca="false">S8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>13671.1271181654</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <f aca="false">T8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>14704.4158469837</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <f aca="false">U8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>15727.3716885139</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <f aca="false">V8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>16740.0979716288</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <f aca="false">W8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>17742.6969919125</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <f aca="false">X8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>18735.2700219934</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <f aca="false">Y8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>19717.9173217734</v>
+      </c>
+      <c r="Z14" s="6" t="n">
         <f aca="false">SUM(B14:M14)</f>
-        <v>3132</v>
+        <v>20358</v>
+      </c>
+      <c r="AA14" s="6" t="n">
+        <f aca="false">SUM(N14:Y14)</f>
+        <v>169526.185144431</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <f aca="false">B6*Assumptions!$B$17</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <f aca="false">C6*Assumptions!$B$17</f>
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <f aca="false">D6*Assumptions!$B$17</f>
-        <v>5</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <f aca="false">E6*Assumptions!$B$17</f>
-        <v>7</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <f aca="false">F6*Assumptions!$B$17</f>
-        <v>9</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <f aca="false">G6*Assumptions!$B$17</f>
-        <v>11</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <f aca="false">H6*Assumptions!$B$17</f>
+        <v>83</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <f aca="false">B7*Assumptions!$B$15</f>
+        <v>6</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <f aca="false">C7*Assumptions!$B$15</f>
         <v>18</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <f aca="false">I6*Assumptions!$B$17</f>
-        <v>33</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <f aca="false">J6*Assumptions!$B$17</f>
-        <v>55</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <f aca="false">K6*Assumptions!$B$17</f>
-        <v>85</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <f aca="false">L6*Assumptions!$B$17</f>
-        <v>123</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <f aca="false">M6*Assumptions!$B$17</f>
-        <v>172</v>
-      </c>
-      <c r="N15" s="5" t="n">
+      <c r="D15" s="6" t="n">
+        <f aca="false">D7*Assumptions!$B$15</f>
+        <v>30</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">E7*Assumptions!$B$15</f>
+        <v>42</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <f aca="false">F7*Assumptions!$B$15</f>
+        <v>54</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <f aca="false">G7*Assumptions!$B$15</f>
+        <v>66</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <f aca="false">H7*Assumptions!$B$15</f>
+        <v>108</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <f aca="false">I7*Assumptions!$B$15</f>
+        <v>198</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <f aca="false">J7*Assumptions!$B$15</f>
+        <v>330</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <f aca="false">K7*Assumptions!$B$15</f>
+        <v>510</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <f aca="false">L7*Assumptions!$B$15</f>
+        <v>738</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <f aca="false">M7*Assumptions!$B$15</f>
+        <v>1032</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <f aca="false">N7*Assumptions!$B$15</f>
+        <v>1284</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <f aca="false">O7*Assumptions!$B$15</f>
+        <v>1451.16</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <f aca="false">P7*Assumptions!$B$15</f>
+        <v>1616.6484</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <f aca="false">Q7*Assumptions!$B$15</f>
+        <v>1780.481916</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <f aca="false">R7*Assumptions!$B$15</f>
+        <v>1942.67709684</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <f aca="false">S7*Assumptions!$B$15</f>
+        <v>2103.2503258716</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <f aca="false">T7*Assumptions!$B$15</f>
+        <v>2262.21782261288</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <f aca="false">U7*Assumptions!$B$15</f>
+        <v>2419.59564438676</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <f aca="false">V7*Assumptions!$B$15</f>
+        <v>2575.39968794289</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <f aca="false">W7*Assumptions!$B$15</f>
+        <v>2729.64569106346</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <f aca="false">X7*Assumptions!$B$15</f>
+        <v>2882.34923415282</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <f aca="false">Y7*Assumptions!$B$15</f>
+        <v>3033.5257418113</v>
+      </c>
+      <c r="Z15" s="6" t="n">
         <f aca="false">SUM(B15:M15)</f>
-        <v>522</v>
+        <v>3132</v>
+      </c>
+      <c r="AA15" s="6" t="n">
+        <f aca="false">SUM(N15:Y15)</f>
+        <v>26080.9515606817</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <f aca="false">B13+B14+B15</f>
+        <v>84</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <f aca="false">B7*Assumptions!$B$17</f>
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <f aca="false">C7*Assumptions!$B$17</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <f aca="false">D7*Assumptions!$B$17</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">E7*Assumptions!$B$17</f>
+        <v>7</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <f aca="false">F7*Assumptions!$B$17</f>
+        <v>9</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <f aca="false">G7*Assumptions!$B$17</f>
+        <v>11</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <f aca="false">H7*Assumptions!$B$17</f>
+        <v>18</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <f aca="false">I7*Assumptions!$B$17</f>
+        <v>33</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <f aca="false">J7*Assumptions!$B$17</f>
+        <v>55</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <f aca="false">K7*Assumptions!$B$17</f>
+        <v>85</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <f aca="false">L7*Assumptions!$B$17</f>
+        <v>123</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <f aca="false">M7*Assumptions!$B$17</f>
+        <v>172</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <f aca="false">N7*Assumptions!$B$17</f>
+        <v>214</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <f aca="false">O7*Assumptions!$B$17</f>
+        <v>241.86</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <f aca="false">P7*Assumptions!$B$17</f>
+        <v>269.4414</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <f aca="false">Q7*Assumptions!$B$17</f>
+        <v>296.746986</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <f aca="false">R7*Assumptions!$B$17</f>
+        <v>323.77951614</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <f aca="false">S7*Assumptions!$B$17</f>
+        <v>350.5417209786</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <f aca="false">T7*Assumptions!$B$17</f>
+        <v>377.036303768814</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <f aca="false">U7*Assumptions!$B$17</f>
+        <v>403.265940731126</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <f aca="false">V7*Assumptions!$B$17</f>
+        <v>429.233281323815</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <f aca="false">W7*Assumptions!$B$17</f>
+        <v>454.940948510576</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <f aca="false">X7*Assumptions!$B$17</f>
+        <v>480.391539025471</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <f aca="false">Y7*Assumptions!$B$17</f>
+        <v>505.587623635216</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>522</v>
+      </c>
+      <c r="AA16" s="6" t="n">
+        <f aca="false">SUM(N16:Y16)</f>
+        <v>4346.82526011362</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <f aca="false">B14+B15+B16</f>
         <v>46</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <f aca="false">C13+C14+C15</f>
+      <c r="C17" s="6" t="n">
+        <f aca="false">C14+C15+C16</f>
         <v>138</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <f aca="false">D13+D14+D15</f>
+      <c r="D17" s="6" t="n">
+        <f aca="false">D14+D15+D16</f>
         <v>230</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <f aca="false">E13+E14+E15</f>
+      <c r="E17" s="6" t="n">
+        <f aca="false">E14+E15+E16</f>
         <v>322</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <f aca="false">F13+F14+F15</f>
+      <c r="F17" s="6" t="n">
+        <f aca="false">F14+F15+F16</f>
         <v>414</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <f aca="false">G13+G14+G15</f>
+      <c r="G17" s="6" t="n">
+        <f aca="false">G14+G15+G16</f>
         <v>506</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <f aca="false">H13+H14+H15</f>
+      <c r="H17" s="6" t="n">
+        <f aca="false">H14+H15+H16</f>
         <v>828</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <f aca="false">I13+I14+I15</f>
+      <c r="I17" s="6" t="n">
+        <f aca="false">I14+I15+I16</f>
         <v>1518</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <f aca="false">J13+J14+J15</f>
+      <c r="J17" s="6" t="n">
+        <f aca="false">J14+J15+J16</f>
         <v>2530</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <f aca="false">K13+K14+K15</f>
+      <c r="K17" s="6" t="n">
+        <f aca="false">K14+K15+K16</f>
         <v>3910</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <f aca="false">L13+L14+L15</f>
+      <c r="L17" s="6" t="n">
+        <f aca="false">L14+L15+L16</f>
         <v>5658</v>
       </c>
-      <c r="M16" s="5" t="n">
-        <f aca="false">M13+M14+M15</f>
+      <c r="M17" s="6" t="n">
+        <f aca="false">M14+M15+M16</f>
         <v>7912</v>
       </c>
-      <c r="N16" s="5" t="n">
-        <f aca="false">SUM(B16:M16)</f>
+      <c r="N17" s="6" t="n">
+        <f aca="false">N14+N15+N16</f>
+        <v>9844</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <f aca="false">O14+O15+O16</f>
+        <v>11125.56</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <f aca="false">P14+P15+P16</f>
+        <v>12394.3044</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <f aca="false">Q14+Q15+Q16</f>
+        <v>13650.361356</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <f aca="false">R14+R15+R16</f>
+        <v>14893.85774244</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <f aca="false">S14+S15+S16</f>
+        <v>16124.9191650156</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <f aca="false">T14+T15+T16</f>
+        <v>17343.6699733654</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <f aca="false">U14+U15+U16</f>
+        <v>18550.2332736318</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <f aca="false">V14+V15+V16</f>
+        <v>19744.7309408955</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <f aca="false">W14+W15+W16</f>
+        <v>20927.2836314865</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <f aca="false">X14+X15+X16</f>
+        <v>22098.0107951717</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <f aca="false">Y14+Y15+Y16</f>
+        <v>23257.0306872199</v>
+      </c>
+      <c r="Z17" s="6" t="n">
+        <f aca="false">SUM(B17:M17)</f>
         <v>24012</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="6" t="n">
-        <f aca="false">B11-B16</f>
+      <c r="AA17" s="6" t="n">
+        <f aca="false">SUM(N17:Y17)</f>
+        <v>199953.961965226</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <f aca="false">B12-B17</f>
         <v>249</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <f aca="false">C11-C16</f>
+      <c r="C18" s="7" t="n">
+        <f aca="false">C12-C17</f>
         <v>747</v>
       </c>
-      <c r="D17" s="6" t="n">
-        <f aca="false">D11-D16</f>
+      <c r="D18" s="7" t="n">
+        <f aca="false">D12-D17</f>
         <v>1245</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <f aca="false">E11-E16</f>
+      <c r="E18" s="7" t="n">
+        <f aca="false">E12-E17</f>
         <v>1743</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <f aca="false">F11-F16</f>
+      <c r="F18" s="7" t="n">
+        <f aca="false">F12-F17</f>
         <v>2241</v>
       </c>
-      <c r="G17" s="6" t="n">
-        <f aca="false">G11-G16</f>
+      <c r="G18" s="7" t="n">
+        <f aca="false">G12-G17</f>
         <v>2739</v>
       </c>
-      <c r="H17" s="6" t="n">
-        <f aca="false">H11-H16</f>
+      <c r="H18" s="7" t="n">
+        <f aca="false">H12-H17</f>
         <v>4482</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <f aca="false">I11-I16</f>
+      <c r="I18" s="7" t="n">
+        <f aca="false">I12-I17</f>
         <v>8217</v>
       </c>
-      <c r="J17" s="6" t="n">
-        <f aca="false">J11-J16</f>
+      <c r="J18" s="7" t="n">
+        <f aca="false">J12-J17</f>
         <v>13695</v>
       </c>
-      <c r="K17" s="6" t="n">
-        <f aca="false">K11-K16</f>
+      <c r="K18" s="7" t="n">
+        <f aca="false">K12-K17</f>
         <v>21165</v>
       </c>
-      <c r="L17" s="6" t="n">
-        <f aca="false">L11-L16</f>
+      <c r="L18" s="7" t="n">
+        <f aca="false">L12-L17</f>
         <v>30627</v>
       </c>
-      <c r="M17" s="6" t="n">
-        <f aca="false">M11-M16</f>
+      <c r="M18" s="7" t="n">
+        <f aca="false">M12-M17</f>
         <v>42828</v>
       </c>
-      <c r="N17" s="6" t="n">
-        <f aca="false">SUM(B17:M17)</f>
+      <c r="N18" s="7" t="n">
+        <f aca="false">N12-N17</f>
+        <v>53286</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <f aca="false">O12-O17</f>
+        <v>60223.14</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <f aca="false">P12-P17</f>
+        <v>67090.9086</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <f aca="false">Q12-Q17</f>
+        <v>73889.999514</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <f aca="false">R12-R17</f>
+        <v>80621.09951886</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <f aca="false">S12-S17</f>
+        <v>87284.8885236714</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <f aca="false">T12-T17</f>
+        <v>93882.0396384347</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <f aca="false">U12-U17</f>
+        <v>100413.21924205</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <f aca="false">V12-V17</f>
+        <v>106879.08704963</v>
+      </c>
+      <c r="W18" s="7" t="n">
+        <f aca="false">W12-W17</f>
+        <v>113280.296179134</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <f aca="false">X12-X17</f>
+        <v>119617.493217342</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <f aca="false">Y12-Y17</f>
+        <v>125891.318285169</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <f aca="false">SUM(B18:M18)</f>
         <v>129978</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <f aca="false">B17/B11</f>
+      <c r="AA18" s="7" t="n">
+        <f aca="false">SUM(N18:Y18)</f>
+        <v>1082359.48976829</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <f aca="false">B18/B12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <f aca="false">C17/C11</f>
+      <c r="C19" s="8" t="n">
+        <f aca="false">C18/C12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <f aca="false">D17/D11</f>
+      <c r="D19" s="8" t="n">
+        <f aca="false">D18/D12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <f aca="false">E17/E11</f>
+      <c r="E19" s="8" t="n">
+        <f aca="false">E18/E12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <f aca="false">F17/F11</f>
+      <c r="F19" s="8" t="n">
+        <f aca="false">F18/F12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <f aca="false">G17/G11</f>
+      <c r="G19" s="8" t="n">
+        <f aca="false">G18/G12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="H18" s="7" t="n">
-        <f aca="false">H17/H11</f>
+      <c r="H19" s="8" t="n">
+        <f aca="false">H18/H12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="I18" s="7" t="n">
-        <f aca="false">I17/I11</f>
+      <c r="I19" s="8" t="n">
+        <f aca="false">I18/I12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="J18" s="7" t="n">
-        <f aca="false">J17/J11</f>
+      <c r="J19" s="8" t="n">
+        <f aca="false">J18/J12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="K18" s="7" t="n">
-        <f aca="false">K17/K11</f>
+      <c r="K19" s="8" t="n">
+        <f aca="false">K18/K12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="L18" s="7" t="n">
-        <f aca="false">L17/L11</f>
+      <c r="L19" s="8" t="n">
+        <f aca="false">L18/L12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="M18" s="7" t="n">
-        <f aca="false">M17/M11</f>
+      <c r="M19" s="8" t="n">
+        <f aca="false">M18/M12</f>
         <v>0.84406779661017</v>
       </c>
-      <c r="N18" s="7" t="n">
-        <f aca="false">N17/N11</f>
+      <c r="N19" s="8" t="n">
+        <f aca="false">N18/N12</f>
         <v>0.84406779661017</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
+      <c r="O19" s="8" t="n">
+        <f aca="false">O18/O12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <f aca="false">P18/P12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <f aca="false">Q18/Q12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <f aca="false">R18/R12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <f aca="false">S18/S12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <f aca="false">T18/T12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <f aca="false">U18/U12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <f aca="false">V18/V12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <f aca="false">W18/W12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <f aca="false">X18/X12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <f aca="false">Y18/Y12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <f aca="false">Z18/Z12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <f aca="false">AA18/AA12</f>
+        <v>0.844067796610169</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="5" t="n">
+      <c r="A20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="6" t="n">
         <f aca="false">B3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <f aca="false">C3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <f aca="false">D3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <f aca="false">E3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <f aca="false">F3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <f aca="false">G3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>900</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H21" s="6" t="n">
         <f aca="false">H3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>5400</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="6" t="n">
         <f aca="false">I3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>8100</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J21" s="6" t="n">
         <f aca="false">J3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>11700</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="K21" s="6" t="n">
         <f aca="false">K3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>15300</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L21" s="6" t="n">
         <f aca="false">L3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>18900</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="M21" s="6" t="n">
         <f aca="false">M3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>25200</v>
       </c>
-      <c r="N20" s="5" t="n">
-        <f aca="false">SUM(B20:M20)</f>
+      <c r="N21" s="6" t="n">
+        <f aca="false">N3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <f aca="false">O3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <f aca="false">P3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <f aca="false">Q3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <f aca="false">R3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <f aca="false">S3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <f aca="false">T3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <f aca="false">U3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <f aca="false">V3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <f aca="false">W3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <f aca="false">X3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <f aca="false">Y3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>13500</v>
+      </c>
+      <c r="Z21" s="6" t="n">
+        <f aca="false">SUM(B21:M21)</f>
         <v>90000</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <f aca="false">B6*Assumptions!$B$16</f>
-        <v>25</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <f aca="false">C6*Assumptions!$B$16</f>
-        <v>75</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <f aca="false">D6*Assumptions!$B$16</f>
-        <v>125</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <f aca="false">E6*Assumptions!$B$16</f>
-        <v>175</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <f aca="false">F6*Assumptions!$B$16</f>
-        <v>225</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <f aca="false">G6*Assumptions!$B$16</f>
-        <v>275</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <f aca="false">H6*Assumptions!$B$16</f>
-        <v>450</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <f aca="false">I6*Assumptions!$B$16</f>
-        <v>825</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <f aca="false">J6*Assumptions!$B$16</f>
-        <v>1375</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <f aca="false">K6*Assumptions!$B$16</f>
-        <v>2125</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <f aca="false">L6*Assumptions!$B$16</f>
-        <v>3075</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <f aca="false">M6*Assumptions!$B$16</f>
-        <v>4300</v>
-      </c>
-      <c r="N21" s="5" t="n">
-        <f aca="false">SUM(B21:M21)</f>
-        <v>13050</v>
+      <c r="AA21" s="6" t="n">
+        <f aca="false">SUM(N21:Y21)</f>
+        <v>162000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <f aca="false">B7*Assumptions!$B$16</f>
+        <v>25</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <f aca="false">C7*Assumptions!$B$16</f>
         <v>75</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="D22" s="6" t="n">
+        <f aca="false">D7*Assumptions!$B$16</f>
+        <v>125</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <f aca="false">E7*Assumptions!$B$16</f>
+        <v>175</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <f aca="false">F7*Assumptions!$B$16</f>
+        <v>225</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <f aca="false">G7*Assumptions!$B$16</f>
+        <v>275</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <f aca="false">H7*Assumptions!$B$16</f>
+        <v>450</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <f aca="false">I7*Assumptions!$B$16</f>
+        <v>825</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <f aca="false">J7*Assumptions!$B$16</f>
+        <v>1375</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <f aca="false">K7*Assumptions!$B$16</f>
+        <v>2125</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <f aca="false">L7*Assumptions!$B$16</f>
+        <v>3075</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <f aca="false">M7*Assumptions!$B$16</f>
+        <v>4300</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <f aca="false">N7*Assumptions!$B$16</f>
+        <v>5350</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <f aca="false">O7*Assumptions!$B$16</f>
+        <v>6046.5</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <f aca="false">P7*Assumptions!$B$16</f>
+        <v>6736.035</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <f aca="false">Q7*Assumptions!$B$16</f>
+        <v>7418.67465</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <f aca="false">R7*Assumptions!$B$16</f>
+        <v>8094.4879035</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <f aca="false">S7*Assumptions!$B$16</f>
+        <v>8763.543024465</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <f aca="false">T7*Assumptions!$B$16</f>
+        <v>9425.90759422035</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <f aca="false">U7*Assumptions!$B$16</f>
+        <v>10081.6485182781</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <f aca="false">V7*Assumptions!$B$16</f>
+        <v>10730.8320330954</v>
+      </c>
+      <c r="W22" s="6" t="n">
+        <f aca="false">W7*Assumptions!$B$16</f>
+        <v>11373.5237127644</v>
+      </c>
+      <c r="X22" s="6" t="n">
+        <f aca="false">X7*Assumptions!$B$16</f>
+        <v>12009.7884756368</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <f aca="false">Y7*Assumptions!$B$16</f>
+        <v>12639.6905908804</v>
+      </c>
+      <c r="Z22" s="6" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>13050</v>
+      </c>
+      <c r="AA22" s="6" t="n">
+        <f aca="false">SUM(N22:Y22)</f>
+        <v>108670.63150284</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="K23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="M23" s="6" t="n">
         <f aca="false">Assumptions!$B$21</f>
         <v>150</v>
       </c>
-      <c r="N22" s="5" t="n">
-        <f aca="false">SUM(B22:M22)</f>
+      <c r="N23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="Y23" s="6" t="n">
+        <f aca="false">Assumptions!$B$21</f>
+        <v>150</v>
+      </c>
+      <c r="Z23" s="6" t="n">
+        <f aca="false">SUM(B23:M23)</f>
         <v>1800</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="5" t="n">
+      <c r="AA23" s="6" t="n">
+        <f aca="false">SUM(N23:Y23)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="K24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="M24" s="6" t="n">
         <f aca="false">Assumptions!$B$22</f>
         <v>500</v>
       </c>
-      <c r="N23" s="5" t="n">
-        <f aca="false">SUM(B23:M23)</f>
+      <c r="N24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="X24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="Y24" s="6" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>500</v>
+      </c>
+      <c r="Z24" s="6" t="n">
+        <f aca="false">SUM(B24:M24)</f>
         <v>6000</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="5" t="n">
+      <c r="AA24" s="6" t="n">
+        <f aca="false">SUM(N24:Y24)</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="K25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="M25" s="6" t="n">
         <f aca="false">Assumptions!$B$23</f>
         <v>1200</v>
       </c>
-      <c r="N24" s="5" t="n">
-        <f aca="false">SUM(B24:M24)</f>
+      <c r="N25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="X25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="Y25" s="6" t="n">
+        <f aca="false">Assumptions!$B$23</f>
+        <v>1200</v>
+      </c>
+      <c r="Z25" s="6" t="n">
+        <f aca="false">SUM(B25:M25)</f>
         <v>14400</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="5" t="n">
+      <c r="AA25" s="6" t="n">
+        <f aca="false">SUM(N25:Y25)</f>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="K26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="M26" s="6" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>7500</v>
       </c>
-      <c r="N25" s="5" t="n">
-        <f aca="false">SUM(B25:M25)</f>
+      <c r="N26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="W26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="X26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="Y26" s="6" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>7500</v>
+      </c>
+      <c r="Z26" s="6" t="n">
+        <f aca="false">SUM(B26:M26)</f>
         <v>90000</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="6" t="n">
-        <f aca="false">SUM(B20:B25)</f>
-        <v>10275</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <f aca="false">SUM(C20:C25)</f>
-        <v>10325</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <f aca="false">SUM(D20:D25)</f>
-        <v>10375</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <f aca="false">SUM(E20:E25)</f>
-        <v>10425</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <f aca="false">SUM(F20:F25)</f>
-        <v>10475</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <f aca="false">SUM(G20:G25)</f>
-        <v>10525</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <f aca="false">SUM(H20:H25)</f>
-        <v>15200</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <f aca="false">SUM(I20:I25)</f>
-        <v>18275</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <f aca="false">SUM(J20:J25)</f>
-        <v>22425</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <f aca="false">SUM(K20:K25)</f>
-        <v>26775</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <f aca="false">SUM(L20:L25)</f>
-        <v>31325</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <f aca="false">SUM(M20:M25)</f>
-        <v>38850</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <f aca="false">SUM(B26:M26)</f>
-        <v>215250</v>
+      <c r="AA26" s="6" t="n">
+        <f aca="false">SUM(N26:Y26)</f>
+        <v>90000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="6" t="n">
-        <f aca="false">B17-B26</f>
+        <v>94</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <f aca="false">SUM(B21:B26)</f>
+        <v>10275</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <f aca="false">SUM(C21:C26)</f>
+        <v>10325</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <f aca="false">SUM(D21:D26)</f>
+        <v>10375</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <f aca="false">SUM(E21:E26)</f>
+        <v>10425</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <f aca="false">SUM(F21:F26)</f>
+        <v>10475</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <f aca="false">SUM(G21:G26)</f>
+        <v>10525</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <f aca="false">SUM(H21:H26)</f>
+        <v>15200</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <f aca="false">SUM(I21:I26)</f>
+        <v>18275</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <f aca="false">SUM(J21:J26)</f>
+        <v>22425</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <f aca="false">SUM(K21:K26)</f>
+        <v>26775</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <f aca="false">SUM(L21:L26)</f>
+        <v>31325</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <f aca="false">SUM(M21:M26)</f>
+        <v>38850</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <f aca="false">SUM(N21:N26)</f>
+        <v>28200</v>
+      </c>
+      <c r="O27" s="7" t="n">
+        <f aca="false">SUM(O21:O26)</f>
+        <v>28896.5</v>
+      </c>
+      <c r="P27" s="7" t="n">
+        <f aca="false">SUM(P21:P26)</f>
+        <v>29586.035</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <f aca="false">SUM(Q21:Q26)</f>
+        <v>30268.67465</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <f aca="false">SUM(R21:R26)</f>
+        <v>30944.4879035</v>
+      </c>
+      <c r="S27" s="7" t="n">
+        <f aca="false">SUM(S21:S26)</f>
+        <v>31613.543024465</v>
+      </c>
+      <c r="T27" s="7" t="n">
+        <f aca="false">SUM(T21:T26)</f>
+        <v>32275.9075942204</v>
+      </c>
+      <c r="U27" s="7" t="n">
+        <f aca="false">SUM(U21:U26)</f>
+        <v>32931.6485182782</v>
+      </c>
+      <c r="V27" s="7" t="n">
+        <f aca="false">SUM(V21:V26)</f>
+        <v>33580.8320330954</v>
+      </c>
+      <c r="W27" s="7" t="n">
+        <f aca="false">SUM(W21:W26)</f>
+        <v>34223.5237127644</v>
+      </c>
+      <c r="X27" s="7" t="n">
+        <f aca="false">SUM(X21:X26)</f>
+        <v>34859.7884756368</v>
+      </c>
+      <c r="Y27" s="7" t="n">
+        <f aca="false">SUM(Y21:Y26)</f>
+        <v>35489.6905908804</v>
+      </c>
+      <c r="Z27" s="7" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>215250</v>
+      </c>
+      <c r="AA27" s="7" t="n">
+        <f aca="false">SUM(N27:Y27)</f>
+        <v>382870.63150284</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <f aca="false">B18-B27</f>
         <v>-10026</v>
       </c>
-      <c r="C27" s="6" t="n">
-        <f aca="false">C17-C26</f>
+      <c r="C28" s="7" t="n">
+        <f aca="false">C18-C27</f>
         <v>-9578</v>
       </c>
-      <c r="D27" s="6" t="n">
-        <f aca="false">D17-D26</f>
+      <c r="D28" s="7" t="n">
+        <f aca="false">D18-D27</f>
         <v>-9130</v>
       </c>
-      <c r="E27" s="6" t="n">
-        <f aca="false">E17-E26</f>
+      <c r="E28" s="7" t="n">
+        <f aca="false">E18-E27</f>
         <v>-8682</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <f aca="false">F17-F26</f>
+      <c r="F28" s="7" t="n">
+        <f aca="false">F18-F27</f>
         <v>-8234</v>
       </c>
-      <c r="G27" s="6" t="n">
-        <f aca="false">G17-G26</f>
+      <c r="G28" s="7" t="n">
+        <f aca="false">G18-G27</f>
         <v>-7786</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false">H17-H26</f>
+      <c r="H28" s="7" t="n">
+        <f aca="false">H18-H27</f>
         <v>-10718</v>
       </c>
-      <c r="I27" s="6" t="n">
-        <f aca="false">I17-I26</f>
+      <c r="I28" s="7" t="n">
+        <f aca="false">I18-I27</f>
         <v>-10058</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <f aca="false">J17-J26</f>
+      <c r="J28" s="7" t="n">
+        <f aca="false">J18-J27</f>
         <v>-8730</v>
       </c>
-      <c r="K27" s="6" t="n">
-        <f aca="false">K17-K26</f>
+      <c r="K28" s="7" t="n">
+        <f aca="false">K18-K27</f>
         <v>-5610</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <f aca="false">L17-L26</f>
+      <c r="L28" s="7" t="n">
+        <f aca="false">L18-L27</f>
         <v>-698</v>
       </c>
-      <c r="M27" s="6" t="n">
-        <f aca="false">M17-M26</f>
+      <c r="M28" s="7" t="n">
+        <f aca="false">M18-M27</f>
         <v>3978</v>
       </c>
-      <c r="N27" s="6" t="n">
-        <f aca="false">SUM(B27:M27)</f>
+      <c r="N28" s="7" t="n">
+        <f aca="false">N18-N27</f>
+        <v>25086</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <f aca="false">O18-O27</f>
+        <v>31326.64</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <f aca="false">P18-P27</f>
+        <v>37504.8736</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <f aca="false">Q18-Q27</f>
+        <v>43621.324864</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <f aca="false">R18-R27</f>
+        <v>49676.61161536</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <f aca="false">S18-S27</f>
+        <v>55671.3454992064</v>
+      </c>
+      <c r="T28" s="7" t="n">
+        <f aca="false">T18-T27</f>
+        <v>61606.1320442143</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <f aca="false">U18-U27</f>
+        <v>67481.5707237722</v>
+      </c>
+      <c r="V28" s="7" t="n">
+        <f aca="false">V18-V27</f>
+        <v>73298.2550165345</v>
+      </c>
+      <c r="W28" s="7" t="n">
+        <f aca="false">W18-W27</f>
+        <v>79056.7724663691</v>
+      </c>
+      <c r="X28" s="7" t="n">
+        <f aca="false">X18-X27</f>
+        <v>84757.7047417054</v>
+      </c>
+      <c r="Y28" s="7" t="n">
+        <f aca="false">Y18-Y27</f>
+        <v>90401.6276942884</v>
+      </c>
+      <c r="Z28" s="7" t="n">
+        <f aca="false">SUM(B28:M28)</f>
         <v>-85272</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:B27))-0)</f>
+      <c r="AA28" s="7" t="n">
+        <f aca="false">SUM(N28:Y28)</f>
+        <v>699488.85826545</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:B28))-0)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:C27))-SUM($B28:B28))</f>
+      <c r="C29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:C28))-SUM($B29:B29))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:D27))-SUM($B28:C28))</f>
+      <c r="D29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:D28))-SUM($B29:C29))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:E27))-SUM($B28:D28))</f>
+      <c r="E29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:E28))-SUM($B29:D29))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:F27))-SUM($B28:E28))</f>
+      <c r="F29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:F28))-SUM($B29:E29))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:G27))-SUM($B28:F28))</f>
+      <c r="G29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:G28))-SUM($B29:F29))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:H27))-SUM($B28:G28))</f>
+      <c r="H29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:H28))-SUM($B29:G29))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:I27))-SUM($B28:H28))</f>
+      <c r="I29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:I28))-SUM($B29:H29))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:J27))-SUM($B28:I28))</f>
+      <c r="J29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:J28))-SUM($B29:I29))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:K27))-SUM($B28:J28))</f>
+      <c r="K29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:K28))-SUM($B29:J29))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:L27))-SUM($B28:K28))</f>
+      <c r="L29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:L28))-SUM($B29:K29))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="5" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B27:M27))-SUM($B28:L28))</f>
+      <c r="M29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:M28))-SUM($B29:L29))</f>
         <v>0</v>
       </c>
-      <c r="N28" s="5" t="n">
-        <f aca="false">SUM(B28:M28)</f>
+      <c r="N29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:N28))-SUM($B29:M29))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="6" t="n">
-        <f aca="false">B27-B28</f>
+      <c r="O29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:O28))-SUM($B29:N29))</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:P28))-SUM($B29:O29))</f>
+        <v>2161.3784</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:Q28))-SUM($B29:P29))</f>
+        <v>10905.331216</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:R28))-SUM($B29:Q29))</f>
+        <v>12419.15290384</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:S28))-SUM($B29:R29))</f>
+        <v>13917.8363748016</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:T28))-SUM($B29:S29))</f>
+        <v>15401.5330110536</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:U28))-SUM($B29:T29))</f>
+        <v>16870.392680943</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:V28))-SUM($B29:U29))</f>
+        <v>18324.5637541336</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:W28))-SUM($B29:V29))</f>
+        <v>19764.1931165923</v>
+      </c>
+      <c r="X29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:X28))-SUM($B29:W29))</f>
+        <v>21189.4261854264</v>
+      </c>
+      <c r="Y29" s="6" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:Y28))-SUM($B29:X29))</f>
+        <v>22600.4069235721</v>
+      </c>
+      <c r="Z29" s="6" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="6" t="n">
+        <f aca="false">SUM(N29:Y29)</f>
+        <v>153554.214566363</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <f aca="false">B28-B29</f>
         <v>-10026</v>
       </c>
-      <c r="C29" s="6" t="n">
-        <f aca="false">C27-C28</f>
+      <c r="C30" s="7" t="n">
+        <f aca="false">C28-C29</f>
         <v>-9578</v>
       </c>
-      <c r="D29" s="6" t="n">
-        <f aca="false">D27-D28</f>
+      <c r="D30" s="7" t="n">
+        <f aca="false">D28-D29</f>
         <v>-9130</v>
       </c>
-      <c r="E29" s="6" t="n">
-        <f aca="false">E27-E28</f>
+      <c r="E30" s="7" t="n">
+        <f aca="false">E28-E29</f>
         <v>-8682</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <f aca="false">F27-F28</f>
+      <c r="F30" s="7" t="n">
+        <f aca="false">F28-F29</f>
         <v>-8234</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <f aca="false">G27-G28</f>
+      <c r="G30" s="7" t="n">
+        <f aca="false">G28-G29</f>
         <v>-7786</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <f aca="false">H27-H28</f>
+      <c r="H30" s="7" t="n">
+        <f aca="false">H28-H29</f>
         <v>-10718</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <f aca="false">I27-I28</f>
+      <c r="I30" s="7" t="n">
+        <f aca="false">I28-I29</f>
         <v>-10058</v>
       </c>
-      <c r="J29" s="6" t="n">
-        <f aca="false">J27-J28</f>
+      <c r="J30" s="7" t="n">
+        <f aca="false">J28-J29</f>
         <v>-8730</v>
       </c>
-      <c r="K29" s="6" t="n">
-        <f aca="false">K27-K28</f>
+      <c r="K30" s="7" t="n">
+        <f aca="false">K28-K29</f>
         <v>-5610</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <f aca="false">L27-L28</f>
+      <c r="L30" s="7" t="n">
+        <f aca="false">L28-L29</f>
         <v>-698</v>
       </c>
-      <c r="M29" s="6" t="n">
-        <f aca="false">M27-M28</f>
+      <c r="M30" s="7" t="n">
+        <f aca="false">M28-M29</f>
         <v>3978</v>
       </c>
-      <c r="N29" s="6" t="n">
-        <f aca="false">SUM(B29:M29)</f>
+      <c r="N30" s="7" t="n">
+        <f aca="false">N28-N29</f>
+        <v>25086</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <f aca="false">O28-O29</f>
+        <v>31326.64</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <f aca="false">P28-P29</f>
+        <v>35343.4952</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <f aca="false">Q28-Q29</f>
+        <v>32715.993648</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <f aca="false">R28-R29</f>
+        <v>37257.45871152</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <f aca="false">S28-S29</f>
+        <v>41753.5091244048</v>
+      </c>
+      <c r="T30" s="7" t="n">
+        <f aca="false">T28-T29</f>
+        <v>46204.5990331607</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <f aca="false">U28-U29</f>
+        <v>50611.1780428292</v>
+      </c>
+      <c r="V30" s="7" t="n">
+        <f aca="false">V28-V29</f>
+        <v>54973.6912624009</v>
+      </c>
+      <c r="W30" s="7" t="n">
+        <f aca="false">W28-W29</f>
+        <v>59292.5793497768</v>
+      </c>
+      <c r="X30" s="7" t="n">
+        <f aca="false">X28-X29</f>
+        <v>63568.2785562791</v>
+      </c>
+      <c r="Y30" s="7" t="n">
+        <f aca="false">Y28-Y29</f>
+        <v>67801.2207707163</v>
+      </c>
+      <c r="Z30" s="7" t="n">
+        <f aca="false">SUM(B30:M30)</f>
         <v>-85272</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <f aca="false">SUM($B29:B29)</f>
+      <c r="AA30" s="7" t="n">
+        <f aca="false">SUM(N30:Y30)</f>
+        <v>545934.643699088</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <f aca="false">SUM($B30:B30)</f>
         <v>-10026</v>
       </c>
-      <c r="C30" s="5" t="n">
-        <f aca="false">SUM($B29:C29)</f>
+      <c r="C31" s="6" t="n">
+        <f aca="false">SUM($B30:C30)</f>
         <v>-19604</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <f aca="false">SUM($B29:D29)</f>
+      <c r="D31" s="6" t="n">
+        <f aca="false">SUM($B30:D30)</f>
         <v>-28734</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <f aca="false">SUM($B29:E29)</f>
+      <c r="E31" s="6" t="n">
+        <f aca="false">SUM($B30:E30)</f>
         <v>-37416</v>
       </c>
-      <c r="F30" s="5" t="n">
-        <f aca="false">SUM($B29:F29)</f>
+      <c r="F31" s="6" t="n">
+        <f aca="false">SUM($B30:F30)</f>
         <v>-45650</v>
       </c>
-      <c r="G30" s="5" t="n">
-        <f aca="false">SUM($B29:G29)</f>
+      <c r="G31" s="6" t="n">
+        <f aca="false">SUM($B30:G30)</f>
         <v>-53436</v>
       </c>
-      <c r="H30" s="5" t="n">
-        <f aca="false">SUM($B29:H29)</f>
+      <c r="H31" s="6" t="n">
+        <f aca="false">SUM($B30:H30)</f>
         <v>-64154</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <f aca="false">SUM($B29:I29)</f>
+      <c r="I31" s="6" t="n">
+        <f aca="false">SUM($B30:I30)</f>
         <v>-74212</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <f aca="false">SUM($B29:J29)</f>
+      <c r="J31" s="6" t="n">
+        <f aca="false">SUM($B30:J30)</f>
         <v>-82942</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <f aca="false">SUM($B29:K29)</f>
+      <c r="K31" s="6" t="n">
+        <f aca="false">SUM($B30:K30)</f>
         <v>-88552</v>
       </c>
-      <c r="L30" s="5" t="n">
-        <f aca="false">SUM($B29:L29)</f>
+      <c r="L31" s="6" t="n">
+        <f aca="false">SUM($B30:L30)</f>
         <v>-89250</v>
       </c>
-      <c r="M30" s="5" t="n">
-        <f aca="false">SUM($B29:M29)</f>
+      <c r="M31" s="6" t="n">
+        <f aca="false">SUM($B30:M30)</f>
         <v>-85272</v>
       </c>
-      <c r="N30" s="5" t="n">
-        <f aca="false">M30</f>
+      <c r="N31" s="6" t="n">
+        <f aca="false">SUM($B30:N30)</f>
+        <v>-60186</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <f aca="false">SUM($B30:O30)</f>
+        <v>-28859.36</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <f aca="false">SUM($B30:P30)</f>
+        <v>6484.1352</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <f aca="false">SUM($B30:Q30)</f>
+        <v>39200.128848</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <f aca="false">SUM($B30:R30)</f>
+        <v>76457.58755952</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <f aca="false">SUM($B30:S30)</f>
+        <v>118211.096683925</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <f aca="false">SUM($B30:T30)</f>
+        <v>164415.695717086</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <f aca="false">SUM($B30:U30)</f>
+        <v>215026.873759915</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <f aca="false">SUM($B30:V30)</f>
+        <v>270000.565022316</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <f aca="false">SUM($B30:W30)</f>
+        <v>329293.144372092</v>
+      </c>
+      <c r="X31" s="6" t="n">
+        <f aca="false">SUM($B30:X30)</f>
+        <v>392861.422928371</v>
+      </c>
+      <c r="Y31" s="6" t="n">
+        <f aca="false">SUM($B30:Y30)</f>
+        <v>460662.643699088</v>
+      </c>
+      <c r="Z31" s="6" t="n">
+        <f aca="false">M31</f>
         <v>-85272</v>
+      </c>
+      <c r="AA31" s="6" t="n">
+        <f aca="false">Y31</f>
+        <v>460662.643699088</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OnSite-forecast-PnL.xlsx
+++ b/docs/OnSite-forecast-PnL.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
   <si>
     <t xml:space="preserve">OnSite - forecast assumptions (blue = editable inputs). All amounts AUD, excluding GST.</t>
   </si>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">A$3/month each (docs/TWILIO.md)</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMED ~0.5 hr/park/month</t>
+    <t xml:space="preserve">Support tools &amp; helpdesk software (per park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMED; support labour is now the hires below</t>
   </si>
   <si>
     <t xml:space="preserve">Hosting variable (per park)</t>
@@ -107,16 +107,28 @@
     <t xml:space="preserve">ONE-OFF / FIXED</t>
   </si>
   <si>
-    <t xml:space="preserve">Sales &amp; onboarding cost per new park (CAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMED demos, events, outreach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onboarding/setup cost per new park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMED NewBook link, number setup</t>
+    <t xml:space="preserve">Sales cost per new park (non-labour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMED travel, events, demo costs; founder does the selling (in salary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onboarding cost per new park (non-labour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMED test calls/SMS; labour is the tech support hire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical support hire: monthly cost (fully loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMED ~A$80k salary + super and on-costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First hire starts in month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second hire when parks at start of month reach</t>
   </si>
   <si>
     <t xml:space="preserve">Hosting base (always-on container, DB, logs)</t>
@@ -290,7 +302,16 @@
     <t xml:space="preserve">OPERATING EXPENSES</t>
   </si>
   <si>
-    <t xml:space="preserve">Sales &amp; onboarding</t>
+    <t xml:space="preserve">Sales &amp; onboarding (non-labour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support tools &amp; helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical support staff (count)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical support salaries</t>
   </si>
   <si>
     <t xml:space="preserve">Hosting base</t>
@@ -704,7 +725,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -846,7 +867,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>25</v>
@@ -873,7 +894,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>29</v>
@@ -884,7 +905,7 @@
         <v>30</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>31</v>
@@ -895,18 +916,18 @@
         <v>32</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>150</v>
+        <v>9000</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>20</v>
@@ -914,10 +935,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>20</v>
@@ -925,13 +946,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>7500</v>
+        <v>150</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -939,254 +960,287 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.25</v>
+        <v>500</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>38</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="0" t="n">
         <f aca="false">$B$6*$B$7</f>
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="0" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C33" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D33" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F33" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G33" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H33" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I30" s="0" t="n">
+      <c r="I33" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J30" s="0" t="n">
+      <c r="J33" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="K33" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L33" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M33" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N33" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="O30" s="0" t="n">
+      <c r="O33" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P33" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="Q30" s="0" t="n">
+      <c r="Q33" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="R30" s="0" t="n">
+      <c r="R33" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="S30" s="0" t="n">
+      <c r="S33" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="T30" s="0" t="n">
+      <c r="T33" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="U30" s="0" t="n">
+      <c r="U33" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="V30" s="0" t="n">
+      <c r="V33" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="W30" s="0" t="n">
+      <c r="W33" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="X30" s="0" t="n">
+      <c r="X33" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="Y30" s="0" t="n">
+      <c r="Y33" s="0" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="L34" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="M31" s="3" t="n">
+      <c r="M34" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="T31" s="3" t="n">
+      <c r="T34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="X31" s="3" t="n">
+      <c r="X34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="Y31" s="3" t="n">
+      <c r="Y34" s="3" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P32" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q32" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="R32" s="5" t="n">
+      <c r="R35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="S32" s="5" t="n">
+      <c r="S35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="T32" s="5" t="n">
+      <c r="T35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="U32" s="5" t="n">
+      <c r="U35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="V32" s="5" t="n">
+      <c r="V35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="W32" s="5" t="n">
+      <c r="W35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="X32" s="5" t="n">
+      <c r="X35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="Y32" s="5" t="n">
+      <c r="Y35" s="5" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -1206,7 +1260,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1215,190 +1269,190 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">Assumptions!B31</f>
+        <f aca="false">Assumptions!B34</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">Assumptions!C31</f>
+        <f aca="false">Assumptions!C34</f>
         <v>2</v>
       </c>
       <c r="D3" s="6" t="n">
-        <f aca="false">Assumptions!D31</f>
+        <f aca="false">Assumptions!D34</f>
         <v>2</v>
       </c>
       <c r="E3" s="6" t="n">
-        <f aca="false">Assumptions!E31</f>
+        <f aca="false">Assumptions!E34</f>
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">Assumptions!F31</f>
+        <f aca="false">Assumptions!F34</f>
         <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
-        <f aca="false">Assumptions!G31</f>
+        <f aca="false">Assumptions!G34</f>
         <v>2</v>
       </c>
       <c r="H3" s="6" t="n">
-        <f aca="false">Assumptions!H31</f>
+        <f aca="false">Assumptions!H34</f>
         <v>12</v>
       </c>
       <c r="I3" s="6" t="n">
-        <f aca="false">Assumptions!I31</f>
+        <f aca="false">Assumptions!I34</f>
         <v>18</v>
       </c>
       <c r="J3" s="6" t="n">
-        <f aca="false">Assumptions!J31</f>
+        <f aca="false">Assumptions!J34</f>
         <v>26</v>
       </c>
       <c r="K3" s="6" t="n">
-        <f aca="false">Assumptions!K31</f>
+        <f aca="false">Assumptions!K34</f>
         <v>34</v>
       </c>
       <c r="L3" s="6" t="n">
-        <f aca="false">Assumptions!L31</f>
+        <f aca="false">Assumptions!L34</f>
         <v>42</v>
       </c>
       <c r="M3" s="6" t="n">
-        <f aca="false">Assumptions!M31</f>
+        <f aca="false">Assumptions!M34</f>
         <v>56</v>
       </c>
       <c r="N3" s="6" t="n">
-        <f aca="false">Assumptions!N31</f>
+        <f aca="false">Assumptions!N34</f>
         <v>30</v>
       </c>
       <c r="O3" s="6" t="n">
-        <f aca="false">Assumptions!O31</f>
+        <f aca="false">Assumptions!O34</f>
         <v>30</v>
       </c>
       <c r="P3" s="6" t="n">
-        <f aca="false">Assumptions!P31</f>
+        <f aca="false">Assumptions!P34</f>
         <v>30</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <f aca="false">Assumptions!Q31</f>
+        <f aca="false">Assumptions!Q34</f>
         <v>30</v>
       </c>
       <c r="R3" s="6" t="n">
-        <f aca="false">Assumptions!R31</f>
+        <f aca="false">Assumptions!R34</f>
         <v>30</v>
       </c>
       <c r="S3" s="6" t="n">
-        <f aca="false">Assumptions!S31</f>
+        <f aca="false">Assumptions!S34</f>
         <v>30</v>
       </c>
       <c r="T3" s="6" t="n">
-        <f aca="false">Assumptions!T31</f>
+        <f aca="false">Assumptions!T34</f>
         <v>30</v>
       </c>
       <c r="U3" s="6" t="n">
-        <f aca="false">Assumptions!U31</f>
+        <f aca="false">Assumptions!U34</f>
         <v>30</v>
       </c>
       <c r="V3" s="6" t="n">
-        <f aca="false">Assumptions!V31</f>
+        <f aca="false">Assumptions!V34</f>
         <v>30</v>
       </c>
       <c r="W3" s="6" t="n">
-        <f aca="false">Assumptions!W31</f>
+        <f aca="false">Assumptions!W34</f>
         <v>30</v>
       </c>
       <c r="X3" s="6" t="n">
-        <f aca="false">Assumptions!X31</f>
+        <f aca="false">Assumptions!X34</f>
         <v>30</v>
       </c>
       <c r="Y3" s="6" t="n">
-        <f aca="false">Assumptions!Y31</f>
+        <f aca="false">Assumptions!Y34</f>
         <v>30</v>
       </c>
       <c r="Z3" s="6" t="n">
@@ -1412,102 +1466,102 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">B5*Assumptions!B32</f>
+        <f aca="false">B5*Assumptions!B35</f>
         <v>0</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">C5*Assumptions!C32</f>
+        <f aca="false">C5*Assumptions!C35</f>
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <f aca="false">D5*Assumptions!D32</f>
+        <f aca="false">D5*Assumptions!D35</f>
         <v>0</v>
       </c>
       <c r="E4" s="6" t="n">
-        <f aca="false">E5*Assumptions!E32</f>
+        <f aca="false">E5*Assumptions!E35</f>
         <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">F5*Assumptions!F32</f>
+        <f aca="false">F5*Assumptions!F35</f>
         <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
-        <f aca="false">G5*Assumptions!G32</f>
+        <f aca="false">G5*Assumptions!G35</f>
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <f aca="false">H5*Assumptions!H32</f>
+        <f aca="false">H5*Assumptions!H35</f>
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <f aca="false">I5*Assumptions!I32</f>
+        <f aca="false">I5*Assumptions!I35</f>
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <f aca="false">J5*Assumptions!J32</f>
+        <f aca="false">J5*Assumptions!J35</f>
         <v>0</v>
       </c>
       <c r="K4" s="6" t="n">
-        <f aca="false">K5*Assumptions!K32</f>
+        <f aca="false">K5*Assumptions!K35</f>
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <f aca="false">L5*Assumptions!L32</f>
+        <f aca="false">L5*Assumptions!L35</f>
         <v>0</v>
       </c>
       <c r="M4" s="6" t="n">
-        <f aca="false">M5*Assumptions!M32</f>
+        <f aca="false">M5*Assumptions!M35</f>
         <v>0</v>
       </c>
       <c r="N4" s="6" t="n">
-        <f aca="false">N5*Assumptions!N32</f>
+        <f aca="false">N5*Assumptions!N35</f>
         <v>2</v>
       </c>
       <c r="O4" s="6" t="n">
-        <f aca="false">O5*Assumptions!O32</f>
+        <f aca="false">O5*Assumptions!O35</f>
         <v>2.28</v>
       </c>
       <c r="P4" s="6" t="n">
-        <f aca="false">P5*Assumptions!P32</f>
+        <f aca="false">P5*Assumptions!P35</f>
         <v>2.5572</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <f aca="false">Q5*Assumptions!Q32</f>
+        <f aca="false">Q5*Assumptions!Q35</f>
         <v>2.831628</v>
       </c>
       <c r="R4" s="6" t="n">
-        <f aca="false">R5*Assumptions!R32</f>
+        <f aca="false">R5*Assumptions!R35</f>
         <v>3.10331172</v>
       </c>
       <c r="S4" s="6" t="n">
-        <f aca="false">S5*Assumptions!S32</f>
+        <f aca="false">S5*Assumptions!S35</f>
         <v>3.3722786028</v>
       </c>
       <c r="T4" s="6" t="n">
-        <f aca="false">T5*Assumptions!T32</f>
+        <f aca="false">T5*Assumptions!T35</f>
         <v>3.638555816772</v>
       </c>
       <c r="U4" s="6" t="n">
-        <f aca="false">U5*Assumptions!U32</f>
+        <f aca="false">U5*Assumptions!U35</f>
         <v>3.90217025860428</v>
       </c>
       <c r="V4" s="6" t="n">
-        <f aca="false">V5*Assumptions!V32</f>
+        <f aca="false">V5*Assumptions!V35</f>
         <v>4.16314855601824</v>
       </c>
       <c r="W4" s="6" t="n">
-        <f aca="false">W5*Assumptions!W32</f>
+        <f aca="false">W5*Assumptions!W35</f>
         <v>4.42151707045805</v>
       </c>
       <c r="X4" s="6" t="n">
-        <f aca="false">X5*Assumptions!X32</f>
+        <f aca="false">X5*Assumptions!X35</f>
         <v>4.67730189975347</v>
       </c>
       <c r="Y4" s="6" t="n">
-        <f aca="false">Y5*Assumptions!Y32</f>
+        <f aca="false">Y5*Assumptions!Y35</f>
         <v>4.93052888075594</v>
       </c>
       <c r="Z4" s="6" t="n">
@@ -1521,7 +1575,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -1629,7 +1683,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">B5+B3-B4</f>
@@ -1738,7 +1792,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">(B5+B6)/2</f>
@@ -1841,102 +1895,102 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">B7*Assumptions!$B$27</f>
+        <f aca="false">B7*Assumptions!$B$30</f>
         <v>65</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">C7*Assumptions!$B$27</f>
+        <f aca="false">C7*Assumptions!$B$30</f>
         <v>195</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">D7*Assumptions!$B$27</f>
+        <f aca="false">D7*Assumptions!$B$30</f>
         <v>325</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">E7*Assumptions!$B$27</f>
+        <f aca="false">E7*Assumptions!$B$30</f>
         <v>455</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">F7*Assumptions!$B$27</f>
+        <f aca="false">F7*Assumptions!$B$30</f>
         <v>585</v>
       </c>
       <c r="G8" s="6" t="n">
-        <f aca="false">G7*Assumptions!$B$27</f>
+        <f aca="false">G7*Assumptions!$B$30</f>
         <v>715</v>
       </c>
       <c r="H8" s="6" t="n">
-        <f aca="false">H7*Assumptions!$B$27</f>
+        <f aca="false">H7*Assumptions!$B$30</f>
         <v>1170</v>
       </c>
       <c r="I8" s="6" t="n">
-        <f aca="false">I7*Assumptions!$B$27</f>
+        <f aca="false">I7*Assumptions!$B$30</f>
         <v>2145</v>
       </c>
       <c r="J8" s="6" t="n">
-        <f aca="false">J7*Assumptions!$B$27</f>
+        <f aca="false">J7*Assumptions!$B$30</f>
         <v>3575</v>
       </c>
       <c r="K8" s="6" t="n">
-        <f aca="false">K7*Assumptions!$B$27</f>
+        <f aca="false">K7*Assumptions!$B$30</f>
         <v>5525</v>
       </c>
       <c r="L8" s="6" t="n">
-        <f aca="false">L7*Assumptions!$B$27</f>
+        <f aca="false">L7*Assumptions!$B$30</f>
         <v>7995</v>
       </c>
       <c r="M8" s="6" t="n">
-        <f aca="false">M7*Assumptions!$B$27</f>
+        <f aca="false">M7*Assumptions!$B$30</f>
         <v>11180</v>
       </c>
       <c r="N8" s="6" t="n">
-        <f aca="false">N7*Assumptions!$B$27</f>
+        <f aca="false">N7*Assumptions!$B$30</f>
         <v>13910</v>
       </c>
       <c r="O8" s="6" t="n">
-        <f aca="false">O7*Assumptions!$B$27</f>
+        <f aca="false">O7*Assumptions!$B$30</f>
         <v>15720.9</v>
       </c>
       <c r="P8" s="6" t="n">
-        <f aca="false">P7*Assumptions!$B$27</f>
+        <f aca="false">P7*Assumptions!$B$30</f>
         <v>17513.691</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <f aca="false">Q7*Assumptions!$B$27</f>
+        <f aca="false">Q7*Assumptions!$B$30</f>
         <v>19288.55409</v>
       </c>
       <c r="R8" s="6" t="n">
-        <f aca="false">R7*Assumptions!$B$27</f>
+        <f aca="false">R7*Assumptions!$B$30</f>
         <v>21045.6685491</v>
       </c>
       <c r="S8" s="6" t="n">
-        <f aca="false">S7*Assumptions!$B$27</f>
+        <f aca="false">S7*Assumptions!$B$30</f>
         <v>22785.211863609</v>
       </c>
       <c r="T8" s="6" t="n">
-        <f aca="false">T7*Assumptions!$B$27</f>
+        <f aca="false">T7*Assumptions!$B$30</f>
         <v>24507.3597449729</v>
       </c>
       <c r="U8" s="6" t="n">
-        <f aca="false">U7*Assumptions!$B$27</f>
+        <f aca="false">U7*Assumptions!$B$30</f>
         <v>26212.2861475232</v>
       </c>
       <c r="V8" s="6" t="n">
-        <f aca="false">V7*Assumptions!$B$27</f>
+        <f aca="false">V7*Assumptions!$B$30</f>
         <v>27900.1632860479</v>
       </c>
       <c r="W8" s="6" t="n">
-        <f aca="false">W7*Assumptions!$B$27</f>
+        <f aca="false">W7*Assumptions!$B$30</f>
         <v>29571.1616531875</v>
       </c>
       <c r="X8" s="6" t="n">
-        <f aca="false">X7*Assumptions!$B$27</f>
+        <f aca="false">X7*Assumptions!$B$30</f>
         <v>31225.4500366556</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <f aca="false">Y7*Assumptions!$B$27</f>
+        <f aca="false">Y7*Assumptions!$B$30</f>
         <v>32863.195536289</v>
       </c>
       <c r="Z8" s="6" t="n">
@@ -1950,7 +2004,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1981,7 +2035,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">B7*Assumptions!$B$4</f>
@@ -2090,7 +2144,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
@@ -2199,7 +2253,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">B10+B11</f>
@@ -2308,7 +2362,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -2339,7 +2393,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">B8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
@@ -2448,7 +2502,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" s="6" t="n">
         <f aca="false">B7*Assumptions!$B$15</f>
@@ -2557,7 +2611,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B16" s="6" t="n">
         <f aca="false">B7*Assumptions!$B$17</f>
@@ -2666,7 +2720,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B17" s="6" t="n">
         <f aca="false">B14+B15+B16</f>
@@ -2775,7 +2829,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B18" s="7" t="n">
         <f aca="false">B12-B17</f>
@@ -2884,7 +2938,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">B18/B12</f>
@@ -2993,7 +3047,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3024,1201 +3078,1419 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="C21" s="6" t="n">
         <f aca="false">C3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="D21" s="6" t="n">
         <f aca="false">D3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="E21" s="6" t="n">
         <f aca="false">E3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="F21" s="6" t="n">
         <f aca="false">F3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="G21" s="6" t="n">
         <f aca="false">G3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="H21" s="6" t="n">
         <f aca="false">H3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>5400</v>
+        <v>2400</v>
       </c>
       <c r="I21" s="6" t="n">
         <f aca="false">I3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>8100</v>
+        <v>3600</v>
       </c>
       <c r="J21" s="6" t="n">
         <f aca="false">J3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>11700</v>
+        <v>5200</v>
       </c>
       <c r="K21" s="6" t="n">
         <f aca="false">K3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>15300</v>
+        <v>6800</v>
       </c>
       <c r="L21" s="6" t="n">
         <f aca="false">L3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>18900</v>
+        <v>8400</v>
       </c>
       <c r="M21" s="6" t="n">
         <f aca="false">M3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>25200</v>
+        <v>11200</v>
       </c>
       <c r="N21" s="6" t="n">
         <f aca="false">N3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="O21" s="6" t="n">
         <f aca="false">O3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="P21" s="6" t="n">
         <f aca="false">P3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="Q21" s="6" t="n">
         <f aca="false">Q3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="R21" s="6" t="n">
         <f aca="false">R3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="S21" s="6" t="n">
         <f aca="false">S3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="T21" s="6" t="n">
         <f aca="false">T3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="U21" s="6" t="n">
         <f aca="false">U3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="V21" s="6" t="n">
         <f aca="false">V3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="W21" s="6" t="n">
         <f aca="false">W3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="X21" s="6" t="n">
         <f aca="false">X3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="Y21" s="6" t="n">
         <f aca="false">Y3*(Assumptions!$B$19+Assumptions!$B$20)</f>
-        <v>13500</v>
+        <v>6000</v>
       </c>
       <c r="Z21" s="6" t="n">
         <f aca="false">SUM(B21:M21)</f>
-        <v>90000</v>
+        <v>40000</v>
       </c>
       <c r="AA21" s="6" t="n">
         <f aca="false">SUM(N21:Y21)</f>
-        <v>162000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">B7*Assumptions!$B$16</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C22" s="6" t="n">
         <f aca="false">C7*Assumptions!$B$16</f>
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D22" s="6" t="n">
         <f aca="false">D7*Assumptions!$B$16</f>
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">E7*Assumptions!$B$16</f>
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="F22" s="6" t="n">
         <f aca="false">F7*Assumptions!$B$16</f>
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="G22" s="6" t="n">
         <f aca="false">G7*Assumptions!$B$16</f>
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="H22" s="6" t="n">
         <f aca="false">H7*Assumptions!$B$16</f>
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="I22" s="6" t="n">
         <f aca="false">I7*Assumptions!$B$16</f>
-        <v>825</v>
+        <v>165</v>
       </c>
       <c r="J22" s="6" t="n">
         <f aca="false">J7*Assumptions!$B$16</f>
-        <v>1375</v>
+        <v>275</v>
       </c>
       <c r="K22" s="6" t="n">
         <f aca="false">K7*Assumptions!$B$16</f>
-        <v>2125</v>
+        <v>425</v>
       </c>
       <c r="L22" s="6" t="n">
         <f aca="false">L7*Assumptions!$B$16</f>
-        <v>3075</v>
+        <v>615</v>
       </c>
       <c r="M22" s="6" t="n">
         <f aca="false">M7*Assumptions!$B$16</f>
-        <v>4300</v>
+        <v>860</v>
       </c>
       <c r="N22" s="6" t="n">
         <f aca="false">N7*Assumptions!$B$16</f>
-        <v>5350</v>
+        <v>1070</v>
       </c>
       <c r="O22" s="6" t="n">
         <f aca="false">O7*Assumptions!$B$16</f>
-        <v>6046.5</v>
+        <v>1209.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <f aca="false">P7*Assumptions!$B$16</f>
-        <v>6736.035</v>
+        <v>1347.207</v>
       </c>
       <c r="Q22" s="6" t="n">
         <f aca="false">Q7*Assumptions!$B$16</f>
-        <v>7418.67465</v>
+        <v>1483.73493</v>
       </c>
       <c r="R22" s="6" t="n">
         <f aca="false">R7*Assumptions!$B$16</f>
-        <v>8094.4879035</v>
+        <v>1618.8975807</v>
       </c>
       <c r="S22" s="6" t="n">
         <f aca="false">S7*Assumptions!$B$16</f>
-        <v>8763.543024465</v>
+        <v>1752.708604893</v>
       </c>
       <c r="T22" s="6" t="n">
         <f aca="false">T7*Assumptions!$B$16</f>
-        <v>9425.90759422035</v>
+        <v>1885.18151884407</v>
       </c>
       <c r="U22" s="6" t="n">
         <f aca="false">U7*Assumptions!$B$16</f>
-        <v>10081.6485182781</v>
+        <v>2016.32970365563</v>
       </c>
       <c r="V22" s="6" t="n">
         <f aca="false">V7*Assumptions!$B$16</f>
-        <v>10730.8320330954</v>
+        <v>2146.16640661907</v>
       </c>
       <c r="W22" s="6" t="n">
         <f aca="false">W7*Assumptions!$B$16</f>
-        <v>11373.5237127644</v>
+        <v>2274.70474255288</v>
       </c>
       <c r="X22" s="6" t="n">
         <f aca="false">X7*Assumptions!$B$16</f>
-        <v>12009.7884756368</v>
+        <v>2401.95769512735</v>
       </c>
       <c r="Y22" s="6" t="n">
         <f aca="false">Y7*Assumptions!$B$16</f>
-        <v>12639.6905908804</v>
+        <v>2527.93811817608</v>
       </c>
       <c r="Z22" s="6" t="n">
         <f aca="false">SUM(B22:M22)</f>
-        <v>13050</v>
+        <v>2610</v>
       </c>
       <c r="AA22" s="6" t="n">
         <f aca="false">SUM(N22:Y22)</f>
-        <v>108670.63150284</v>
+        <v>21734.1263005681</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!B33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!B33&gt;=Assumptions!$B$22,B5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!C33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!C33&gt;=Assumptions!$B$22,C5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="D23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!D33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!D33&gt;=Assumptions!$B$22,D5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!E33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!E33&gt;=Assumptions!$B$22,E5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!F33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!F33&gt;=Assumptions!$B$22,F5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!G33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!G33&gt;=Assumptions!$B$22,G5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!H33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!H33&gt;=Assumptions!$B$22,H5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!I33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!I33&gt;=Assumptions!$B$22,I5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!J33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!J33&gt;=Assumptions!$B$22,J5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!K33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!K33&gt;=Assumptions!$B$22,K5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="L23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!L33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!L33&gt;=Assumptions!$B$22,L5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="M23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!M33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!M33&gt;=Assumptions!$B$22,M5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!N33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!N33&gt;=Assumptions!$B$22,N5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="O23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!O33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!O33&gt;=Assumptions!$B$22,O5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="P23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!P33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!P33&gt;=Assumptions!$B$22,P5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!Q33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Q33&gt;=Assumptions!$B$22,Q5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="R23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!R33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!R33&gt;=Assumptions!$B$22,R5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="S23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!S33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!S33&gt;=Assumptions!$B$22,S5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="T23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!T33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!T33&gt;=Assumptions!$B$22,T5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="U23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!U33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!U33&gt;=Assumptions!$B$22,U5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
       </c>
       <c r="V23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!V33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!V33&gt;=Assumptions!$B$22,V5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>2</v>
       </c>
       <c r="W23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!W33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!W33&gt;=Assumptions!$B$22,W5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>2</v>
       </c>
       <c r="X23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!X33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!X33&gt;=Assumptions!$B$22,X5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>2</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <f aca="false">Assumptions!$B$21</f>
-        <v>150</v>
+        <f aca="false">IF(Assumptions!Y33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Y33&gt;=Assumptions!$B$22,Y5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>2</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <f aca="false">SUM(B23:M23)</f>
-        <v>1800</v>
+        <f aca="false">M23</f>
+        <v>1</v>
       </c>
       <c r="AA23" s="6" t="n">
-        <f aca="false">SUM(N23:Y23)</f>
-        <v>1800</v>
+        <f aca="false">Y23</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">B23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">C23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">D23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">E23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">F23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">G23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">H23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">I23*Assumptions!$B$21</f>
+        <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">J23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">K23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">L23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="M24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">M23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="N24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">N23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="O24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">O23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="P24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">P23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">Q23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="R24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">R23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="S24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">S23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="T24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">T23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="U24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">U23*Assumptions!$B$21</f>
+        <v>9000</v>
       </c>
       <c r="V24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">V23*Assumptions!$B$21</f>
+        <v>18000</v>
       </c>
       <c r="W24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">W23*Assumptions!$B$21</f>
+        <v>18000</v>
       </c>
       <c r="X24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">X23*Assumptions!$B$21</f>
+        <v>18000</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>500</v>
+        <f aca="false">Y23*Assumptions!$B$21</f>
+        <v>18000</v>
       </c>
       <c r="Z24" s="6" t="n">
         <f aca="false">SUM(B24:M24)</f>
-        <v>6000</v>
+        <v>36000</v>
       </c>
       <c r="AA24" s="6" t="n">
         <f aca="false">SUM(N24:Y24)</f>
-        <v>6000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="C25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="D25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="E25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="F25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="G25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="H25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="I25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="J25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="K25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="L25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="M25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="N25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="O25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="P25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="R25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="S25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="T25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="U25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="V25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="W25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="X25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <f aca="false">Assumptions!$B$23</f>
-        <v>1200</v>
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
       </c>
       <c r="Z25" s="6" t="n">
         <f aca="false">SUM(B25:M25)</f>
-        <v>14400</v>
+        <v>1800</v>
       </c>
       <c r="AA25" s="6" t="n">
         <f aca="false">SUM(N25:Y25)</f>
-        <v>14400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="C26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="D26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="E26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="F26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="G26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="H26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="I26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="J26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="K26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="L26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="M26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="N26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="O26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="P26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="R26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="S26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="T26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="U26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="V26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="W26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="X26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <f aca="false">Assumptions!$B$24</f>
-        <v>7500</v>
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
       </c>
       <c r="Z26" s="6" t="n">
         <f aca="false">SUM(B26:M26)</f>
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="AA26" s="6" t="n">
         <f aca="false">SUM(N26:Y26)</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="T27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="U27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="V27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="W27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="X27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Y27" s="6" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Z27" s="6" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>14400</v>
+      </c>
+      <c r="AA27" s="6" t="n">
+        <f aca="false">SUM(N27:Y27)</f>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="X28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Y28" s="6" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Z28" s="6" t="n">
+        <f aca="false">SUM(B28:M28)</f>
         <v>90000</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="7" t="n">
-        <f aca="false">SUM(B21:B26)</f>
-        <v>10275</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <f aca="false">SUM(C21:C26)</f>
-        <v>10325</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <f aca="false">SUM(D21:D26)</f>
-        <v>10375</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <f aca="false">SUM(E21:E26)</f>
-        <v>10425</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <f aca="false">SUM(F21:F26)</f>
-        <v>10475</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <f aca="false">SUM(G21:G26)</f>
-        <v>10525</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <f aca="false">SUM(H21:H26)</f>
-        <v>15200</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <f aca="false">SUM(I21:I26)</f>
-        <v>18275</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <f aca="false">SUM(J21:J26)</f>
-        <v>22425</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <f aca="false">SUM(K21:K26)</f>
-        <v>26775</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <f aca="false">SUM(L21:L26)</f>
-        <v>31325</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <f aca="false">SUM(M21:M26)</f>
-        <v>38850</v>
-      </c>
-      <c r="N27" s="7" t="n">
-        <f aca="false">SUM(N21:N26)</f>
-        <v>28200</v>
-      </c>
-      <c r="O27" s="7" t="n">
-        <f aca="false">SUM(O21:O26)</f>
-        <v>28896.5</v>
-      </c>
-      <c r="P27" s="7" t="n">
-        <f aca="false">SUM(P21:P26)</f>
-        <v>29586.035</v>
-      </c>
-      <c r="Q27" s="7" t="n">
-        <f aca="false">SUM(Q21:Q26)</f>
-        <v>30268.67465</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <f aca="false">SUM(R21:R26)</f>
-        <v>30944.4879035</v>
-      </c>
-      <c r="S27" s="7" t="n">
-        <f aca="false">SUM(S21:S26)</f>
-        <v>31613.543024465</v>
-      </c>
-      <c r="T27" s="7" t="n">
-        <f aca="false">SUM(T21:T26)</f>
-        <v>32275.9075942204</v>
-      </c>
-      <c r="U27" s="7" t="n">
-        <f aca="false">SUM(U21:U26)</f>
-        <v>32931.6485182782</v>
-      </c>
-      <c r="V27" s="7" t="n">
-        <f aca="false">SUM(V21:V26)</f>
-        <v>33580.8320330954</v>
-      </c>
-      <c r="W27" s="7" t="n">
-        <f aca="false">SUM(W21:W26)</f>
-        <v>34223.5237127644</v>
-      </c>
-      <c r="X27" s="7" t="n">
-        <f aca="false">SUM(X21:X26)</f>
-        <v>34859.7884756368</v>
-      </c>
-      <c r="Y27" s="7" t="n">
-        <f aca="false">SUM(Y21:Y26)</f>
-        <v>35489.6905908804</v>
-      </c>
-      <c r="Z27" s="7" t="n">
-        <f aca="false">SUM(B27:M27)</f>
-        <v>215250</v>
-      </c>
-      <c r="AA27" s="7" t="n">
-        <f aca="false">SUM(N27:Y27)</f>
-        <v>382870.63150284</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="7" t="n">
-        <f aca="false">B18-B27</f>
-        <v>-10026</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <f aca="false">C18-C27</f>
-        <v>-9578</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <f aca="false">D18-D27</f>
-        <v>-9130</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <f aca="false">E18-E27</f>
-        <v>-8682</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <f aca="false">F18-F27</f>
-        <v>-8234</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <f aca="false">G18-G27</f>
-        <v>-7786</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <f aca="false">H18-H27</f>
-        <v>-10718</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <f aca="false">I18-I27</f>
-        <v>-10058</v>
-      </c>
-      <c r="J28" s="7" t="n">
-        <f aca="false">J18-J27</f>
-        <v>-8730</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <f aca="false">K18-K27</f>
-        <v>-5610</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <f aca="false">L18-L27</f>
-        <v>-698</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <f aca="false">M18-M27</f>
-        <v>3978</v>
-      </c>
-      <c r="N28" s="7" t="n">
-        <f aca="false">N18-N27</f>
-        <v>25086</v>
-      </c>
-      <c r="O28" s="7" t="n">
-        <f aca="false">O18-O27</f>
-        <v>31326.64</v>
-      </c>
-      <c r="P28" s="7" t="n">
-        <f aca="false">P18-P27</f>
-        <v>37504.8736</v>
-      </c>
-      <c r="Q28" s="7" t="n">
-        <f aca="false">Q18-Q27</f>
-        <v>43621.324864</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <f aca="false">R18-R27</f>
-        <v>49676.61161536</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <f aca="false">S18-S27</f>
-        <v>55671.3454992064</v>
-      </c>
-      <c r="T28" s="7" t="n">
-        <f aca="false">T18-T27</f>
-        <v>61606.1320442143</v>
-      </c>
-      <c r="U28" s="7" t="n">
-        <f aca="false">U18-U27</f>
-        <v>67481.5707237722</v>
-      </c>
-      <c r="V28" s="7" t="n">
-        <f aca="false">V18-V27</f>
-        <v>73298.2550165345</v>
-      </c>
-      <c r="W28" s="7" t="n">
-        <f aca="false">W18-W27</f>
-        <v>79056.7724663691</v>
-      </c>
-      <c r="X28" s="7" t="n">
-        <f aca="false">X18-X27</f>
-        <v>84757.7047417054</v>
-      </c>
-      <c r="Y28" s="7" t="n">
-        <f aca="false">Y18-Y27</f>
-        <v>90401.6276942884</v>
-      </c>
-      <c r="Z28" s="7" t="n">
-        <f aca="false">SUM(B28:M28)</f>
-        <v>-85272</v>
-      </c>
-      <c r="AA28" s="7" t="n">
+      <c r="AA28" s="6" t="n">
         <f aca="false">SUM(N28:Y28)</f>
-        <v>699488.85826545</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:B28))-0)</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:C28))-SUM($B29:B29))</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:D28))-SUM($B29:C29))</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:E28))-SUM($B29:D29))</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:F28))-SUM($B29:E29))</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:G28))-SUM($B29:F29))</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:H28))-SUM($B29:G29))</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:I28))-SUM($B29:H29))</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:J28))-SUM($B29:I29))</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:K28))-SUM($B29:J29))</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:L28))-SUM($B29:K29))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:M28))-SUM($B29:L29))</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:N28))-SUM($B29:M29))</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:O28))-SUM($B29:N29))</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:P28))-SUM($B29:O29))</f>
-        <v>2161.3784</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:Q28))-SUM($B29:P29))</f>
-        <v>10905.331216</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:R28))-SUM($B29:Q29))</f>
-        <v>12419.15290384</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:S28))-SUM($B29:R29))</f>
-        <v>13917.8363748016</v>
-      </c>
-      <c r="T29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:T28))-SUM($B29:S29))</f>
-        <v>15401.5330110536</v>
-      </c>
-      <c r="U29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:U28))-SUM($B29:T29))</f>
-        <v>16870.392680943</v>
-      </c>
-      <c r="V29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:V28))-SUM($B29:U29))</f>
-        <v>18324.5637541336</v>
-      </c>
-      <c r="W29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:W28))-SUM($B29:V29))</f>
-        <v>19764.1931165923</v>
-      </c>
-      <c r="X29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:X28))-SUM($B29:W29))</f>
-        <v>21189.4261854264</v>
-      </c>
-      <c r="Y29" s="6" t="n">
-        <f aca="false">MAX(0,Assumptions!$B$25*MAX(0,SUM($B28:Y28))-SUM($B29:X29))</f>
-        <v>22600.4069235721</v>
-      </c>
-      <c r="Z29" s="6" t="n">
+      <c r="A29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <f aca="false">SUM(B21:B28)</f>
+        <v>9755</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <f aca="false">SUM(C21:C28)</f>
+        <v>9765</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <f aca="false">SUM(D21:D28)</f>
+        <v>9775</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <f aca="false">SUM(E21:E28)</f>
+        <v>9785</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <f aca="false">SUM(F21:F28)</f>
+        <v>9795</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <f aca="false">SUM(G21:G28)</f>
+        <v>9805</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <f aca="false">SUM(H21:H28)</f>
+        <v>11840</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <f aca="false">SUM(I21:I28)</f>
+        <v>13115</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <f aca="false">SUM(J21:J28)</f>
+        <v>23826</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <f aca="false">SUM(K21:K28)</f>
+        <v>25576</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <f aca="false">SUM(L21:L28)</f>
+        <v>27366</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <f aca="false">SUM(M21:M28)</f>
+        <v>30411</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <f aca="false">SUM(N21:N28)</f>
+        <v>25421</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <f aca="false">SUM(O21:O28)</f>
+        <v>25560.3</v>
+      </c>
+      <c r="P29" s="7" t="n">
+        <f aca="false">SUM(P21:P28)</f>
+        <v>25698.207</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <f aca="false">SUM(Q21:Q28)</f>
+        <v>25834.73493</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <f aca="false">SUM(R21:R28)</f>
+        <v>25969.8975807</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <f aca="false">SUM(S21:S28)</f>
+        <v>26103.708604893</v>
+      </c>
+      <c r="T29" s="7" t="n">
+        <f aca="false">SUM(T21:T28)</f>
+        <v>26236.1815188441</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <f aca="false">SUM(U21:U28)</f>
+        <v>26367.3297036556</v>
+      </c>
+      <c r="V29" s="7" t="n">
+        <f aca="false">SUM(V21:V28)</f>
+        <v>35498.1664066191</v>
+      </c>
+      <c r="W29" s="7" t="n">
+        <f aca="false">SUM(W21:W28)</f>
+        <v>35626.7047425529</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <f aca="false">SUM(X21:X28)</f>
+        <v>35753.9576951274</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <f aca="false">SUM(Y21:Y28)</f>
+        <v>35879.9381181761</v>
+      </c>
+      <c r="Z29" s="7" t="n">
         <f aca="false">SUM(B29:M29)</f>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="6" t="n">
+        <v>190814</v>
+      </c>
+      <c r="AA29" s="7" t="n">
         <f aca="false">SUM(N29:Y29)</f>
-        <v>153554.214566363</v>
+        <v>349950.126300568</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B30" s="7" t="n">
-        <f aca="false">B28-B29</f>
-        <v>-10026</v>
+        <f aca="false">B18-B29</f>
+        <v>-9506</v>
       </c>
       <c r="C30" s="7" t="n">
-        <f aca="false">C28-C29</f>
-        <v>-9578</v>
+        <f aca="false">C18-C29</f>
+        <v>-9018</v>
       </c>
       <c r="D30" s="7" t="n">
-        <f aca="false">D28-D29</f>
-        <v>-9130</v>
+        <f aca="false">D18-D29</f>
+        <v>-8530</v>
       </c>
       <c r="E30" s="7" t="n">
-        <f aca="false">E28-E29</f>
-        <v>-8682</v>
+        <f aca="false">E18-E29</f>
+        <v>-8042</v>
       </c>
       <c r="F30" s="7" t="n">
-        <f aca="false">F28-F29</f>
-        <v>-8234</v>
+        <f aca="false">F18-F29</f>
+        <v>-7554</v>
       </c>
       <c r="G30" s="7" t="n">
-        <f aca="false">G28-G29</f>
-        <v>-7786</v>
+        <f aca="false">G18-G29</f>
+        <v>-7066</v>
       </c>
       <c r="H30" s="7" t="n">
-        <f aca="false">H28-H29</f>
-        <v>-10718</v>
+        <f aca="false">H18-H29</f>
+        <v>-7358</v>
       </c>
       <c r="I30" s="7" t="n">
-        <f aca="false">I28-I29</f>
-        <v>-10058</v>
+        <f aca="false">I18-I29</f>
+        <v>-4898</v>
       </c>
       <c r="J30" s="7" t="n">
-        <f aca="false">J28-J29</f>
-        <v>-8730</v>
+        <f aca="false">J18-J29</f>
+        <v>-10131</v>
       </c>
       <c r="K30" s="7" t="n">
-        <f aca="false">K28-K29</f>
-        <v>-5610</v>
+        <f aca="false">K18-K29</f>
+        <v>-4411</v>
       </c>
       <c r="L30" s="7" t="n">
-        <f aca="false">L28-L29</f>
-        <v>-698</v>
+        <f aca="false">L18-L29</f>
+        <v>3261</v>
       </c>
       <c r="M30" s="7" t="n">
-        <f aca="false">M28-M29</f>
-        <v>3978</v>
+        <f aca="false">M18-M29</f>
+        <v>12417</v>
       </c>
       <c r="N30" s="7" t="n">
-        <f aca="false">N28-N29</f>
-        <v>25086</v>
+        <f aca="false">N18-N29</f>
+        <v>27865</v>
       </c>
       <c r="O30" s="7" t="n">
-        <f aca="false">O28-O29</f>
-        <v>31326.64</v>
+        <f aca="false">O18-O29</f>
+        <v>34662.84</v>
       </c>
       <c r="P30" s="7" t="n">
-        <f aca="false">P28-P29</f>
-        <v>35343.4952</v>
+        <f aca="false">P18-P29</f>
+        <v>41392.7016</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <f aca="false">Q28-Q29</f>
-        <v>32715.993648</v>
+        <f aca="false">Q18-Q29</f>
+        <v>48055.264584</v>
       </c>
       <c r="R30" s="7" t="n">
-        <f aca="false">R28-R29</f>
-        <v>37257.45871152</v>
+        <f aca="false">R18-R29</f>
+        <v>54651.20193816</v>
       </c>
       <c r="S30" s="7" t="n">
-        <f aca="false">S28-S29</f>
-        <v>41753.5091244048</v>
+        <f aca="false">S18-S29</f>
+        <v>61181.1799187784</v>
       </c>
       <c r="T30" s="7" t="n">
-        <f aca="false">T28-T29</f>
-        <v>46204.5990331607</v>
+        <f aca="false">T18-T29</f>
+        <v>67645.8581195906</v>
       </c>
       <c r="U30" s="7" t="n">
-        <f aca="false">U28-U29</f>
-        <v>50611.1780428292</v>
+        <f aca="false">U18-U29</f>
+        <v>74045.8895383947</v>
       </c>
       <c r="V30" s="7" t="n">
-        <f aca="false">V28-V29</f>
-        <v>54973.6912624009</v>
+        <f aca="false">V18-V29</f>
+        <v>71380.9206430108</v>
       </c>
       <c r="W30" s="7" t="n">
-        <f aca="false">W28-W29</f>
-        <v>59292.5793497768</v>
+        <f aca="false">W18-W29</f>
+        <v>77653.5914365807</v>
       </c>
       <c r="X30" s="7" t="n">
-        <f aca="false">X28-X29</f>
-        <v>63568.2785562791</v>
+        <f aca="false">X18-X29</f>
+        <v>83863.5355222149</v>
       </c>
       <c r="Y30" s="7" t="n">
-        <f aca="false">Y28-Y29</f>
-        <v>67801.2207707163</v>
+        <f aca="false">Y18-Y29</f>
+        <v>90011.3801669927</v>
       </c>
       <c r="Z30" s="7" t="n">
         <f aca="false">SUM(B30:M30)</f>
-        <v>-85272</v>
+        <v>-60836</v>
       </c>
       <c r="AA30" s="7" t="n">
         <f aca="false">SUM(N30:Y30)</f>
-        <v>545934.643699088</v>
+        <v>732409.363467723</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B31" s="6" t="n">
-        <f aca="false">SUM($B30:B30)</f>
-        <v>-10026</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:B30))-0)</f>
+        <v>0</v>
       </c>
       <c r="C31" s="6" t="n">
-        <f aca="false">SUM($B30:C30)</f>
-        <v>-19604</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:C30))-SUM($B31:B31))</f>
+        <v>0</v>
       </c>
       <c r="D31" s="6" t="n">
-        <f aca="false">SUM($B30:D30)</f>
-        <v>-28734</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:D30))-SUM($B31:C31))</f>
+        <v>0</v>
       </c>
       <c r="E31" s="6" t="n">
-        <f aca="false">SUM($B30:E30)</f>
-        <v>-37416</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:E30))-SUM($B31:D31))</f>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <f aca="false">SUM($B30:F30)</f>
-        <v>-45650</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:F30))-SUM($B31:E31))</f>
+        <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <f aca="false">SUM($B30:G30)</f>
-        <v>-53436</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:G30))-SUM($B31:F31))</f>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <f aca="false">SUM($B30:H30)</f>
-        <v>-64154</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:H30))-SUM($B31:G31))</f>
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
-        <f aca="false">SUM($B30:I30)</f>
-        <v>-74212</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:I30))-SUM($B31:H31))</f>
+        <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <f aca="false">SUM($B30:J30)</f>
-        <v>-82942</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:J30))-SUM($B31:I31))</f>
+        <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <f aca="false">SUM($B30:K30)</f>
-        <v>-88552</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:K30))-SUM($B31:J31))</f>
+        <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <f aca="false">SUM($B30:L30)</f>
-        <v>-89250</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:L30))-SUM($B31:K31))</f>
+        <v>0</v>
       </c>
       <c r="M31" s="6" t="n">
-        <f aca="false">SUM($B30:M30)</f>
-        <v>-85272</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:M30))-SUM($B31:L31))</f>
+        <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <f aca="false">SUM($B30:N30)</f>
-        <v>-60186</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:N30))-SUM($B31:M31))</f>
+        <v>0</v>
       </c>
       <c r="O31" s="6" t="n">
-        <f aca="false">SUM($B30:O30)</f>
-        <v>-28859.36</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:O30))-SUM($B31:N31))</f>
+        <v>422.960000000003</v>
       </c>
       <c r="P31" s="6" t="n">
-        <f aca="false">SUM($B30:P30)</f>
-        <v>6484.1352</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:P30))-SUM($B31:O31))</f>
+        <v>10348.1754</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <f aca="false">SUM($B30:Q30)</f>
-        <v>39200.128848</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Q30))-SUM($B31:P31))</f>
+        <v>12013.816146</v>
       </c>
       <c r="R31" s="6" t="n">
-        <f aca="false">SUM($B30:R30)</f>
-        <v>76457.58755952</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:R30))-SUM($B31:Q31))</f>
+        <v>13662.80048454</v>
       </c>
       <c r="S31" s="6" t="n">
-        <f aca="false">SUM($B30:S30)</f>
-        <v>118211.096683925</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:S30))-SUM($B31:R31))</f>
+        <v>15295.2949796946</v>
       </c>
       <c r="T31" s="6" t="n">
-        <f aca="false">SUM($B30:T30)</f>
-        <v>164415.695717086</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:T30))-SUM($B31:S31))</f>
+        <v>16911.4645298977</v>
       </c>
       <c r="U31" s="6" t="n">
-        <f aca="false">SUM($B30:U30)</f>
-        <v>215026.873759915</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:U30))-SUM($B31:T31))</f>
+        <v>18511.4723845987</v>
       </c>
       <c r="V31" s="6" t="n">
-        <f aca="false">SUM($B30:V30)</f>
-        <v>270000.565022316</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:V30))-SUM($B31:U31))</f>
+        <v>17845.2301607527</v>
       </c>
       <c r="W31" s="6" t="n">
-        <f aca="false">SUM($B30:W30)</f>
-        <v>329293.144372092</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:W30))-SUM($B31:V31))</f>
+        <v>19413.3978591452</v>
       </c>
       <c r="X31" s="6" t="n">
-        <f aca="false">SUM($B30:X30)</f>
-        <v>392861.422928371</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:X30))-SUM($B31:W31))</f>
+        <v>20965.8838805537</v>
       </c>
       <c r="Y31" s="6" t="n">
-        <f aca="false">SUM($B30:Y30)</f>
-        <v>460662.643699088</v>
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Y30))-SUM($B31:X31))</f>
+        <v>22502.8450417482</v>
       </c>
       <c r="Z31" s="6" t="n">
-        <f aca="false">M31</f>
-        <v>-85272</v>
+        <f aca="false">SUM(B31:M31)</f>
+        <v>0</v>
       </c>
       <c r="AA31" s="6" t="n">
-        <f aca="false">Y31</f>
-        <v>460662.643699088</v>
+        <f aca="false">SUM(N31:Y31)</f>
+        <v>167893.340866931</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">B30-B31</f>
+        <v>-9506</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <f aca="false">C30-C31</f>
+        <v>-9018</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <f aca="false">D30-D31</f>
+        <v>-8530</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <f aca="false">E30-E31</f>
+        <v>-8042</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <f aca="false">F30-F31</f>
+        <v>-7554</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <f aca="false">G30-G31</f>
+        <v>-7066</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <f aca="false">H30-H31</f>
+        <v>-7358</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <f aca="false">I30-I31</f>
+        <v>-4898</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <f aca="false">J30-J31</f>
+        <v>-10131</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <f aca="false">K30-K31</f>
+        <v>-4411</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <f aca="false">L30-L31</f>
+        <v>3261</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <f aca="false">M30-M31</f>
+        <v>12417</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <f aca="false">N30-N31</f>
+        <v>27865</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <f aca="false">O30-O31</f>
+        <v>34239.88</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <f aca="false">P30-P31</f>
+        <v>31044.5262</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <f aca="false">Q30-Q31</f>
+        <v>36041.448438</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <f aca="false">R30-R31</f>
+        <v>40988.40145362</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <f aca="false">S30-S31</f>
+        <v>45885.8849390838</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <f aca="false">T30-T31</f>
+        <v>50734.393589693</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <f aca="false">U30-U31</f>
+        <v>55534.417153796</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <f aca="false">V30-V31</f>
+        <v>53535.6904822581</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <f aca="false">W30-W31</f>
+        <v>58240.1935774355</v>
+      </c>
+      <c r="X32" s="7" t="n">
+        <f aca="false">X30-X31</f>
+        <v>62897.6516416611</v>
+      </c>
+      <c r="Y32" s="7" t="n">
+        <f aca="false">Y30-Y31</f>
+        <v>67508.5351252445</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <f aca="false">SUM(B32:M32)</f>
+        <v>-60836</v>
+      </c>
+      <c r="AA32" s="7" t="n">
+        <f aca="false">SUM(N32:Y32)</f>
+        <v>564516.022600792</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <f aca="false">SUM($B32:B32)</f>
+        <v>-9506</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <f aca="false">SUM($B32:C32)</f>
+        <v>-18524</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <f aca="false">SUM($B32:D32)</f>
+        <v>-27054</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <f aca="false">SUM($B32:E32)</f>
+        <v>-35096</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <f aca="false">SUM($B32:F32)</f>
+        <v>-42650</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <f aca="false">SUM($B32:G32)</f>
+        <v>-49716</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <f aca="false">SUM($B32:H32)</f>
+        <v>-57074</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <f aca="false">SUM($B32:I32)</f>
+        <v>-61972</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <f aca="false">SUM($B32:J32)</f>
+        <v>-72103</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <f aca="false">SUM($B32:K32)</f>
+        <v>-76514</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <f aca="false">SUM($B32:L32)</f>
+        <v>-73253</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <f aca="false">SUM($B32:M32)</f>
+        <v>-60836</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <f aca="false">SUM($B32:N32)</f>
+        <v>-32971</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <f aca="false">SUM($B32:O32)</f>
+        <v>1268.88</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <f aca="false">SUM($B32:P32)</f>
+        <v>32313.4062</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <f aca="false">SUM($B32:Q32)</f>
+        <v>68354.854638</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <f aca="false">SUM($B32:R32)</f>
+        <v>109343.25609162</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <f aca="false">SUM($B32:S32)</f>
+        <v>155229.141030704</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <f aca="false">SUM($B32:T32)</f>
+        <v>205963.534620397</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <f aca="false">SUM($B32:U32)</f>
+        <v>261497.951774193</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <f aca="false">SUM($B32:V32)</f>
+        <v>315033.642256451</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <f aca="false">SUM($B32:W32)</f>
+        <v>373273.835833886</v>
+      </c>
+      <c r="X33" s="6" t="n">
+        <f aca="false">SUM($B32:X32)</f>
+        <v>436171.487475548</v>
+      </c>
+      <c r="Y33" s="6" t="n">
+        <f aca="false">SUM($B32:Y32)</f>
+        <v>503680.022600792</v>
+      </c>
+      <c r="Z33" s="6" t="n">
+        <f aca="false">M33</f>
+        <v>-60836</v>
+      </c>
+      <c r="AA33" s="6" t="n">
+        <f aca="false">Y33</f>
+        <v>503680.022600792</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OnSite-forecast-PnL.xlsx
+++ b/docs/OnSite-forecast-PnL.xlsx
@@ -8,8 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="P&amp;L" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="P&amp;L cautious" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="117">
+  <si>
+    <t xml:space="preserve">OnSite - base vs cautious (AUD, ex GST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cautious Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cautious Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parks at end of year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total operating expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit before tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative net profit</t>
+  </si>
   <si>
     <t xml:space="preserve">OnSite - forecast assumptions (blue = editable inputs). All amounts AUD, excluding GST.</t>
   </si>
@@ -155,7 +196,7 @@
     <t xml:space="preserve">Calls per park per month</t>
   </si>
   <si>
-    <t xml:space="preserve">New parks signed per month (growth plan)</t>
+    <t xml:space="preserve">BASE CASE - new parks signed per month</t>
   </si>
   <si>
     <t xml:space="preserve">Month</t>
@@ -167,7 +208,16 @@
     <t xml:space="preserve">Monthly churn (% of parks at start of month)</t>
   </si>
   <si>
-    <t xml:space="preserve">OnSite - 24-month forecast profit &amp; loss (AUD, ex GST)</t>
+    <t xml:space="preserve">CAUTIOUS CASE - Year 1 as base, Year 2 sign-ups cut to 10 a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New parks (cautious)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly churn (cautious)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnSite - 24-month forecast profit &amp; loss, base case (AUD, ex GST)</t>
   </si>
   <si>
     <t xml:space="preserve">M1</t>
@@ -275,9 +325,6 @@
     <t xml:space="preserve">Per-call fees</t>
   </si>
   <si>
-    <t xml:space="preserve">Total revenue</t>
-  </si>
-  <si>
     <t xml:space="preserve">COST OF SERVICE</t>
   </si>
   <si>
@@ -293,9 +340,6 @@
     <t xml:space="preserve">Total cost of service</t>
   </si>
   <si>
-    <t xml:space="preserve">Gross profit</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gross margin %</t>
   </si>
   <si>
@@ -326,19 +370,10 @@
     <t xml:space="preserve">Founder salary</t>
   </si>
   <si>
-    <t xml:space="preserve">Total operating expenses</t>
-  </si>
-  <si>
     <t xml:space="preserve">EBITDA / profit before tax</t>
   </si>
   <si>
-    <t xml:space="preserve">Income tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative net profit</t>
+    <t xml:space="preserve">OnSite - 24-month forecast profit &amp; loss, cautious case (10 sign-ups a month in Year 2) (AUD, ex GST)</t>
   </si>
 </sst>
 </file>
@@ -347,8 +382,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -449,6 +484,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -457,19 +496,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -725,11 +760,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -738,41 +773,81 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
         <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
+        <f aca="false">'P&amp;L'!Z6</f>
+        <v>200</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA6</f>
+        <v>518.122359194838</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z6</f>
+        <v>200</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA6</f>
+        <v>290.892102627097</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>5</v>
+        <f aca="false">'P&amp;L'!Z12</f>
+        <v>153990</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA12</f>
+        <v>1282313.45173352</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z12</f>
+        <v>153990</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA12</f>
+        <v>872089.557638148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
+        <f aca="false">'P&amp;L'!Z18</f>
+        <v>129978</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA18</f>
+        <v>1082359.48976829</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z18</f>
+        <v>129978</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA18</f>
+        <v>736102.711362369</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -780,468 +855,104 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4.33333333333333</v>
-      </c>
-      <c r="C7" s="4" t="s">
+        <f aca="false">'P&amp;L'!Z29</f>
+        <v>190814</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA29</f>
+        <v>349950.126300568</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z29</f>
+        <v>190814</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA29</f>
+        <v>258993.178943019</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
+      <c r="B8" s="3" t="n">
+        <f aca="false">'P&amp;L'!Z30</f>
+        <v>-60836</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA30</f>
+        <v>732409.363467723</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z30</f>
+        <v>-60836</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA30</f>
+        <v>477109.532419349</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
+        <f aca="false">'P&amp;L'!Z31</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA31</f>
+        <v>167893.340866931</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z31</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA31</f>
+        <v>104068.383104837</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>14</v>
+        <f aca="false">'P&amp;L'!Z32</f>
+        <v>-60836</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA32</f>
+        <v>564516.022600792</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z32</f>
+        <v>-60836</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA32</f>
+        <v>373041.149314512</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <f aca="false">$B$6*$B$7</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="I33" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="M33" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="N33" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="O33" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="P33" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q33" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="R33" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="S33" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="T33" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="U33" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="V33" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="W33" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y33" s="0" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="W35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="X35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Y35" s="5" t="n">
-        <v>0.01</v>
+        <f aca="false">'P&amp;L'!Z33</f>
+        <v>-60836</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <f aca="false">'P&amp;L'!AA33</f>
+        <v>503680.022600792</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!Z33</f>
+        <v>-60836</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <f aca="false">'P&amp;L cautious'!AA33</f>
+        <v>312205.149314512</v>
       </c>
     </row>
   </sheetData>
@@ -1260,6 +971,700 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:Y38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <f aca="false">$B$6*$B$7</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="N33" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="R33" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="T33" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="U33" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="V33" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="W33" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y33" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y38" s="6" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:AA33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1269,991 +1674,991 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <f aca="false">Assumptions!B34</f>
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="3" t="n">
         <f aca="false">Assumptions!C34</f>
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <f aca="false">Assumptions!D34</f>
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
         <f aca="false">Assumptions!E34</f>
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
         <f aca="false">Assumptions!F34</f>
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
         <f aca="false">Assumptions!G34</f>
         <v>2</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="3" t="n">
         <f aca="false">Assumptions!H34</f>
         <v>12</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="3" t="n">
         <f aca="false">Assumptions!I34</f>
         <v>18</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="3" t="n">
         <f aca="false">Assumptions!J34</f>
         <v>26</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="3" t="n">
         <f aca="false">Assumptions!K34</f>
         <v>34</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="3" t="n">
         <f aca="false">Assumptions!L34</f>
         <v>42</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="3" t="n">
         <f aca="false">Assumptions!M34</f>
         <v>56</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="N3" s="3" t="n">
         <f aca="false">Assumptions!N34</f>
         <v>30</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="O3" s="3" t="n">
         <f aca="false">Assumptions!O34</f>
         <v>30</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="3" t="n">
         <f aca="false">Assumptions!P34</f>
         <v>30</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" s="3" t="n">
         <f aca="false">Assumptions!Q34</f>
         <v>30</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="3" t="n">
         <f aca="false">Assumptions!R34</f>
         <v>30</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="S3" s="3" t="n">
         <f aca="false">Assumptions!S34</f>
         <v>30</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="T3" s="3" t="n">
         <f aca="false">Assumptions!T34</f>
         <v>30</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="U3" s="3" t="n">
         <f aca="false">Assumptions!U34</f>
         <v>30</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="V3" s="3" t="n">
         <f aca="false">Assumptions!V34</f>
         <v>30</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="W3" s="3" t="n">
         <f aca="false">Assumptions!W34</f>
         <v>30</v>
       </c>
-      <c r="X3" s="6" t="n">
+      <c r="X3" s="3" t="n">
         <f aca="false">Assumptions!X34</f>
         <v>30</v>
       </c>
-      <c r="Y3" s="6" t="n">
+      <c r="Y3" s="3" t="n">
         <f aca="false">Assumptions!Y34</f>
         <v>30</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="Z3" s="3" t="n">
         <f aca="false">SUM(B3:M3)</f>
         <v>200</v>
       </c>
-      <c r="AA3" s="6" t="n">
+      <c r="AA3" s="3" t="n">
         <f aca="false">SUM(N3:Y3)</f>
         <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <f aca="false">B5*Assumptions!B35</f>
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="3" t="n">
         <f aca="false">C5*Assumptions!C35</f>
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
         <f aca="false">D5*Assumptions!D35</f>
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">E5*Assumptions!E35</f>
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
         <f aca="false">F5*Assumptions!F35</f>
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
         <f aca="false">G5*Assumptions!G35</f>
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="3" t="n">
         <f aca="false">H5*Assumptions!H35</f>
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="3" t="n">
         <f aca="false">I5*Assumptions!I35</f>
         <v>0</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="3" t="n">
         <f aca="false">J5*Assumptions!J35</f>
         <v>0</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="3" t="n">
         <f aca="false">K5*Assumptions!K35</f>
         <v>0</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="3" t="n">
         <f aca="false">L5*Assumptions!L35</f>
         <v>0</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="3" t="n">
         <f aca="false">M5*Assumptions!M35</f>
         <v>0</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="3" t="n">
         <f aca="false">N5*Assumptions!N35</f>
         <v>2</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="3" t="n">
         <f aca="false">O5*Assumptions!O35</f>
         <v>2.28</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="3" t="n">
         <f aca="false">P5*Assumptions!P35</f>
         <v>2.5572</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="3" t="n">
         <f aca="false">Q5*Assumptions!Q35</f>
         <v>2.831628</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="3" t="n">
         <f aca="false">R5*Assumptions!R35</f>
         <v>3.10331172</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="3" t="n">
         <f aca="false">S5*Assumptions!S35</f>
         <v>3.3722786028</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="T4" s="3" t="n">
         <f aca="false">T5*Assumptions!T35</f>
         <v>3.638555816772</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="U4" s="3" t="n">
         <f aca="false">U5*Assumptions!U35</f>
         <v>3.90217025860428</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="V4" s="3" t="n">
         <f aca="false">V5*Assumptions!V35</f>
         <v>4.16314855601824</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="3" t="n">
         <f aca="false">W5*Assumptions!W35</f>
         <v>4.42151707045805</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="X4" s="3" t="n">
         <f aca="false">X5*Assumptions!X35</f>
         <v>4.67730189975347</v>
       </c>
-      <c r="Y4" s="6" t="n">
+      <c r="Y4" s="3" t="n">
         <f aca="false">Y5*Assumptions!Y35</f>
         <v>4.93052888075594</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="Z4" s="3" t="n">
         <f aca="false">SUM(B4:M4)</f>
         <v>0</v>
       </c>
-      <c r="AA4" s="6" t="n">
+      <c r="AA4" s="3" t="n">
         <f aca="false">SUM(N4:Y4)</f>
         <v>41.877640805162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <f aca="false">B6</f>
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <f aca="false">C6</f>
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="3" t="n">
         <f aca="false">D6</f>
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
         <f aca="false">E6</f>
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
         <f aca="false">F6</f>
         <v>10</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="3" t="n">
         <f aca="false">G6</f>
         <v>12</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="3" t="n">
         <f aca="false">H6</f>
         <v>24</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="3" t="n">
         <f aca="false">I6</f>
         <v>42</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="3" t="n">
         <f aca="false">J6</f>
         <v>68</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="3" t="n">
         <f aca="false">K6</f>
         <v>102</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="3" t="n">
         <f aca="false">L6</f>
         <v>144</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="3" t="n">
         <f aca="false">M6</f>
         <v>200</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="3" t="n">
         <f aca="false">N6</f>
         <v>228</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="3" t="n">
         <f aca="false">O6</f>
         <v>255.72</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="3" t="n">
         <f aca="false">P6</f>
         <v>283.1628</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="3" t="n">
         <f aca="false">Q6</f>
         <v>310.331172</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="3" t="n">
         <f aca="false">R6</f>
         <v>337.22786028</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="3" t="n">
         <f aca="false">S6</f>
         <v>363.8555816772</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" s="3" t="n">
         <f aca="false">T6</f>
         <v>390.217025860428</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V5" s="3" t="n">
         <f aca="false">U6</f>
         <v>416.314855601824</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" s="3" t="n">
         <f aca="false">V6</f>
         <v>442.151707045805</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" s="3" t="n">
         <f aca="false">W6</f>
         <v>467.730189975347</v>
       </c>
-      <c r="Y5" s="6" t="n">
+      <c r="Y5" s="3" t="n">
         <f aca="false">X6</f>
         <v>493.052888075594</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="Z5" s="3" t="n">
         <f aca="false">B5</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="6" t="n">
+      <c r="AA5" s="3" t="n">
         <f aca="false">N5</f>
         <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <f aca="false">B5+B3-B4</f>
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="3" t="n">
         <f aca="false">C5+C3-C4</f>
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="3" t="n">
         <f aca="false">D5+D3-D4</f>
         <v>6</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="3" t="n">
         <f aca="false">E5+E3-E4</f>
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n">
         <f aca="false">F5+F3-F4</f>
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
         <f aca="false">G5+G3-G4</f>
         <v>12</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="3" t="n">
         <f aca="false">H5+H3-H4</f>
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="3" t="n">
         <f aca="false">I5+I3-I4</f>
         <v>42</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="3" t="n">
         <f aca="false">J5+J3-J4</f>
         <v>68</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="3" t="n">
         <f aca="false">K5+K3-K4</f>
         <v>102</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="3" t="n">
         <f aca="false">L5+L3-L4</f>
         <v>144</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="3" t="n">
         <f aca="false">M5+M3-M4</f>
         <v>200</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="3" t="n">
         <f aca="false">N5+N3-N4</f>
         <v>228</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="3" t="n">
         <f aca="false">O5+O3-O4</f>
         <v>255.72</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="3" t="n">
         <f aca="false">P5+P3-P4</f>
         <v>283.1628</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="3" t="n">
         <f aca="false">Q5+Q3-Q4</f>
         <v>310.331172</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="3" t="n">
         <f aca="false">R5+R3-R4</f>
         <v>337.22786028</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="3" t="n">
         <f aca="false">S5+S3-S4</f>
         <v>363.8555816772</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="T6" s="3" t="n">
         <f aca="false">T5+T3-T4</f>
         <v>390.217025860428</v>
       </c>
-      <c r="U6" s="6" t="n">
+      <c r="U6" s="3" t="n">
         <f aca="false">U5+U3-U4</f>
         <v>416.314855601824</v>
       </c>
-      <c r="V6" s="6" t="n">
+      <c r="V6" s="3" t="n">
         <f aca="false">V5+V3-V4</f>
         <v>442.151707045805</v>
       </c>
-      <c r="W6" s="6" t="n">
+      <c r="W6" s="3" t="n">
         <f aca="false">W5+W3-W4</f>
         <v>467.730189975347</v>
       </c>
-      <c r="X6" s="6" t="n">
+      <c r="X6" s="3" t="n">
         <f aca="false">X5+X3-X4</f>
         <v>493.052888075594</v>
       </c>
-      <c r="Y6" s="6" t="n">
+      <c r="Y6" s="3" t="n">
         <f aca="false">Y5+Y3-Y4</f>
         <v>518.122359194838</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="Z6" s="3" t="n">
         <f aca="false">M6</f>
         <v>200</v>
       </c>
-      <c r="AA6" s="6" t="n">
+      <c r="AA6" s="3" t="n">
         <f aca="false">Y6</f>
         <v>518.122359194838</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <f aca="false">(B5+B6)/2</f>
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="3" t="n">
         <f aca="false">(C5+C6)/2</f>
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <f aca="false">(D5+D6)/2</f>
         <v>5</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="3" t="n">
         <f aca="false">(E5+E6)/2</f>
         <v>7</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="3" t="n">
         <f aca="false">(F5+F6)/2</f>
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
         <f aca="false">(G5+G6)/2</f>
         <v>11</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="3" t="n">
         <f aca="false">(H5+H6)/2</f>
         <v>18</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="3" t="n">
         <f aca="false">(I5+I6)/2</f>
         <v>33</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="3" t="n">
         <f aca="false">(J5+J6)/2</f>
         <v>55</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="3" t="n">
         <f aca="false">(K5+K6)/2</f>
         <v>85</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="3" t="n">
         <f aca="false">(L5+L6)/2</f>
         <v>123</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" s="3" t="n">
         <f aca="false">(M5+M6)/2</f>
         <v>172</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="3" t="n">
         <f aca="false">(N5+N6)/2</f>
         <v>214</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="O7" s="3" t="n">
         <f aca="false">(O5+O6)/2</f>
         <v>241.86</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="3" t="n">
         <f aca="false">(P5+P6)/2</f>
         <v>269.4414</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="3" t="n">
         <f aca="false">(Q5+Q6)/2</f>
         <v>296.746986</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" s="3" t="n">
         <f aca="false">(R5+R6)/2</f>
         <v>323.77951614</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="S7" s="3" t="n">
         <f aca="false">(S5+S6)/2</f>
         <v>350.5417209786</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="T7" s="3" t="n">
         <f aca="false">(T5+T6)/2</f>
         <v>377.036303768814</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U7" s="3" t="n">
         <f aca="false">(U5+U6)/2</f>
         <v>403.265940731126</v>
       </c>
-      <c r="V7" s="6" t="n">
+      <c r="V7" s="3" t="n">
         <f aca="false">(V5+V6)/2</f>
         <v>429.233281323815</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="W7" s="3" t="n">
         <f aca="false">(W5+W6)/2</f>
         <v>454.940948510576</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="X7" s="3" t="n">
         <f aca="false">(X5+X6)/2</f>
         <v>480.391539025471</v>
       </c>
-      <c r="Y7" s="6" t="n">
+      <c r="Y7" s="3" t="n">
         <f aca="false">(Y5+Y6)/2</f>
         <v>505.587623635216</v>
       </c>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$30</f>
         <v>65</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="3" t="n">
         <f aca="false">C7*Assumptions!$B$30</f>
         <v>195</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="3" t="n">
         <f aca="false">D7*Assumptions!$B$30</f>
         <v>325</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="3" t="n">
         <f aca="false">E7*Assumptions!$B$30</f>
         <v>455</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="3" t="n">
         <f aca="false">F7*Assumptions!$B$30</f>
         <v>585</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="3" t="n">
         <f aca="false">G7*Assumptions!$B$30</f>
         <v>715</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="3" t="n">
         <f aca="false">H7*Assumptions!$B$30</f>
         <v>1170</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="3" t="n">
         <f aca="false">I7*Assumptions!$B$30</f>
         <v>2145</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="3" t="n">
         <f aca="false">J7*Assumptions!$B$30</f>
         <v>3575</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="3" t="n">
         <f aca="false">K7*Assumptions!$B$30</f>
         <v>5525</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="3" t="n">
         <f aca="false">L7*Assumptions!$B$30</f>
         <v>7995</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="M8" s="3" t="n">
         <f aca="false">M7*Assumptions!$B$30</f>
         <v>11180</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" s="3" t="n">
         <f aca="false">N7*Assumptions!$B$30</f>
         <v>13910</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="O8" s="3" t="n">
         <f aca="false">O7*Assumptions!$B$30</f>
         <v>15720.9</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="3" t="n">
         <f aca="false">P7*Assumptions!$B$30</f>
         <v>17513.691</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" s="3" t="n">
         <f aca="false">Q7*Assumptions!$B$30</f>
         <v>19288.55409</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="3" t="n">
         <f aca="false">R7*Assumptions!$B$30</f>
         <v>21045.6685491</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="S8" s="3" t="n">
         <f aca="false">S7*Assumptions!$B$30</f>
         <v>22785.211863609</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="T8" s="3" t="n">
         <f aca="false">T7*Assumptions!$B$30</f>
         <v>24507.3597449729</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="U8" s="3" t="n">
         <f aca="false">U7*Assumptions!$B$30</f>
         <v>26212.2861475232</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="V8" s="3" t="n">
         <f aca="false">V7*Assumptions!$B$30</f>
         <v>27900.1632860479</v>
       </c>
-      <c r="W8" s="6" t="n">
+      <c r="W8" s="3" t="n">
         <f aca="false">W7*Assumptions!$B$30</f>
         <v>29571.1616531875</v>
       </c>
-      <c r="X8" s="6" t="n">
+      <c r="X8" s="3" t="n">
         <f aca="false">X7*Assumptions!$B$30</f>
         <v>31225.4500366556</v>
       </c>
-      <c r="Y8" s="6" t="n">
+      <c r="Y8" s="3" t="n">
         <f aca="false">Y7*Assumptions!$B$30</f>
         <v>32863.195536289</v>
       </c>
-      <c r="Z8" s="6" t="n">
+      <c r="Z8" s="3" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>33930</v>
       </c>
-      <c r="AA8" s="6" t="n">
+      <c r="AA8" s="3" t="n">
         <f aca="false">SUM(N8:Y8)</f>
         <v>282543.641907385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$4</f>
         <v>100</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="3" t="n">
         <f aca="false">C7*Assumptions!$B$4</f>
         <v>300</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="3" t="n">
         <f aca="false">D7*Assumptions!$B$4</f>
         <v>500</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="3" t="n">
         <f aca="false">E7*Assumptions!$B$4</f>
         <v>700</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="3" t="n">
         <f aca="false">F7*Assumptions!$B$4</f>
         <v>900</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="3" t="n">
         <f aca="false">G7*Assumptions!$B$4</f>
         <v>1100</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="3" t="n">
         <f aca="false">H7*Assumptions!$B$4</f>
         <v>1800</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="3" t="n">
         <f aca="false">I7*Assumptions!$B$4</f>
         <v>3300</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="3" t="n">
         <f aca="false">J7*Assumptions!$B$4</f>
         <v>5500</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="3" t="n">
         <f aca="false">K7*Assumptions!$B$4</f>
         <v>8500</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="3" t="n">
         <f aca="false">L7*Assumptions!$B$4</f>
         <v>12300</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="M10" s="3" t="n">
         <f aca="false">M7*Assumptions!$B$4</f>
         <v>17200</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" s="3" t="n">
         <f aca="false">N7*Assumptions!$B$4</f>
         <v>21400</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="O10" s="3" t="n">
         <f aca="false">O7*Assumptions!$B$4</f>
         <v>24186</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="3" t="n">
         <f aca="false">P7*Assumptions!$B$4</f>
         <v>26944.14</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="3" t="n">
         <f aca="false">Q7*Assumptions!$B$4</f>
         <v>29674.6986</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="3" t="n">
         <f aca="false">R7*Assumptions!$B$4</f>
         <v>32377.951614</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="S10" s="3" t="n">
         <f aca="false">S7*Assumptions!$B$4</f>
         <v>35054.17209786</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="T10" s="3" t="n">
         <f aca="false">T7*Assumptions!$B$4</f>
         <v>37703.6303768814</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="U10" s="3" t="n">
         <f aca="false">U7*Assumptions!$B$4</f>
         <v>40326.5940731126</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="V10" s="3" t="n">
         <f aca="false">V7*Assumptions!$B$4</f>
         <v>42923.3281323815</v>
       </c>
-      <c r="W10" s="6" t="n">
+      <c r="W10" s="3" t="n">
         <f aca="false">W7*Assumptions!$B$4</f>
         <v>45494.0948510576</v>
       </c>
-      <c r="X10" s="6" t="n">
+      <c r="X10" s="3" t="n">
         <f aca="false">X7*Assumptions!$B$4</f>
         <v>48039.1539025471</v>
       </c>
-      <c r="Y10" s="6" t="n">
+      <c r="Y10" s="3" t="n">
         <f aca="false">Y7*Assumptions!$B$4</f>
         <v>50558.7623635216</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="Z10" s="3" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>52200</v>
       </c>
-      <c r="AA10" s="6" t="n">
+      <c r="AA10" s="3" t="n">
         <f aca="false">SUM(N10:Y10)</f>
         <v>434682.526011362</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
         <v>195</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="3" t="n">
         <f aca="false">C8*Assumptions!$B$5</f>
         <v>585</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <f aca="false">D8*Assumptions!$B$5</f>
         <v>975</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="3" t="n">
         <f aca="false">E8*Assumptions!$B$5</f>
         <v>1365</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="3" t="n">
         <f aca="false">F8*Assumptions!$B$5</f>
         <v>1755</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="3" t="n">
         <f aca="false">G8*Assumptions!$B$5</f>
         <v>2145</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="3" t="n">
         <f aca="false">H8*Assumptions!$B$5</f>
         <v>3510</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="3" t="n">
         <f aca="false">I8*Assumptions!$B$5</f>
         <v>6435</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="3" t="n">
         <f aca="false">J8*Assumptions!$B$5</f>
         <v>10725</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="3" t="n">
         <f aca="false">K8*Assumptions!$B$5</f>
         <v>16575</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="3" t="n">
         <f aca="false">L8*Assumptions!$B$5</f>
         <v>23985</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="3" t="n">
         <f aca="false">M8*Assumptions!$B$5</f>
         <v>33540</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="3" t="n">
         <f aca="false">N8*Assumptions!$B$5</f>
         <v>41730</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="3" t="n">
         <f aca="false">O8*Assumptions!$B$5</f>
         <v>47162.7</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="3" t="n">
         <f aca="false">P8*Assumptions!$B$5</f>
         <v>52541.073</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="3" t="n">
         <f aca="false">Q8*Assumptions!$B$5</f>
         <v>57865.66227</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="3" t="n">
         <f aca="false">R8*Assumptions!$B$5</f>
         <v>63137.0056473</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="3" t="n">
         <f aca="false">S8*Assumptions!$B$5</f>
         <v>68355.635590827</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="3" t="n">
         <f aca="false">T8*Assumptions!$B$5</f>
         <v>73522.0792349187</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="3" t="n">
         <f aca="false">U8*Assumptions!$B$5</f>
         <v>78636.8584425695</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="3" t="n">
         <f aca="false">V8*Assumptions!$B$5</f>
         <v>83700.4898581439</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="3" t="n">
         <f aca="false">W8*Assumptions!$B$5</f>
         <v>88713.4849595624</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="3" t="n">
         <f aca="false">X8*Assumptions!$B$5</f>
         <v>93676.3501099668</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="3" t="n">
         <f aca="false">Y8*Assumptions!$B$5</f>
         <v>98589.5866088671</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="Z11" s="3" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>101790</v>
       </c>
-      <c r="AA11" s="6" t="n">
+      <c r="AA11" s="3" t="n">
         <f aca="false">SUM(N11:Y11)</f>
         <v>847630.925722155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">B10+B11</f>
@@ -2362,474 +2767,474 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <f aca="false">B8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>39</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="3" t="n">
         <f aca="false">C8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>117</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="3" t="n">
         <f aca="false">D8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>195</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="3" t="n">
         <f aca="false">E8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>273</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="3" t="n">
         <f aca="false">F8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>351</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="3" t="n">
         <f aca="false">G8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>429</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="3" t="n">
         <f aca="false">H8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>702</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="3" t="n">
         <f aca="false">I8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>1287</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="3" t="n">
         <f aca="false">J8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>2145</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="3" t="n">
         <f aca="false">K8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>3315</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="3" t="n">
         <f aca="false">L8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>4797</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="3" t="n">
         <f aca="false">M8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>6708</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="3" t="n">
         <f aca="false">N8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>8346</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="3" t="n">
         <f aca="false">O8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>9432.54</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="3" t="n">
         <f aca="false">P8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>10508.2146</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="3" t="n">
         <f aca="false">Q8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>11573.132454</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="3" t="n">
         <f aca="false">R8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>12627.40112946</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="3" t="n">
         <f aca="false">S8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>13671.1271181654</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="3" t="n">
         <f aca="false">T8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>14704.4158469837</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="3" t="n">
         <f aca="false">U8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>15727.3716885139</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="3" t="n">
         <f aca="false">V8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>16740.0979716288</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="3" t="n">
         <f aca="false">W8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>17742.6969919125</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="3" t="n">
         <f aca="false">X8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>18735.2700219934</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="3" t="n">
         <f aca="false">Y8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
         <v>19717.9173217734</v>
       </c>
-      <c r="Z14" s="6" t="n">
+      <c r="Z14" s="3" t="n">
         <f aca="false">SUM(B14:M14)</f>
         <v>20358</v>
       </c>
-      <c r="AA14" s="6" t="n">
+      <c r="AA14" s="3" t="n">
         <f aca="false">SUM(N14:Y14)</f>
         <v>169526.185144431</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$15</f>
         <v>6</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="3" t="n">
         <f aca="false">C7*Assumptions!$B$15</f>
         <v>18</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <f aca="false">D7*Assumptions!$B$15</f>
         <v>30</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="3" t="n">
         <f aca="false">E7*Assumptions!$B$15</f>
         <v>42</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="3" t="n">
         <f aca="false">F7*Assumptions!$B$15</f>
         <v>54</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="3" t="n">
         <f aca="false">G7*Assumptions!$B$15</f>
         <v>66</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="3" t="n">
         <f aca="false">H7*Assumptions!$B$15</f>
         <v>108</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="3" t="n">
         <f aca="false">I7*Assumptions!$B$15</f>
         <v>198</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="3" t="n">
         <f aca="false">J7*Assumptions!$B$15</f>
         <v>330</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="3" t="n">
         <f aca="false">K7*Assumptions!$B$15</f>
         <v>510</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="3" t="n">
         <f aca="false">L7*Assumptions!$B$15</f>
         <v>738</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="3" t="n">
         <f aca="false">M7*Assumptions!$B$15</f>
         <v>1032</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="3" t="n">
         <f aca="false">N7*Assumptions!$B$15</f>
         <v>1284</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="3" t="n">
         <f aca="false">O7*Assumptions!$B$15</f>
         <v>1451.16</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="3" t="n">
         <f aca="false">P7*Assumptions!$B$15</f>
         <v>1616.6484</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="3" t="n">
         <f aca="false">Q7*Assumptions!$B$15</f>
         <v>1780.481916</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="3" t="n">
         <f aca="false">R7*Assumptions!$B$15</f>
         <v>1942.67709684</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="3" t="n">
         <f aca="false">S7*Assumptions!$B$15</f>
         <v>2103.2503258716</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="3" t="n">
         <f aca="false">T7*Assumptions!$B$15</f>
         <v>2262.21782261288</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="3" t="n">
         <f aca="false">U7*Assumptions!$B$15</f>
         <v>2419.59564438676</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" s="3" t="n">
         <f aca="false">V7*Assumptions!$B$15</f>
         <v>2575.39968794289</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="3" t="n">
         <f aca="false">W7*Assumptions!$B$15</f>
         <v>2729.64569106346</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="3" t="n">
         <f aca="false">X7*Assumptions!$B$15</f>
         <v>2882.34923415282</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="3" t="n">
         <f aca="false">Y7*Assumptions!$B$15</f>
         <v>3033.5257418113</v>
       </c>
-      <c r="Z15" s="6" t="n">
+      <c r="Z15" s="3" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>3132</v>
       </c>
-      <c r="AA15" s="6" t="n">
+      <c r="AA15" s="3" t="n">
         <f aca="false">SUM(N15:Y15)</f>
         <v>26080.9515606817</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B16" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$17</f>
         <v>1</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="3" t="n">
         <f aca="false">C7*Assumptions!$B$17</f>
         <v>3</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="3" t="n">
         <f aca="false">D7*Assumptions!$B$17</f>
         <v>5</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="3" t="n">
         <f aca="false">E7*Assumptions!$B$17</f>
         <v>7</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="3" t="n">
         <f aca="false">F7*Assumptions!$B$17</f>
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="3" t="n">
         <f aca="false">G7*Assumptions!$B$17</f>
         <v>11</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="3" t="n">
         <f aca="false">H7*Assumptions!$B$17</f>
         <v>18</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="3" t="n">
         <f aca="false">I7*Assumptions!$B$17</f>
         <v>33</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="3" t="n">
         <f aca="false">J7*Assumptions!$B$17</f>
         <v>55</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="3" t="n">
         <f aca="false">K7*Assumptions!$B$17</f>
         <v>85</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="3" t="n">
         <f aca="false">L7*Assumptions!$B$17</f>
         <v>123</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="3" t="n">
         <f aca="false">M7*Assumptions!$B$17</f>
         <v>172</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="3" t="n">
         <f aca="false">N7*Assumptions!$B$17</f>
         <v>214</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="3" t="n">
         <f aca="false">O7*Assumptions!$B$17</f>
         <v>241.86</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="3" t="n">
         <f aca="false">P7*Assumptions!$B$17</f>
         <v>269.4414</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="3" t="n">
         <f aca="false">Q7*Assumptions!$B$17</f>
         <v>296.746986</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="3" t="n">
         <f aca="false">R7*Assumptions!$B$17</f>
         <v>323.77951614</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="3" t="n">
         <f aca="false">S7*Assumptions!$B$17</f>
         <v>350.5417209786</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="3" t="n">
         <f aca="false">T7*Assumptions!$B$17</f>
         <v>377.036303768814</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="3" t="n">
         <f aca="false">U7*Assumptions!$B$17</f>
         <v>403.265940731126</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="3" t="n">
         <f aca="false">V7*Assumptions!$B$17</f>
         <v>429.233281323815</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="3" t="n">
         <f aca="false">W7*Assumptions!$B$17</f>
         <v>454.940948510576</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="3" t="n">
         <f aca="false">X7*Assumptions!$B$17</f>
         <v>480.391539025471</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="3" t="n">
         <f aca="false">Y7*Assumptions!$B$17</f>
         <v>505.587623635216</v>
       </c>
-      <c r="Z16" s="6" t="n">
+      <c r="Z16" s="3" t="n">
         <f aca="false">SUM(B16:M16)</f>
         <v>522</v>
       </c>
-      <c r="AA16" s="6" t="n">
+      <c r="AA16" s="3" t="n">
         <f aca="false">SUM(N16:Y16)</f>
         <v>4346.82526011362</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B17" s="3" t="n">
         <f aca="false">B14+B15+B16</f>
         <v>46</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="3" t="n">
         <f aca="false">C14+C15+C16</f>
         <v>138</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <f aca="false">D14+D15+D16</f>
         <v>230</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="3" t="n">
         <f aca="false">E14+E15+E16</f>
         <v>322</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="3" t="n">
         <f aca="false">F14+F15+F16</f>
         <v>414</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="3" t="n">
         <f aca="false">G14+G15+G16</f>
         <v>506</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="3" t="n">
         <f aca="false">H14+H15+H16</f>
         <v>828</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="3" t="n">
         <f aca="false">I14+I15+I16</f>
         <v>1518</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="3" t="n">
         <f aca="false">J14+J15+J16</f>
         <v>2530</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="3" t="n">
         <f aca="false">K14+K15+K16</f>
         <v>3910</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="3" t="n">
         <f aca="false">L14+L15+L16</f>
         <v>5658</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="3" t="n">
         <f aca="false">M14+M15+M16</f>
         <v>7912</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="3" t="n">
         <f aca="false">N14+N15+N16</f>
         <v>9844</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="O17" s="3" t="n">
         <f aca="false">O14+O15+O16</f>
         <v>11125.56</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="3" t="n">
         <f aca="false">P14+P15+P16</f>
         <v>12394.3044</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="3" t="n">
         <f aca="false">Q14+Q15+Q16</f>
         <v>13650.361356</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="3" t="n">
         <f aca="false">R14+R15+R16</f>
         <v>14893.85774244</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="3" t="n">
         <f aca="false">S14+S15+S16</f>
         <v>16124.9191650156</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="3" t="n">
         <f aca="false">T14+T15+T16</f>
         <v>17343.6699733654</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="3" t="n">
         <f aca="false">U14+U15+U16</f>
         <v>18550.2332736318</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="3" t="n">
         <f aca="false">V14+V15+V16</f>
         <v>19744.7309408955</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="3" t="n">
         <f aca="false">W14+W15+W16</f>
         <v>20927.2836314865</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="3" t="n">
         <f aca="false">X14+X15+X16</f>
         <v>22098.0107951717</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="3" t="n">
         <f aca="false">Y14+Y15+Y16</f>
         <v>23257.0306872199</v>
       </c>
-      <c r="Z17" s="6" t="n">
+      <c r="Z17" s="3" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>24012</v>
       </c>
-      <c r="AA17" s="6" t="n">
+      <c r="AA17" s="3" t="n">
         <f aca="false">SUM(N17:Y17)</f>
         <v>199953.961965226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B18" s="7" t="n">
         <f aca="false">B12-B17</f>
@@ -2938,7 +3343,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">B18/B12</f>
@@ -3047,910 +3452,910 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
+        <v>106</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B21" s="3" t="n">
         <f aca="false">B3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="3" t="n">
         <f aca="false">C3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <f aca="false">D3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="3" t="n">
         <f aca="false">E3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="3" t="n">
         <f aca="false">F3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="3" t="n">
         <f aca="false">G3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>400</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="3" t="n">
         <f aca="false">H3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>2400</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="3" t="n">
         <f aca="false">I3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>3600</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="3" t="n">
         <f aca="false">J3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>5200</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="3" t="n">
         <f aca="false">K3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6800</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="3" t="n">
         <f aca="false">L3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>8400</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="3" t="n">
         <f aca="false">M3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>11200</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="3" t="n">
         <f aca="false">N3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="3" t="n">
         <f aca="false">O3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="3" t="n">
         <f aca="false">P3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="3" t="n">
         <f aca="false">Q3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="3" t="n">
         <f aca="false">R3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="3" t="n">
         <f aca="false">S3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="3" t="n">
         <f aca="false">T3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="3" t="n">
         <f aca="false">U3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="3" t="n">
         <f aca="false">V3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="3" t="n">
         <f aca="false">W3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="3" t="n">
         <f aca="false">X3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="3" t="n">
         <f aca="false">Y3*(Assumptions!$B$19+Assumptions!$B$20)</f>
         <v>6000</v>
       </c>
-      <c r="Z21" s="6" t="n">
+      <c r="Z21" s="3" t="n">
         <f aca="false">SUM(B21:M21)</f>
         <v>40000</v>
       </c>
-      <c r="AA21" s="6" t="n">
+      <c r="AA21" s="3" t="n">
         <f aca="false">SUM(N21:Y21)</f>
         <v>72000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B22" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$16</f>
         <v>5</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="3" t="n">
         <f aca="false">C7*Assumptions!$B$16</f>
         <v>15</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="3" t="n">
         <f aca="false">D7*Assumptions!$B$16</f>
         <v>25</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="3" t="n">
         <f aca="false">E7*Assumptions!$B$16</f>
         <v>35</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="3" t="n">
         <f aca="false">F7*Assumptions!$B$16</f>
         <v>45</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="3" t="n">
         <f aca="false">G7*Assumptions!$B$16</f>
         <v>55</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="3" t="n">
         <f aca="false">H7*Assumptions!$B$16</f>
         <v>90</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="3" t="n">
         <f aca="false">I7*Assumptions!$B$16</f>
         <v>165</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="3" t="n">
         <f aca="false">J7*Assumptions!$B$16</f>
         <v>275</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="3" t="n">
         <f aca="false">K7*Assumptions!$B$16</f>
         <v>425</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="3" t="n">
         <f aca="false">L7*Assumptions!$B$16</f>
         <v>615</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="3" t="n">
         <f aca="false">M7*Assumptions!$B$16</f>
         <v>860</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="3" t="n">
         <f aca="false">N7*Assumptions!$B$16</f>
         <v>1070</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="3" t="n">
         <f aca="false">O7*Assumptions!$B$16</f>
         <v>1209.3</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="3" t="n">
         <f aca="false">P7*Assumptions!$B$16</f>
         <v>1347.207</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="3" t="n">
         <f aca="false">Q7*Assumptions!$B$16</f>
         <v>1483.73493</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="3" t="n">
         <f aca="false">R7*Assumptions!$B$16</f>
         <v>1618.8975807</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="3" t="n">
         <f aca="false">S7*Assumptions!$B$16</f>
         <v>1752.708604893</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="3" t="n">
         <f aca="false">T7*Assumptions!$B$16</f>
         <v>1885.18151884407</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="3" t="n">
         <f aca="false">U7*Assumptions!$B$16</f>
         <v>2016.32970365563</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="3" t="n">
         <f aca="false">V7*Assumptions!$B$16</f>
         <v>2146.16640661907</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="3" t="n">
         <f aca="false">W7*Assumptions!$B$16</f>
         <v>2274.70474255288</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="3" t="n">
         <f aca="false">X7*Assumptions!$B$16</f>
         <v>2401.95769512735</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="3" t="n">
         <f aca="false">Y7*Assumptions!$B$16</f>
         <v>2527.93811817608</v>
       </c>
-      <c r="Z22" s="6" t="n">
+      <c r="Z22" s="3" t="n">
         <f aca="false">SUM(B22:M22)</f>
         <v>2610</v>
       </c>
-      <c r="AA22" s="6" t="n">
+      <c r="AA22" s="3" t="n">
         <f aca="false">SUM(N22:Y22)</f>
         <v>21734.1263005681</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B23" s="3" t="n">
         <f aca="false">IF(Assumptions!B33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!B33&gt;=Assumptions!$B$22,B5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="3" t="n">
         <f aca="false">IF(Assumptions!C33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!C33&gt;=Assumptions!$B$22,C5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <f aca="false">IF(Assumptions!D33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!D33&gt;=Assumptions!$B$22,D5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="3" t="n">
         <f aca="false">IF(Assumptions!E33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!E33&gt;=Assumptions!$B$22,E5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="3" t="n">
         <f aca="false">IF(Assumptions!F33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!F33&gt;=Assumptions!$B$22,F5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="3" t="n">
         <f aca="false">IF(Assumptions!G33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!G33&gt;=Assumptions!$B$22,G5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="3" t="n">
         <f aca="false">IF(Assumptions!H33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!H33&gt;=Assumptions!$B$22,H5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="3" t="n">
         <f aca="false">IF(Assumptions!I33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!I33&gt;=Assumptions!$B$22,I5&gt;=Assumptions!$B$23),1,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="3" t="n">
         <f aca="false">IF(Assumptions!J33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!J33&gt;=Assumptions!$B$22,J5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="3" t="n">
         <f aca="false">IF(Assumptions!K33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!K33&gt;=Assumptions!$B$22,K5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="3" t="n">
         <f aca="false">IF(Assumptions!L33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!L33&gt;=Assumptions!$B$22,L5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="3" t="n">
         <f aca="false">IF(Assumptions!M33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!M33&gt;=Assumptions!$B$22,M5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="3" t="n">
         <f aca="false">IF(Assumptions!N33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!N33&gt;=Assumptions!$B$22,N5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="3" t="n">
         <f aca="false">IF(Assumptions!O33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!O33&gt;=Assumptions!$B$22,O5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="3" t="n">
         <f aca="false">IF(Assumptions!P33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!P33&gt;=Assumptions!$B$22,P5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="3" t="n">
         <f aca="false">IF(Assumptions!Q33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Q33&gt;=Assumptions!$B$22,Q5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="3" t="n">
         <f aca="false">IF(Assumptions!R33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!R33&gt;=Assumptions!$B$22,R5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="3" t="n">
         <f aca="false">IF(Assumptions!S33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!S33&gt;=Assumptions!$B$22,S5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="3" t="n">
         <f aca="false">IF(Assumptions!T33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!T33&gt;=Assumptions!$B$22,T5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="3" t="n">
         <f aca="false">IF(Assumptions!U33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!U33&gt;=Assumptions!$B$22,U5&gt;=Assumptions!$B$23),1,0)</f>
         <v>1</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="3" t="n">
         <f aca="false">IF(Assumptions!V33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!V33&gt;=Assumptions!$B$22,V5&gt;=Assumptions!$B$23),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="3" t="n">
         <f aca="false">IF(Assumptions!W33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!W33&gt;=Assumptions!$B$22,W5&gt;=Assumptions!$B$23),1,0)</f>
         <v>2</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="3" t="n">
         <f aca="false">IF(Assumptions!X33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!X33&gt;=Assumptions!$B$22,X5&gt;=Assumptions!$B$23),1,0)</f>
         <v>2</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="3" t="n">
         <f aca="false">IF(Assumptions!Y33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Y33&gt;=Assumptions!$B$22,Y5&gt;=Assumptions!$B$23),1,0)</f>
         <v>2</v>
       </c>
-      <c r="Z23" s="6" t="n">
+      <c r="Z23" s="3" t="n">
         <f aca="false">M23</f>
         <v>1</v>
       </c>
-      <c r="AA23" s="6" t="n">
+      <c r="AA23" s="3" t="n">
         <f aca="false">Y23</f>
         <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B24" s="3" t="n">
         <f aca="false">B23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="3" t="n">
         <f aca="false">C23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="3" t="n">
         <f aca="false">D23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="3" t="n">
         <f aca="false">E23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="3" t="n">
         <f aca="false">F23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="3" t="n">
         <f aca="false">G23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="3" t="n">
         <f aca="false">H23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="3" t="n">
         <f aca="false">I23*Assumptions!$B$21</f>
         <v>0</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="3" t="n">
         <f aca="false">J23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" s="3" t="n">
         <f aca="false">K23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="3" t="n">
         <f aca="false">L23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M24" s="3" t="n">
         <f aca="false">M23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="3" t="n">
         <f aca="false">N23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="3" t="n">
         <f aca="false">O23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="3" t="n">
         <f aca="false">P23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="3" t="n">
         <f aca="false">Q23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="3" t="n">
         <f aca="false">R23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="3" t="n">
         <f aca="false">S23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="3" t="n">
         <f aca="false">T23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="3" t="n">
         <f aca="false">U23*Assumptions!$B$21</f>
         <v>9000</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="V24" s="3" t="n">
         <f aca="false">V23*Assumptions!$B$21</f>
         <v>18000</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="3" t="n">
         <f aca="false">W23*Assumptions!$B$21</f>
         <v>18000</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="3" t="n">
         <f aca="false">X23*Assumptions!$B$21</f>
         <v>18000</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="3" t="n">
         <f aca="false">Y23*Assumptions!$B$21</f>
         <v>18000</v>
       </c>
-      <c r="Z24" s="6" t="n">
+      <c r="Z24" s="3" t="n">
         <f aca="false">SUM(B24:M24)</f>
         <v>36000</v>
       </c>
-      <c r="AA24" s="6" t="n">
+      <c r="AA24" s="3" t="n">
         <f aca="false">SUM(N24:Y24)</f>
         <v>144000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="3" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>150</v>
       </c>
-      <c r="Z25" s="6" t="n">
+      <c r="Z25" s="3" t="n">
         <f aca="false">SUM(B25:M25)</f>
         <v>1800</v>
       </c>
-      <c r="AA25" s="6" t="n">
+      <c r="AA25" s="3" t="n">
         <f aca="false">SUM(N25:Y25)</f>
         <v>1800</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="M26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="V26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="3" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>500</v>
       </c>
-      <c r="Z26" s="6" t="n">
+      <c r="Z26" s="3" t="n">
         <f aca="false">SUM(B26:M26)</f>
         <v>6000</v>
       </c>
-      <c r="AA26" s="6" t="n">
+      <c r="AA26" s="3" t="n">
         <f aca="false">SUM(N26:Y26)</f>
         <v>6000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="V27" s="6" t="n">
+      <c r="V27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="3" t="n">
         <f aca="false">Assumptions!$B$26</f>
         <v>1200</v>
       </c>
-      <c r="Z27" s="6" t="n">
+      <c r="Z27" s="3" t="n">
         <f aca="false">SUM(B27:M27)</f>
         <v>14400</v>
       </c>
-      <c r="AA27" s="6" t="n">
+      <c r="AA27" s="3" t="n">
         <f aca="false">SUM(N27:Y27)</f>
         <v>14400</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="V28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="3" t="n">
         <f aca="false">Assumptions!$B$27</f>
         <v>7500</v>
       </c>
-      <c r="Z28" s="6" t="n">
+      <c r="Z28" s="3" t="n">
         <f aca="false">SUM(B28:M28)</f>
         <v>90000</v>
       </c>
-      <c r="AA28" s="6" t="n">
+      <c r="AA28" s="3" t="n">
         <f aca="false">SUM(N28:Y28)</f>
         <v>90000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="B29" s="7" t="n">
         <f aca="false">SUM(B21:B28)</f>
@@ -4059,7 +4464,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B30" s="7" t="n">
         <f aca="false">B18-B29</f>
@@ -4168,116 +4573,116 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:B30))-0)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:C30))-SUM($B31:B31))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:D30))-SUM($B31:C31))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:E30))-SUM($B31:D31))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:F30))-SUM($B31:E31))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:G30))-SUM($B31:F31))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:H30))-SUM($B31:G31))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:I30))-SUM($B31:H31))</f>
         <v>0</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:J30))-SUM($B31:I31))</f>
         <v>0</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:K30))-SUM($B31:J31))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:L30))-SUM($B31:K31))</f>
         <v>0</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="M31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:M30))-SUM($B31:L31))</f>
         <v>0</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:N30))-SUM($B31:M31))</f>
         <v>0</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:O30))-SUM($B31:N31))</f>
         <v>422.960000000003</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:P30))-SUM($B31:O31))</f>
         <v>10348.1754</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Q30))-SUM($B31:P31))</f>
         <v>12013.816146</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:R30))-SUM($B31:Q31))</f>
         <v>13662.80048454</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:S30))-SUM($B31:R31))</f>
         <v>15295.2949796946</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:T30))-SUM($B31:S31))</f>
         <v>16911.4645298977</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:U30))-SUM($B31:T31))</f>
         <v>18511.4723845987</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="V31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:V30))-SUM($B31:U31))</f>
         <v>17845.2301607527</v>
       </c>
-      <c r="W31" s="6" t="n">
+      <c r="W31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:W30))-SUM($B31:V31))</f>
         <v>19413.3978591452</v>
       </c>
-      <c r="X31" s="6" t="n">
+      <c r="X31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:X30))-SUM($B31:W31))</f>
         <v>20965.8838805537</v>
       </c>
-      <c r="Y31" s="6" t="n">
+      <c r="Y31" s="3" t="n">
         <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Y30))-SUM($B31:X31))</f>
         <v>22502.8450417482</v>
       </c>
-      <c r="Z31" s="6" t="n">
+      <c r="Z31" s="3" t="n">
         <f aca="false">SUM(B31:M31)</f>
         <v>0</v>
       </c>
-      <c r="AA31" s="6" t="n">
+      <c r="AA31" s="3" t="n">
         <f aca="false">SUM(N31:Y31)</f>
         <v>167893.340866931</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">B30-B31</f>
@@ -4386,111 +4791,3360 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="3" t="n">
         <f aca="false">SUM($B32:B32)</f>
         <v>-9506</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C33" s="3" t="n">
         <f aca="false">SUM($B32:C32)</f>
         <v>-18524</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <f aca="false">SUM($B32:D32)</f>
         <v>-27054</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="3" t="n">
         <f aca="false">SUM($B32:E32)</f>
         <v>-35096</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="3" t="n">
         <f aca="false">SUM($B32:F32)</f>
         <v>-42650</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="3" t="n">
         <f aca="false">SUM($B32:G32)</f>
         <v>-49716</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="3" t="n">
         <f aca="false">SUM($B32:H32)</f>
         <v>-57074</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="3" t="n">
         <f aca="false">SUM($B32:I32)</f>
         <v>-61972</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="3" t="n">
         <f aca="false">SUM($B32:J32)</f>
         <v>-72103</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" s="3" t="n">
         <f aca="false">SUM($B32:K32)</f>
         <v>-76514</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" s="3" t="n">
         <f aca="false">SUM($B32:L32)</f>
         <v>-73253</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="M33" s="3" t="n">
         <f aca="false">SUM($B32:M32)</f>
         <v>-60836</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="3" t="n">
         <f aca="false">SUM($B32:N32)</f>
         <v>-32971</v>
       </c>
-      <c r="O33" s="6" t="n">
+      <c r="O33" s="3" t="n">
         <f aca="false">SUM($B32:O32)</f>
         <v>1268.88</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="3" t="n">
         <f aca="false">SUM($B32:P32)</f>
         <v>32313.4062</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" s="3" t="n">
         <f aca="false">SUM($B32:Q32)</f>
         <v>68354.854638</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" s="3" t="n">
         <f aca="false">SUM($B32:R32)</f>
         <v>109343.25609162</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="S33" s="3" t="n">
         <f aca="false">SUM($B32:S32)</f>
         <v>155229.141030704</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" s="3" t="n">
         <f aca="false">SUM($B32:T32)</f>
         <v>205963.534620397</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="U33" s="3" t="n">
         <f aca="false">SUM($B32:U32)</f>
         <v>261497.951774193</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="V33" s="3" t="n">
         <f aca="false">SUM($B32:V32)</f>
         <v>315033.642256451</v>
       </c>
-      <c r="W33" s="6" t="n">
+      <c r="W33" s="3" t="n">
         <f aca="false">SUM($B32:W32)</f>
         <v>373273.835833886</v>
       </c>
-      <c r="X33" s="6" t="n">
+      <c r="X33" s="3" t="n">
         <f aca="false">SUM($B32:X32)</f>
         <v>436171.487475548</v>
       </c>
-      <c r="Y33" s="6" t="n">
+      <c r="Y33" s="3" t="n">
         <f aca="false">SUM($B32:Y32)</f>
         <v>503680.022600792</v>
       </c>
-      <c r="Z33" s="6" t="n">
+      <c r="Z33" s="3" t="n">
         <f aca="false">M33</f>
         <v>-60836</v>
       </c>
-      <c r="AA33" s="6" t="n">
+      <c r="AA33" s="3" t="n">
         <f aca="false">Y33</f>
         <v>503680.022600792</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AA33"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="2" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <f aca="false">Assumptions!B37</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">Assumptions!C37</f>
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <f aca="false">Assumptions!D37</f>
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <f aca="false">Assumptions!E37</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <f aca="false">Assumptions!F37</f>
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <f aca="false">Assumptions!G37</f>
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <f aca="false">Assumptions!H37</f>
+        <v>12</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <f aca="false">Assumptions!I37</f>
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <f aca="false">Assumptions!J37</f>
+        <v>26</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <f aca="false">Assumptions!K37</f>
+        <v>34</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <f aca="false">Assumptions!L37</f>
+        <v>42</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <f aca="false">Assumptions!M37</f>
+        <v>56</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <f aca="false">Assumptions!N37</f>
+        <v>10</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <f aca="false">Assumptions!O37</f>
+        <v>10</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <f aca="false">Assumptions!P37</f>
+        <v>10</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <f aca="false">Assumptions!Q37</f>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <f aca="false">Assumptions!R37</f>
+        <v>10</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <f aca="false">Assumptions!S37</f>
+        <v>10</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <f aca="false">Assumptions!T37</f>
+        <v>10</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <f aca="false">Assumptions!U37</f>
+        <v>10</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <f aca="false">Assumptions!V37</f>
+        <v>10</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <f aca="false">Assumptions!W37</f>
+        <v>10</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <f aca="false">Assumptions!X37</f>
+        <v>10</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <f aca="false">Assumptions!Y37</f>
+        <v>10</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <f aca="false">SUM(B3:M3)</f>
+        <v>200</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <f aca="false">SUM(N3:Y3)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <f aca="false">B5*Assumptions!B38</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">C5*Assumptions!C38</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <f aca="false">D5*Assumptions!D38</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <f aca="false">E5*Assumptions!E38</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <f aca="false">F5*Assumptions!F38</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <f aca="false">G5*Assumptions!G38</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <f aca="false">H5*Assumptions!H38</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <f aca="false">I5*Assumptions!I38</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <f aca="false">J5*Assumptions!J38</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <f aca="false">K5*Assumptions!K38</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <f aca="false">L5*Assumptions!L38</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <f aca="false">M5*Assumptions!M38</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <f aca="false">N5*Assumptions!N38</f>
+        <v>2</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <f aca="false">O5*Assumptions!O38</f>
+        <v>2.08</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <f aca="false">P5*Assumptions!P38</f>
+        <v>2.1592</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <f aca="false">Q5*Assumptions!Q38</f>
+        <v>2.237608</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <f aca="false">R5*Assumptions!R38</f>
+        <v>2.31523192</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <f aca="false">S5*Assumptions!S38</f>
+        <v>2.3920796008</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <f aca="false">T5*Assumptions!T38</f>
+        <v>2.468158804792</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <f aca="false">U5*Assumptions!U38</f>
+        <v>2.54347721674408</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <f aca="false">V5*Assumptions!V38</f>
+        <v>2.61804244457664</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <f aca="false">W5*Assumptions!W38</f>
+        <v>2.69186202013087</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <f aca="false">X5*Assumptions!X38</f>
+        <v>2.76494339992956</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <f aca="false">Y5*Assumptions!Y38</f>
+        <v>2.83729396593027</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <f aca="false">SUM(B4:M4)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <f aca="false">SUM(N4:Y4)</f>
+        <v>29.1078973729034</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">B6</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <f aca="false">C6</f>
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <f aca="false">D6</f>
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <f aca="false">E6</f>
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <f aca="false">F6</f>
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <f aca="false">G6</f>
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <f aca="false">H6</f>
+        <v>24</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <f aca="false">I6</f>
+        <v>42</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <f aca="false">J6</f>
+        <v>68</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <f aca="false">K6</f>
+        <v>102</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <f aca="false">L6</f>
+        <v>144</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <f aca="false">M6</f>
+        <v>200</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <f aca="false">N6</f>
+        <v>208</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <f aca="false">O6</f>
+        <v>215.92</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <f aca="false">P6</f>
+        <v>223.7608</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <f aca="false">Q6</f>
+        <v>231.523192</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <f aca="false">R6</f>
+        <v>239.20796008</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <f aca="false">S6</f>
+        <v>246.8158804792</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <f aca="false">T6</f>
+        <v>254.347721674408</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <f aca="false">U6</f>
+        <v>261.804244457664</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <f aca="false">V6</f>
+        <v>269.186202013087</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <f aca="false">W6</f>
+        <v>276.494339992956</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <f aca="false">X6</f>
+        <v>283.729396593027</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <f aca="false">B5</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <f aca="false">N5</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <f aca="false">B5+B3-B4</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">C5+C3-C4</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <f aca="false">D5+D3-D4</f>
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <f aca="false">E5+E3-E4</f>
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <f aca="false">F5+F3-F4</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <f aca="false">G5+G3-G4</f>
+        <v>12</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <f aca="false">H5+H3-H4</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <f aca="false">I5+I3-I4</f>
+        <v>42</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <f aca="false">J5+J3-J4</f>
+        <v>68</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <f aca="false">K5+K3-K4</f>
+        <v>102</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <f aca="false">L5+L3-L4</f>
+        <v>144</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <f aca="false">M5+M3-M4</f>
+        <v>200</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <f aca="false">N5+N3-N4</f>
+        <v>208</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <f aca="false">O5+O3-O4</f>
+        <v>215.92</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <f aca="false">P5+P3-P4</f>
+        <v>223.7608</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <f aca="false">Q5+Q3-Q4</f>
+        <v>231.523192</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <f aca="false">R5+R3-R4</f>
+        <v>239.20796008</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <f aca="false">S5+S3-S4</f>
+        <v>246.8158804792</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <f aca="false">T5+T3-T4</f>
+        <v>254.347721674408</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <f aca="false">U5+U3-U4</f>
+        <v>261.804244457664</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <f aca="false">V5+V3-V4</f>
+        <v>269.186202013087</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <f aca="false">W5+W3-W4</f>
+        <v>276.494339992956</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <f aca="false">X5+X3-X4</f>
+        <v>283.729396593027</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <f aca="false">Y5+Y3-Y4</f>
+        <v>290.892102627097</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <f aca="false">M6</f>
+        <v>200</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <f aca="false">Y6</f>
+        <v>290.892102627097</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <f aca="false">(B5+B6)/2</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <f aca="false">(C5+C6)/2</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <f aca="false">(D5+D6)/2</f>
+        <v>5</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <f aca="false">(E5+E6)/2</f>
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <f aca="false">(F5+F6)/2</f>
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">(G5+G6)/2</f>
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <f aca="false">(H5+H6)/2</f>
+        <v>18</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <f aca="false">(I5+I6)/2</f>
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <f aca="false">(J5+J6)/2</f>
+        <v>55</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <f aca="false">(K5+K6)/2</f>
+        <v>85</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <f aca="false">(L5+L6)/2</f>
+        <v>123</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <f aca="false">(M5+M6)/2</f>
+        <v>172</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <f aca="false">(N5+N6)/2</f>
+        <v>204</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <f aca="false">(O5+O6)/2</f>
+        <v>211.96</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <f aca="false">(P5+P6)/2</f>
+        <v>219.8404</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <f aca="false">(Q5+Q6)/2</f>
+        <v>227.641996</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <f aca="false">(R5+R6)/2</f>
+        <v>235.36557604</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <f aca="false">(S5+S6)/2</f>
+        <v>243.0119202796</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <f aca="false">(T5+T6)/2</f>
+        <v>250.581801076804</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <f aca="false">(U5+U6)/2</f>
+        <v>258.075983066036</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <f aca="false">(V5+V6)/2</f>
+        <v>265.495223235376</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <f aca="false">(W5+W6)/2</f>
+        <v>272.840271003022</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <f aca="false">(X5+X6)/2</f>
+        <v>280.111868292992</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <f aca="false">(Y5+Y6)/2</f>
+        <v>287.310749610062</v>
+      </c>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <f aca="false">B7*Assumptions!$B$30</f>
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <f aca="false">C7*Assumptions!$B$30</f>
+        <v>195</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <f aca="false">D7*Assumptions!$B$30</f>
+        <v>325</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <f aca="false">E7*Assumptions!$B$30</f>
+        <v>455</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <f aca="false">F7*Assumptions!$B$30</f>
+        <v>585</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <f aca="false">G7*Assumptions!$B$30</f>
+        <v>715</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <f aca="false">H7*Assumptions!$B$30</f>
+        <v>1170</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <f aca="false">I7*Assumptions!$B$30</f>
+        <v>2145</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <f aca="false">J7*Assumptions!$B$30</f>
+        <v>3575</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <f aca="false">K7*Assumptions!$B$30</f>
+        <v>5525</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <f aca="false">L7*Assumptions!$B$30</f>
+        <v>7995</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <f aca="false">M7*Assumptions!$B$30</f>
+        <v>11180</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <f aca="false">N7*Assumptions!$B$30</f>
+        <v>13260</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <f aca="false">O7*Assumptions!$B$30</f>
+        <v>13777.4</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <f aca="false">P7*Assumptions!$B$30</f>
+        <v>14289.626</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <f aca="false">Q7*Assumptions!$B$30</f>
+        <v>14796.72974</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <f aca="false">R7*Assumptions!$B$30</f>
+        <v>15298.7624426</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <f aca="false">S7*Assumptions!$B$30</f>
+        <v>15795.774818174</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <f aca="false">T7*Assumptions!$B$30</f>
+        <v>16287.8170699923</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <f aca="false">U7*Assumptions!$B$30</f>
+        <v>16774.9388992923</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <f aca="false">V7*Assumptions!$B$30</f>
+        <v>17257.1895102994</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <f aca="false">W7*Assumptions!$B$30</f>
+        <v>17734.6176151964</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <f aca="false">X7*Assumptions!$B$30</f>
+        <v>18207.2714390445</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <f aca="false">Y7*Assumptions!$B$30</f>
+        <v>18675.198724654</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <f aca="false">SUM(B8:M8)</f>
+        <v>33930</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <f aca="false">SUM(N8:Y8)</f>
+        <v>192155.326259253</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <f aca="false">B7*Assumptions!$B$4</f>
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">C7*Assumptions!$B$4</f>
+        <v>300</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <f aca="false">D7*Assumptions!$B$4</f>
+        <v>500</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <f aca="false">E7*Assumptions!$B$4</f>
+        <v>700</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <f aca="false">F7*Assumptions!$B$4</f>
+        <v>900</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <f aca="false">G7*Assumptions!$B$4</f>
+        <v>1100</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <f aca="false">H7*Assumptions!$B$4</f>
+        <v>1800</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <f aca="false">I7*Assumptions!$B$4</f>
+        <v>3300</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <f aca="false">J7*Assumptions!$B$4</f>
+        <v>5500</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <f aca="false">K7*Assumptions!$B$4</f>
+        <v>8500</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <f aca="false">L7*Assumptions!$B$4</f>
+        <v>12300</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <f aca="false">M7*Assumptions!$B$4</f>
+        <v>17200</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <f aca="false">N7*Assumptions!$B$4</f>
+        <v>20400</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <f aca="false">O7*Assumptions!$B$4</f>
+        <v>21196</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <f aca="false">P7*Assumptions!$B$4</f>
+        <v>21984.04</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <f aca="false">Q7*Assumptions!$B$4</f>
+        <v>22764.1996</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <f aca="false">R7*Assumptions!$B$4</f>
+        <v>23536.557604</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <f aca="false">S7*Assumptions!$B$4</f>
+        <v>24301.19202796</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <f aca="false">T7*Assumptions!$B$4</f>
+        <v>25058.1801076804</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <f aca="false">U7*Assumptions!$B$4</f>
+        <v>25807.5983066036</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <f aca="false">V7*Assumptions!$B$4</f>
+        <v>26549.5223235376</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <f aca="false">W7*Assumptions!$B$4</f>
+        <v>27284.0271003022</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <f aca="false">X7*Assumptions!$B$4</f>
+        <v>28011.1868292992</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <f aca="false">Y7*Assumptions!$B$4</f>
+        <v>28731.0749610062</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <f aca="false">SUM(B10:M10)</f>
+        <v>52200</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <f aca="false">SUM(N10:Y10)</f>
+        <v>295623.578860389</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <f aca="false">B8*Assumptions!$B$5</f>
+        <v>195</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <f aca="false">C8*Assumptions!$B$5</f>
+        <v>585</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <f aca="false">D8*Assumptions!$B$5</f>
+        <v>975</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <f aca="false">E8*Assumptions!$B$5</f>
+        <v>1365</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <f aca="false">F8*Assumptions!$B$5</f>
+        <v>1755</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <f aca="false">G8*Assumptions!$B$5</f>
+        <v>2145</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <f aca="false">H8*Assumptions!$B$5</f>
+        <v>3510</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <f aca="false">I8*Assumptions!$B$5</f>
+        <v>6435</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <f aca="false">J8*Assumptions!$B$5</f>
+        <v>10725</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <f aca="false">K8*Assumptions!$B$5</f>
+        <v>16575</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <f aca="false">L8*Assumptions!$B$5</f>
+        <v>23985</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <f aca="false">M8*Assumptions!$B$5</f>
+        <v>33540</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <f aca="false">N8*Assumptions!$B$5</f>
+        <v>39780</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <f aca="false">O8*Assumptions!$B$5</f>
+        <v>41332.2</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <f aca="false">P8*Assumptions!$B$5</f>
+        <v>42868.878</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <f aca="false">Q8*Assumptions!$B$5</f>
+        <v>44390.18922</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <f aca="false">R8*Assumptions!$B$5</f>
+        <v>45896.2873278</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <f aca="false">S8*Assumptions!$B$5</f>
+        <v>47387.324454522</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <f aca="false">T8*Assumptions!$B$5</f>
+        <v>48863.4512099768</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <f aca="false">U8*Assumptions!$B$5</f>
+        <v>50324.816697877</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <f aca="false">V8*Assumptions!$B$5</f>
+        <v>51771.5685308983</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <f aca="false">W8*Assumptions!$B$5</f>
+        <v>53203.8528455893</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <f aca="false">X8*Assumptions!$B$5</f>
+        <v>54621.8143171334</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <f aca="false">Y8*Assumptions!$B$5</f>
+        <v>56025.596173962</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>101790</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <f aca="false">SUM(N11:Y11)</f>
+        <v>576465.978777759</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">B10+B11</f>
+        <v>295</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <f aca="false">C10+C11</f>
+        <v>885</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <f aca="false">D10+D11</f>
+        <v>1475</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <f aca="false">E10+E11</f>
+        <v>2065</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <f aca="false">F10+F11</f>
+        <v>2655</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">G10+G11</f>
+        <v>3245</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <f aca="false">H10+H11</f>
+        <v>5310</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <f aca="false">I10+I11</f>
+        <v>9735</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <f aca="false">J10+J11</f>
+        <v>16225</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <f aca="false">K10+K11</f>
+        <v>25075</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <f aca="false">L10+L11</f>
+        <v>36285</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <f aca="false">M10+M11</f>
+        <v>50740</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <f aca="false">N10+N11</f>
+        <v>60180</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <f aca="false">O10+O11</f>
+        <v>62528.2</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <f aca="false">P10+P11</f>
+        <v>64852.918</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <f aca="false">Q10+Q11</f>
+        <v>67154.38882</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <f aca="false">R10+R11</f>
+        <v>69432.8449318</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <f aca="false">S10+S11</f>
+        <v>71688.516482482</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <f aca="false">T10+T11</f>
+        <v>73921.6313176572</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <f aca="false">U10+U11</f>
+        <v>76132.4150044806</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <f aca="false">V10+V11</f>
+        <v>78321.0908544358</v>
+      </c>
+      <c r="W12" s="7" t="n">
+        <f aca="false">W10+W11</f>
+        <v>80487.8799458915</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <f aca="false">X10+X11</f>
+        <v>82633.0011464325</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <f aca="false">Y10+Y11</f>
+        <v>84756.6711349682</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>153990</v>
+      </c>
+      <c r="AA12" s="7" t="n">
+        <f aca="false">SUM(N12:Y12)</f>
+        <v>872089.557638148</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <f aca="false">B8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <f aca="false">C8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>117</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <f aca="false">D8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>195</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <f aca="false">E8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>273</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <f aca="false">F8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>351</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <f aca="false">G8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>429</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <f aca="false">H8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>702</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <f aca="false">I8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>1287</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <f aca="false">J8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>2145</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <f aca="false">K8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>3315</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <f aca="false">L8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>4797</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <f aca="false">M8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>6708</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <f aca="false">N8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>7956</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <f aca="false">O8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>8266.44</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <f aca="false">P8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>8573.7756</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <f aca="false">Q8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>8878.037844</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <f aca="false">R8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>9179.25746556</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <f aca="false">S8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>9477.4648909044</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <f aca="false">T8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>9772.69024199536</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <f aca="false">U8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>10064.9633395754</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <f aca="false">V8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>10354.3137061797</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <f aca="false">W8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>10640.7705691179</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <f aca="false">X8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>10924.3628634267</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <f aca="false">Y8*(Assumptions!$B$9+Assumptions!$B$10+Assumptions!$B$11+Assumptions!$B$12+Assumptions!$B$13)</f>
+        <v>11205.1192347924</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <f aca="false">SUM(B14:M14)</f>
+        <v>20358</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <f aca="false">SUM(N14:Y14)</f>
+        <v>115293.195755552</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <f aca="false">B7*Assumptions!$B$15</f>
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <f aca="false">C7*Assumptions!$B$15</f>
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <f aca="false">D7*Assumptions!$B$15</f>
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <f aca="false">E7*Assumptions!$B$15</f>
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <f aca="false">F7*Assumptions!$B$15</f>
+        <v>54</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <f aca="false">G7*Assumptions!$B$15</f>
+        <v>66</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <f aca="false">H7*Assumptions!$B$15</f>
+        <v>108</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <f aca="false">I7*Assumptions!$B$15</f>
+        <v>198</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <f aca="false">J7*Assumptions!$B$15</f>
+        <v>330</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <f aca="false">K7*Assumptions!$B$15</f>
+        <v>510</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <f aca="false">L7*Assumptions!$B$15</f>
+        <v>738</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <f aca="false">M7*Assumptions!$B$15</f>
+        <v>1032</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <f aca="false">N7*Assumptions!$B$15</f>
+        <v>1224</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <f aca="false">O7*Assumptions!$B$15</f>
+        <v>1271.76</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <f aca="false">P7*Assumptions!$B$15</f>
+        <v>1319.0424</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <f aca="false">Q7*Assumptions!$B$15</f>
+        <v>1365.851976</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <f aca="false">R7*Assumptions!$B$15</f>
+        <v>1412.19345624</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <f aca="false">S7*Assumptions!$B$15</f>
+        <v>1458.0715216776</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <f aca="false">T7*Assumptions!$B$15</f>
+        <v>1503.49080646082</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <f aca="false">U7*Assumptions!$B$15</f>
+        <v>1548.45589839622</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <f aca="false">V7*Assumptions!$B$15</f>
+        <v>1592.97133941225</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <f aca="false">W7*Assumptions!$B$15</f>
+        <v>1637.04162601813</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <f aca="false">X7*Assumptions!$B$15</f>
+        <v>1680.67120975795</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <f aca="false">Y7*Assumptions!$B$15</f>
+        <v>1723.86449766037</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <f aca="false">SUM(B15:M15)</f>
+        <v>3132</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <f aca="false">SUM(N15:Y15)</f>
+        <v>17737.4147316233</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <f aca="false">B7*Assumptions!$B$17</f>
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <f aca="false">C7*Assumptions!$B$17</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <f aca="false">D7*Assumptions!$B$17</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <f aca="false">E7*Assumptions!$B$17</f>
+        <v>7</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <f aca="false">F7*Assumptions!$B$17</f>
+        <v>9</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <f aca="false">G7*Assumptions!$B$17</f>
+        <v>11</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <f aca="false">H7*Assumptions!$B$17</f>
+        <v>18</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <f aca="false">I7*Assumptions!$B$17</f>
+        <v>33</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <f aca="false">J7*Assumptions!$B$17</f>
+        <v>55</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <f aca="false">K7*Assumptions!$B$17</f>
+        <v>85</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <f aca="false">L7*Assumptions!$B$17</f>
+        <v>123</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <f aca="false">M7*Assumptions!$B$17</f>
+        <v>172</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <f aca="false">N7*Assumptions!$B$17</f>
+        <v>204</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <f aca="false">O7*Assumptions!$B$17</f>
+        <v>211.96</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <f aca="false">P7*Assumptions!$B$17</f>
+        <v>219.8404</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <f aca="false">Q7*Assumptions!$B$17</f>
+        <v>227.641996</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <f aca="false">R7*Assumptions!$B$17</f>
+        <v>235.36557604</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <f aca="false">S7*Assumptions!$B$17</f>
+        <v>243.0119202796</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <f aca="false">T7*Assumptions!$B$17</f>
+        <v>250.581801076804</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <f aca="false">U7*Assumptions!$B$17</f>
+        <v>258.075983066036</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <f aca="false">V7*Assumptions!$B$17</f>
+        <v>265.495223235376</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <f aca="false">W7*Assumptions!$B$17</f>
+        <v>272.840271003022</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <f aca="false">X7*Assumptions!$B$17</f>
+        <v>280.111868292992</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <f aca="false">Y7*Assumptions!$B$17</f>
+        <v>287.310749610062</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>522</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <f aca="false">SUM(N16:Y16)</f>
+        <v>2956.23578860389</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <f aca="false">B14+B15+B16</f>
+        <v>46</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <f aca="false">C14+C15+C16</f>
+        <v>138</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <f aca="false">D14+D15+D16</f>
+        <v>230</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <f aca="false">E14+E15+E16</f>
+        <v>322</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <f aca="false">F14+F15+F16</f>
+        <v>414</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <f aca="false">G14+G15+G16</f>
+        <v>506</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <f aca="false">H14+H15+H16</f>
+        <v>828</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <f aca="false">I14+I15+I16</f>
+        <v>1518</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <f aca="false">J14+J15+J16</f>
+        <v>2530</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <f aca="false">K14+K15+K16</f>
+        <v>3910</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <f aca="false">L14+L15+L16</f>
+        <v>5658</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <f aca="false">M14+M15+M16</f>
+        <v>7912</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <f aca="false">N14+N15+N16</f>
+        <v>9384</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <f aca="false">O14+O15+O16</f>
+        <v>9750.16</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <f aca="false">P14+P15+P16</f>
+        <v>10112.6584</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <f aca="false">Q14+Q15+Q16</f>
+        <v>10471.531816</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <f aca="false">R14+R15+R16</f>
+        <v>10826.81649784</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <f aca="false">S14+S15+S16</f>
+        <v>11178.5483328616</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <f aca="false">T14+T15+T16</f>
+        <v>11526.762849533</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <f aca="false">U14+U15+U16</f>
+        <v>11871.4952210377</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <f aca="false">V14+V15+V16</f>
+        <v>12212.7802688273</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <f aca="false">W14+W15+W16</f>
+        <v>12550.652466139</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <f aca="false">X14+X15+X16</f>
+        <v>12885.1459414776</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <f aca="false">Y14+Y15+Y16</f>
+        <v>13216.2944820628</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>24012</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <f aca="false">SUM(N17:Y17)</f>
+        <v>135986.846275779</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <f aca="false">B12-B17</f>
+        <v>249</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <f aca="false">C12-C17</f>
+        <v>747</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <f aca="false">D12-D17</f>
+        <v>1245</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <f aca="false">E12-E17</f>
+        <v>1743</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <f aca="false">F12-F17</f>
+        <v>2241</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">G12-G17</f>
+        <v>2739</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <f aca="false">H12-H17</f>
+        <v>4482</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <f aca="false">I12-I17</f>
+        <v>8217</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <f aca="false">J12-J17</f>
+        <v>13695</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <f aca="false">K12-K17</f>
+        <v>21165</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <f aca="false">L12-L17</f>
+        <v>30627</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <f aca="false">M12-M17</f>
+        <v>42828</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <f aca="false">N12-N17</f>
+        <v>50796</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <f aca="false">O12-O17</f>
+        <v>52778.04</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <f aca="false">P12-P17</f>
+        <v>54740.2596</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <f aca="false">Q12-Q17</f>
+        <v>56682.857004</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <f aca="false">R12-R17</f>
+        <v>58606.02843396</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <f aca="false">S12-S17</f>
+        <v>60509.9681496204</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <f aca="false">T12-T17</f>
+        <v>62394.8684681242</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <f aca="false">U12-U17</f>
+        <v>64260.919783443</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <f aca="false">V12-V17</f>
+        <v>66108.3105856085</v>
+      </c>
+      <c r="W18" s="7" t="n">
+        <f aca="false">W12-W17</f>
+        <v>67937.2274797524</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <f aca="false">X12-X17</f>
+        <v>69747.8552049549</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <f aca="false">Y12-Y17</f>
+        <v>71540.3766529054</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>129978</v>
+      </c>
+      <c r="AA18" s="7" t="n">
+        <f aca="false">SUM(N18:Y18)</f>
+        <v>736102.711362369</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <f aca="false">B18/B12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <f aca="false">C18/C12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <f aca="false">D18/D12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <f aca="false">E18/E12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <f aca="false">F18/F12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <f aca="false">G18/G12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <f aca="false">H18/H12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <f aca="false">I18/I12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <f aca="false">J18/J12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <f aca="false">K18/K12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <f aca="false">L18/L12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <f aca="false">M18/M12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <f aca="false">N18/N12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <f aca="false">O18/O12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <f aca="false">P18/P12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <f aca="false">Q18/Q12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <f aca="false">R18/R12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <f aca="false">S18/S12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <f aca="false">T18/T12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <f aca="false">U18/U12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <f aca="false">V18/V12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <f aca="false">W18/W12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <f aca="false">X18/X12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <f aca="false">Y18/Y12</f>
+        <v>0.844067796610169</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <f aca="false">Z18/Z12</f>
+        <v>0.84406779661017</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <f aca="false">AA18/AA12</f>
+        <v>0.84406779661017</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <f aca="false">B3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <f aca="false">C3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <f aca="false">D3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <f aca="false">E3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <f aca="false">F3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <f aca="false">G3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>400</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <f aca="false">H3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2400</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <f aca="false">I3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>3600</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <f aca="false">J3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>5200</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <f aca="false">K3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>6800</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <f aca="false">L3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>8400</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <f aca="false">M3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>11200</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <f aca="false">N3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <f aca="false">O3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <f aca="false">P3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <f aca="false">Q3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <f aca="false">R3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <f aca="false">S3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <f aca="false">T3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <f aca="false">U3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <f aca="false">V3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <f aca="false">W3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <f aca="false">X3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <f aca="false">Y3*(Assumptions!$B$19+Assumptions!$B$20)</f>
+        <v>2000</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <f aca="false">SUM(B21:M21)</f>
+        <v>40000</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <f aca="false">SUM(N21:Y21)</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <f aca="false">B7*Assumptions!$B$16</f>
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <f aca="false">C7*Assumptions!$B$16</f>
+        <v>15</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <f aca="false">D7*Assumptions!$B$16</f>
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <f aca="false">E7*Assumptions!$B$16</f>
+        <v>35</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <f aca="false">F7*Assumptions!$B$16</f>
+        <v>45</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <f aca="false">G7*Assumptions!$B$16</f>
+        <v>55</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <f aca="false">H7*Assumptions!$B$16</f>
+        <v>90</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <f aca="false">I7*Assumptions!$B$16</f>
+        <v>165</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <f aca="false">J7*Assumptions!$B$16</f>
+        <v>275</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <f aca="false">K7*Assumptions!$B$16</f>
+        <v>425</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <f aca="false">L7*Assumptions!$B$16</f>
+        <v>615</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <f aca="false">M7*Assumptions!$B$16</f>
+        <v>860</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <f aca="false">N7*Assumptions!$B$16</f>
+        <v>1020</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <f aca="false">O7*Assumptions!$B$16</f>
+        <v>1059.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <f aca="false">P7*Assumptions!$B$16</f>
+        <v>1099.202</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <f aca="false">Q7*Assumptions!$B$16</f>
+        <v>1138.20998</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <f aca="false">R7*Assumptions!$B$16</f>
+        <v>1176.8278802</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <f aca="false">S7*Assumptions!$B$16</f>
+        <v>1215.059601398</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <f aca="false">T7*Assumptions!$B$16</f>
+        <v>1252.90900538402</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <f aca="false">U7*Assumptions!$B$16</f>
+        <v>1290.37991533018</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <f aca="false">V7*Assumptions!$B$16</f>
+        <v>1327.47611617688</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <f aca="false">W7*Assumptions!$B$16</f>
+        <v>1364.20135501511</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <f aca="false">X7*Assumptions!$B$16</f>
+        <v>1400.55934146496</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <f aca="false">Y7*Assumptions!$B$16</f>
+        <v>1436.55374805031</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>2610</v>
+      </c>
+      <c r="AA22" s="3" t="n">
+        <f aca="false">SUM(N22:Y22)</f>
+        <v>14781.1789430195</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <f aca="false">IF(Assumptions!B33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!B33&gt;=Assumptions!$B$22,B5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <f aca="false">IF(Assumptions!C33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!C33&gt;=Assumptions!$B$22,C5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <f aca="false">IF(Assumptions!D33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!D33&gt;=Assumptions!$B$22,D5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <f aca="false">IF(Assumptions!E33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!E33&gt;=Assumptions!$B$22,E5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <f aca="false">IF(Assumptions!F33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!F33&gt;=Assumptions!$B$22,F5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <f aca="false">IF(Assumptions!G33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!G33&gt;=Assumptions!$B$22,G5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <f aca="false">IF(Assumptions!H33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!H33&gt;=Assumptions!$B$22,H5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <f aca="false">IF(Assumptions!I33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!I33&gt;=Assumptions!$B$22,I5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <f aca="false">IF(Assumptions!J33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!J33&gt;=Assumptions!$B$22,J5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <f aca="false">IF(Assumptions!K33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!K33&gt;=Assumptions!$B$22,K5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <f aca="false">IF(Assumptions!L33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!L33&gt;=Assumptions!$B$22,L5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <f aca="false">IF(Assumptions!M33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!M33&gt;=Assumptions!$B$22,M5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <f aca="false">IF(Assumptions!N33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!N33&gt;=Assumptions!$B$22,N5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <f aca="false">IF(Assumptions!O33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!O33&gt;=Assumptions!$B$22,O5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <f aca="false">IF(Assumptions!P33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!P33&gt;=Assumptions!$B$22,P5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <f aca="false">IF(Assumptions!Q33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Q33&gt;=Assumptions!$B$22,Q5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <f aca="false">IF(Assumptions!R33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!R33&gt;=Assumptions!$B$22,R5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <f aca="false">IF(Assumptions!S33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!S33&gt;=Assumptions!$B$22,S5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <f aca="false">IF(Assumptions!T33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!T33&gt;=Assumptions!$B$22,T5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <f aca="false">IF(Assumptions!U33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!U33&gt;=Assumptions!$B$22,U5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <f aca="false">IF(Assumptions!V33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!V33&gt;=Assumptions!$B$22,V5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <f aca="false">IF(Assumptions!W33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!W33&gt;=Assumptions!$B$22,W5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <f aca="false">IF(Assumptions!X33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!X33&gt;=Assumptions!$B$22,X5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <f aca="false">IF(Assumptions!Y33&gt;=Assumptions!$B$22,1,0)+IF(AND(Assumptions!Y33&gt;=Assumptions!$B$22,Y5&gt;=Assumptions!$B$23),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <f aca="false">M23</f>
+        <v>1</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <f aca="false">Y23</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <f aca="false">B23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <f aca="false">C23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <f aca="false">D23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <f aca="false">E23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <f aca="false">F23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <f aca="false">G23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <f aca="false">H23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <f aca="false">I23*Assumptions!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <f aca="false">J23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <f aca="false">K23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <f aca="false">L23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <f aca="false">M23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <f aca="false">N23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <f aca="false">O23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <f aca="false">P23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <f aca="false">Q23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <f aca="false">R23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <f aca="false">S23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <f aca="false">T23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <f aca="false">U23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <f aca="false">V23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <f aca="false">W23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <f aca="false">X23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <f aca="false">Y23*Assumptions!$B$21</f>
+        <v>9000</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <f aca="false">SUM(B24:M24)</f>
+        <v>36000</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <f aca="false">SUM(N24:Y24)</f>
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <f aca="false">Assumptions!$B$24</f>
+        <v>150</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <f aca="false">SUM(B25:M25)</f>
+        <v>1800</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <f aca="false">SUM(N25:Y25)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <f aca="false">Assumptions!$B$25</f>
+        <v>500</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <f aca="false">SUM(B26:M26)</f>
+        <v>6000</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <f aca="false">SUM(N26:Y26)</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <f aca="false">Assumptions!$B$26</f>
+        <v>1200</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>14400</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <f aca="false">SUM(N27:Y27)</f>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <f aca="false">Assumptions!$B$27</f>
+        <v>7500</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <f aca="false">SUM(B28:M28)</f>
+        <v>90000</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <f aca="false">SUM(N28:Y28)</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <f aca="false">SUM(B21:B28)</f>
+        <v>9755</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <f aca="false">SUM(C21:C28)</f>
+        <v>9765</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <f aca="false">SUM(D21:D28)</f>
+        <v>9775</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <f aca="false">SUM(E21:E28)</f>
+        <v>9785</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <f aca="false">SUM(F21:F28)</f>
+        <v>9795</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <f aca="false">SUM(G21:G28)</f>
+        <v>9805</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <f aca="false">SUM(H21:H28)</f>
+        <v>11840</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <f aca="false">SUM(I21:I28)</f>
+        <v>13115</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <f aca="false">SUM(J21:J28)</f>
+        <v>23826</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <f aca="false">SUM(K21:K28)</f>
+        <v>25576</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <f aca="false">SUM(L21:L28)</f>
+        <v>27366</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <f aca="false">SUM(M21:M28)</f>
+        <v>30411</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <f aca="false">SUM(N21:N28)</f>
+        <v>21371</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <f aca="false">SUM(O21:O28)</f>
+        <v>21410.8</v>
+      </c>
+      <c r="P29" s="7" t="n">
+        <f aca="false">SUM(P21:P28)</f>
+        <v>21450.202</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <f aca="false">SUM(Q21:Q28)</f>
+        <v>21489.20998</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <f aca="false">SUM(R21:R28)</f>
+        <v>21527.8278802</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <f aca="false">SUM(S21:S28)</f>
+        <v>21566.059601398</v>
+      </c>
+      <c r="T29" s="7" t="n">
+        <f aca="false">SUM(T21:T28)</f>
+        <v>21603.909005384</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <f aca="false">SUM(U21:U28)</f>
+        <v>21641.3799153302</v>
+      </c>
+      <c r="V29" s="7" t="n">
+        <f aca="false">SUM(V21:V28)</f>
+        <v>21678.4761161769</v>
+      </c>
+      <c r="W29" s="7" t="n">
+        <f aca="false">SUM(W21:W28)</f>
+        <v>21715.2013550151</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <f aca="false">SUM(X21:X28)</f>
+        <v>21751.559341465</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <f aca="false">SUM(Y21:Y28)</f>
+        <v>21787.5537480503</v>
+      </c>
+      <c r="Z29" s="7" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>190814</v>
+      </c>
+      <c r="AA29" s="7" t="n">
+        <f aca="false">SUM(N29:Y29)</f>
+        <v>258993.178943019</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <f aca="false">B18-B29</f>
+        <v>-9506</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <f aca="false">C18-C29</f>
+        <v>-9018</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <f aca="false">D18-D29</f>
+        <v>-8530</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <f aca="false">E18-E29</f>
+        <v>-8042</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <f aca="false">F18-F29</f>
+        <v>-7554</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <f aca="false">G18-G29</f>
+        <v>-7066</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <f aca="false">H18-H29</f>
+        <v>-7358</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <f aca="false">I18-I29</f>
+        <v>-4898</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <f aca="false">J18-J29</f>
+        <v>-10131</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <f aca="false">K18-K29</f>
+        <v>-4411</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <f aca="false">L18-L29</f>
+        <v>3261</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <f aca="false">M18-M29</f>
+        <v>12417</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <f aca="false">N18-N29</f>
+        <v>29425</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <f aca="false">O18-O29</f>
+        <v>31367.24</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <f aca="false">P18-P29</f>
+        <v>33290.0576</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <f aca="false">Q18-Q29</f>
+        <v>35193.647024</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <f aca="false">R18-R29</f>
+        <v>37078.20055376</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <f aca="false">S18-S29</f>
+        <v>38943.9085482224</v>
+      </c>
+      <c r="T30" s="7" t="n">
+        <f aca="false">T18-T29</f>
+        <v>40790.9594627402</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <f aca="false">U18-U29</f>
+        <v>42619.5398681128</v>
+      </c>
+      <c r="V30" s="7" t="n">
+        <f aca="false">V18-V29</f>
+        <v>44429.8344694317</v>
+      </c>
+      <c r="W30" s="7" t="n">
+        <f aca="false">W18-W29</f>
+        <v>46222.0261247373</v>
+      </c>
+      <c r="X30" s="7" t="n">
+        <f aca="false">X18-X29</f>
+        <v>47996.29586349</v>
+      </c>
+      <c r="Y30" s="7" t="n">
+        <f aca="false">Y18-Y29</f>
+        <v>49752.8229048551</v>
+      </c>
+      <c r="Z30" s="7" t="n">
+        <f aca="false">SUM(B30:M30)</f>
+        <v>-60836</v>
+      </c>
+      <c r="AA30" s="7" t="n">
+        <f aca="false">SUM(N30:Y30)</f>
+        <v>477109.532419349</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:B30))-0)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:C30))-SUM($B31:B31))</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:D30))-SUM($B31:C31))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:E30))-SUM($B31:D31))</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:F30))-SUM($B31:E31))</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:G30))-SUM($B31:F31))</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:H30))-SUM($B31:G31))</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:I30))-SUM($B31:H31))</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:J30))-SUM($B31:I31))</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:K30))-SUM($B31:J31))</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:L30))-SUM($B31:K31))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:M30))-SUM($B31:L31))</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:N30))-SUM($B31:M31))</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:O30))-SUM($B31:N31))</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:P30))-SUM($B31:O31))</f>
+        <v>8311.5744</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Q30))-SUM($B31:P31))</f>
+        <v>8798.411756</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:R30))-SUM($B31:Q31))</f>
+        <v>9269.55013844</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:S30))-SUM($B31:R31))</f>
+        <v>9735.9771370556</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:T30))-SUM($B31:S31))</f>
+        <v>10197.739865685</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:U30))-SUM($B31:T31))</f>
+        <v>10654.8849670282</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:V30))-SUM($B31:U31))</f>
+        <v>11107.4586173579</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:W30))-SUM($B31:V31))</f>
+        <v>11555.5065311843</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:X30))-SUM($B31:W31))</f>
+        <v>11999.0739658725</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <f aca="false">MAX(0,Assumptions!$B$28*MAX(0,SUM($B30:Y30))-SUM($B31:X31))</f>
+        <v>12438.2057262138</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <f aca="false">SUM(N31:Y31)</f>
+        <v>104068.383104837</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">B30-B31</f>
+        <v>-9506</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <f aca="false">C30-C31</f>
+        <v>-9018</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <f aca="false">D30-D31</f>
+        <v>-8530</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <f aca="false">E30-E31</f>
+        <v>-8042</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <f aca="false">F30-F31</f>
+        <v>-7554</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <f aca="false">G30-G31</f>
+        <v>-7066</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <f aca="false">H30-H31</f>
+        <v>-7358</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <f aca="false">I30-I31</f>
+        <v>-4898</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <f aca="false">J30-J31</f>
+        <v>-10131</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <f aca="false">K30-K31</f>
+        <v>-4411</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <f aca="false">L30-L31</f>
+        <v>3261</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <f aca="false">M30-M31</f>
+        <v>12417</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <f aca="false">N30-N31</f>
+        <v>29425</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <f aca="false">O30-O31</f>
+        <v>31367.24</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <f aca="false">P30-P31</f>
+        <v>24978.4832</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <f aca="false">Q30-Q31</f>
+        <v>26395.235268</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <f aca="false">R30-R31</f>
+        <v>27808.65041532</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <f aca="false">S30-S31</f>
+        <v>29207.9314111668</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <f aca="false">T30-T31</f>
+        <v>30593.2195970551</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <f aca="false">U30-U31</f>
+        <v>31964.6549010846</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <f aca="false">V30-V31</f>
+        <v>33322.3758520737</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <f aca="false">W30-W31</f>
+        <v>34666.519593553</v>
+      </c>
+      <c r="X32" s="7" t="n">
+        <f aca="false">X30-X31</f>
+        <v>35997.2218976175</v>
+      </c>
+      <c r="Y32" s="7" t="n">
+        <f aca="false">Y30-Y31</f>
+        <v>37314.6171786413</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <f aca="false">SUM(B32:M32)</f>
+        <v>-60836</v>
+      </c>
+      <c r="AA32" s="7" t="n">
+        <f aca="false">SUM(N32:Y32)</f>
+        <v>373041.149314512</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <f aca="false">SUM($B32:B32)</f>
+        <v>-9506</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <f aca="false">SUM($B32:C32)</f>
+        <v>-18524</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <f aca="false">SUM($B32:D32)</f>
+        <v>-27054</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <f aca="false">SUM($B32:E32)</f>
+        <v>-35096</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <f aca="false">SUM($B32:F32)</f>
+        <v>-42650</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <f aca="false">SUM($B32:G32)</f>
+        <v>-49716</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <f aca="false">SUM($B32:H32)</f>
+        <v>-57074</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <f aca="false">SUM($B32:I32)</f>
+        <v>-61972</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <f aca="false">SUM($B32:J32)</f>
+        <v>-72103</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <f aca="false">SUM($B32:K32)</f>
+        <v>-76514</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <f aca="false">SUM($B32:L32)</f>
+        <v>-73253</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <f aca="false">SUM($B32:M32)</f>
+        <v>-60836</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <f aca="false">SUM($B32:N32)</f>
+        <v>-31411</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <f aca="false">SUM($B32:O32)</f>
+        <v>-43.7600000000057</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <f aca="false">SUM($B32:P32)</f>
+        <v>24934.7232</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <f aca="false">SUM($B32:Q32)</f>
+        <v>51329.958468</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <f aca="false">SUM($B32:R32)</f>
+        <v>79138.60888332</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <f aca="false">SUM($B32:S32)</f>
+        <v>108346.540294487</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <f aca="false">SUM($B32:T32)</f>
+        <v>138939.759891542</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <f aca="false">SUM($B32:U32)</f>
+        <v>170904.414792626</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <f aca="false">SUM($B32:V32)</f>
+        <v>204226.7906447</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <f aca="false">SUM($B32:W32)</f>
+        <v>238893.310238253</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <f aca="false">SUM($B32:X32)</f>
+        <v>274890.532135871</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <f aca="false">SUM($B32:Y32)</f>
+        <v>312205.149314512</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <f aca="false">M33</f>
+        <v>-60836</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <f aca="false">Y33</f>
+        <v>312205.149314512</v>
       </c>
     </row>
   </sheetData>
